--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -955,7 +955,7 @@
         <v>7.79</v>
       </c>
       <c r="P7" t="n">
-        <v>7.8</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="8">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.68</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="9">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>5.23</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="10">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>6.04</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="11">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>7.43</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>8.640000000000001</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="13">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1325,6 +1325,21 @@
       </c>
       <c r="P29" t="n">
         <v>2.08</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Số ngày kể từ lần chào bán tín phiếu NHNN gần nhất (hút thanh khoản)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ngày</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -1545,7 +1560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1681,6 +1696,126 @@
         <v>27.62</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cơ cấu GDP — Nông, Lâm nghiệp &amp; Thủy sản</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>10.61</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cơ cấu GDP — Công nghiệp &amp; Xây dựng</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>37.66</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cơ cấu GDP — Dịch vụ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>43.52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cơ cấu GDP — Thuế sản phẩm trừ trợ cấp sản phẩm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.210000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cơ cấu vốn đầu tư — Khu vực Nhà nước</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cơ cấu vốn đầu tư — Khu vực ngoài Nhà nước (tư nhân)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cơ cấu vốn đầu tư — Khu vực FDI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FDI đăng ký (cấp mới + điều chỉnh + góp vốn mua cổ phần, lũy kế)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>tỷ USD</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>34.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1692,7 +1827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1723,6 +1858,7 @@
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1866,6 +2002,11 @@
           <t>2026-07-06</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2006,6 +2147,21 @@
       </c>
       <c r="Z4" t="n">
         <v>120.69</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Khối ngoại mua/bán ròng HOSE (theo phiên)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tỷ VND</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>1369.1</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -955,7 +955,7 @@
         <v>7.79</v>
       </c>
       <c r="P7" t="n">
-        <v>7.18</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.28</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="9">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.92</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="10">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>5.5</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="11">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>6.5</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="12">
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1249,7 +1249,7 @@
         <v>26270</v>
       </c>
       <c r="P24" t="n">
-        <v>26191.27</v>
+        <v>26178.22</v>
       </c>
     </row>
     <row r="25">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>13.53</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="29">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="30">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -1827,7 +1827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1859,6 +1859,11 @@
     <col width="12" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2007,6 +2012,31 @@
           <t>2026-07-10</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2103,6 +2133,9 @@
       <c r="AB3" t="n">
         <v>69.56</v>
       </c>
+      <c r="AG3" t="n">
+        <v>81.62</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2148,6 +2181,9 @@
       <c r="Z4" t="n">
         <v>120.69</v>
       </c>
+      <c r="AC4" t="n">
+        <v>120.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2162,6 +2198,9 @@
       </c>
       <c r="AC5" t="n">
         <v>1369.1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-25.71</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -955,7 +955,7 @@
         <v>7.79</v>
       </c>
       <c r="P7" t="n">
-        <v>8.029999999999999</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="8">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.11</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="9">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.69</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="10">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>5.59</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="11">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>7.27</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="12">
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="15">
@@ -1249,7 +1249,7 @@
         <v>26270</v>
       </c>
       <c r="P24" t="n">
-        <v>26178.22</v>
+        <v>26215.98</v>
       </c>
     </row>
     <row r="25">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>13.34</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="29">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="30">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -1827,7 +1827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1864,6 +1864,7 @@
     <col width="12" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2037,6 +2038,11 @@
           <t>2026-07-16</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2201,6 +2207,9 @@
       </c>
       <c r="AH5" t="n">
         <v>-25.71</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-678.0599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1633,7 +1633,7 @@
         <v>7.79</v>
       </c>
       <c r="P7" t="n">
-        <v>8.039999999999999</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="8">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.33</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="9">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="10">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="11">
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>7.07</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="12">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>8.15</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="13">
@@ -4413,7 +4413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4452,6 +4452,9 @@
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4635,6 +4638,21 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4734,6 +4752,9 @@
       <c r="AG3" t="n">
         <v>81.62</v>
       </c>
+      <c r="AM3" t="n">
+        <v>86.98999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4781,6 +4802,9 @@
       </c>
       <c r="AC4" t="n">
         <v>120.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>120.53</v>
       </c>
     </row>
     <row r="5">

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -675,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY38"/>
+  <dimension ref="A1:DY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1930,7 +1931,7 @@
         <v>26270</v>
       </c>
       <c r="P24" t="n">
-        <v>26250.54</v>
+        <v>26278.14</v>
       </c>
     </row>
     <row r="25">
@@ -1990,7 +1991,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>12.48</v>
+        <v>10.43598551518464</v>
       </c>
     </row>
     <row r="29">
@@ -2005,7 +2006,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.94</v>
+        <v>1.621001140786313</v>
       </c>
     </row>
     <row r="30">
@@ -3869,6 +3870,66 @@
       </c>
       <c r="DY38" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>VN-Index P/E (ex-VIN)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10.43598551518464</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>VN-Index P/B (ex-VIN)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1.621001140786313</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>VN-Index P/E (headline, có VIN)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>12.38</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>VN-Index P/B (headline, có VIN)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1.92</v>
       </c>
     </row>
   </sheetData>
@@ -4413,7 +4474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4452,6 +4513,7 @@
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4635,6 +4697,11 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4805,6 +4872,291 @@
       </c>
       <c r="AJ5" t="n">
         <v>-491.72</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-1328.11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Chỉ báo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Đơn vị</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2026-W30</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2026-W28</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lãi suất tái cấp vốn (NHNN)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 3 tháng</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7.63</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng qua đêm (O/N)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 1 tuần</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 2 tuần</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 1 tháng</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 6 tháng</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 9 tháng</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lãi suất OMO kỳ hạn 7 ngày (bơm thanh khoản)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lãi suất huy động 12T — Vietcombank (nhóm lớn)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lãi suất huy động 12T — VietinBank (nhóm lớn)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lãi suất huy động 12T — NamABank (nhóm nhỏ)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lãi suất huy động online 12 tháng — CAO NHẤT thị trường (đa ngân hàng)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lãi suất huy động online 12 tháng — TRUNG BÌNH thị trường (đa ngân hàng)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Số ngày kể từ lần chào bán tín phiếu NHNN gần nhất (hút thanh khoản)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ngày</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Lãi suất iPower TCBS (cao nhất)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -675,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY38"/>
+  <dimension ref="A1:DY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1930,7 +1931,7 @@
         <v>26270</v>
       </c>
       <c r="P24" t="n">
-        <v>26250.54</v>
+        <v>26278.14</v>
       </c>
     </row>
     <row r="25">
@@ -3869,6 +3870,66 @@
       </c>
       <c r="DY38" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>VN-Index P/E (ex-VIN)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10.43598551518464</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>VN-Index P/B (ex-VIN)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1.621001140786313</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>VN-Index P/E (headline, có VIN)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>12.38</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>VN-Index P/B (headline, có VIN)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1.92</v>
       </c>
     </row>
   </sheetData>
@@ -4413,7 +4474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM5"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4455,6 +4516,7 @@
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4653,6 +4715,11 @@
           <t>2026-07-20</t>
         </is>
       </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4829,6 +4896,141 @@
       </c>
       <c r="AJ5" t="n">
         <v>-491.72</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-1328.11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Chỉ báo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Đơn vị</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2026-W30</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2026-W28</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lãi suất huy động 12T — Vietcombank (nhóm lớn)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lãi suất huy động 12T — VietinBank (nhóm lớn)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lãi suất huy động 12T — NamABank (nhóm nhỏ)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lãi suất huy động online 12 tháng — CAO NHẤT thị trường (đa ngân hàng)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lãi suất huy động online 12 tháng — TRUNG BÌNH thị trường (đa ngân hàng)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lãi suất iPower TCBS (cao nhất)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -4912,7 +4912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5033,6 +5033,156 @@
         <v>9</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lãi suất tái cấp vốn (NHNN)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 3 tháng</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7.63</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng qua đêm (O/N)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 1 tuần</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 2 tuần</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 1 tháng</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 6 tháng</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 9 tháng</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lãi suất OMO kỳ hạn 7 ngày (bơm thanh khoản)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Số ngày kể từ lần chào bán tín phiếu NHNN gần nhất (hút thanh khoản)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ngày</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>268</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -665,6 +665,69 @@
         <v>2.21</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FDI giải ngân theo quý (rời rạc)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tỷ USD</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.41</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vốn đầu tư thực hiện toàn xã hội theo quý (giá hiện hành)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>nghìn tỷ đồng</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>613.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>834.3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>966.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1274.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>666.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>921.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1100.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1445.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>744.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1059.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -676,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY42"/>
+  <dimension ref="A1:DY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1931,7 +1994,7 @@
         <v>26270</v>
       </c>
       <c r="P24" t="n">
-        <v>26278.14</v>
+        <v>26252.67</v>
       </c>
     </row>
     <row r="25">
@@ -3884,7 +3947,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>10.43598551518464</v>
+        <v>10.38065446675492</v>
       </c>
     </row>
     <row r="40">
@@ -3899,7 +3962,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.621001140786313</v>
+        <v>1.612112285230998</v>
       </c>
     </row>
     <row r="41">
@@ -3914,7 +3977,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>12.38</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="42">
@@ -3929,7 +3992,490 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tỷ lệ giải ngân vốn đầu tư công (lũy kế, % kế hoạch năm)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K43" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M43" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>24</v>
+      </c>
+      <c r="O43" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="DI43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="DJ43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="DL43" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="DM43" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="DO43" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="DP43" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="DR43" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="DS43" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="DU43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="DV43" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="DX43" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="DY43" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FDI đăng ký theo tháng (rời rạc)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>tỷ USD</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3</v>
+      </c>
+      <c r="N44" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="O44" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="DU44" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="DV44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DW44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="DX44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DY44" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Kim ngạch xuất khẩu theo tháng</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>tỷ USD</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>39.8379</v>
+      </c>
+      <c r="D45" t="n">
+        <v>42.4019</v>
+      </c>
+      <c r="E45" t="n">
+        <v>43.4946</v>
+      </c>
+      <c r="F45" t="n">
+        <v>42.8774</v>
+      </c>
+      <c r="G45" t="n">
+        <v>42.1146</v>
+      </c>
+      <c r="H45" t="n">
+        <v>39.9466</v>
+      </c>
+      <c r="I45" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="J45" t="n">
+        <v>43.3028</v>
+      </c>
+      <c r="K45" t="n">
+        <v>33.1894</v>
+      </c>
+      <c r="L45" t="n">
+        <v>46.5362</v>
+      </c>
+      <c r="M45" t="n">
+        <v>45.6985</v>
+      </c>
+      <c r="N45" t="n">
+        <v>46.9994</v>
+      </c>
+      <c r="O45" t="n">
+        <v>50.7872</v>
+      </c>
+      <c r="DU45" t="n">
+        <v>33.1589</v>
+      </c>
+      <c r="DV45" t="n">
+        <v>31.1671</v>
+      </c>
+      <c r="DW45" t="n">
+        <v>38.5676</v>
+      </c>
+      <c r="DX45" t="n">
+        <v>37.7398</v>
+      </c>
+      <c r="DY45" t="n">
+        <v>39.703</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Kim ngạch nhập khẩu theo tháng</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>tỷ USD</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>36.642</v>
+      </c>
+      <c r="D46" t="n">
+        <v>40.0561</v>
+      </c>
+      <c r="E46" t="n">
+        <v>39.7902</v>
+      </c>
+      <c r="F46" t="n">
+        <v>39.9066</v>
+      </c>
+      <c r="G46" t="n">
+        <v>39.7328</v>
+      </c>
+      <c r="H46" t="n">
+        <v>38.5895</v>
+      </c>
+      <c r="I46" t="n">
+        <v>44.6866</v>
+      </c>
+      <c r="J46" t="n">
+        <v>45.2591</v>
+      </c>
+      <c r="K46" t="n">
+        <v>34.3373</v>
+      </c>
+      <c r="L46" t="n">
+        <v>47.0865</v>
+      </c>
+      <c r="M46" t="n">
+        <v>50.6404</v>
+      </c>
+      <c r="N46" t="n">
+        <v>52.4144</v>
+      </c>
+      <c r="O46" t="n">
+        <v>53.4317</v>
+      </c>
+      <c r="DU46" t="n">
+        <v>30.0605</v>
+      </c>
+      <c r="DV46" t="n">
+        <v>32.7464</v>
+      </c>
+      <c r="DW46" t="n">
+        <v>36.8745</v>
+      </c>
+      <c r="DX46" t="n">
+        <v>36.8375</v>
+      </c>
+      <c r="DY46" t="n">
+        <v>39.0836</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cán cân thương mại theo tháng (Hải quan)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>tỷ USD</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3.1959</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.3458</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3.7044</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.9708</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.3818</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.3571</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-0.6366000000000001</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-1.9563</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-1.1479</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.5503</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-4.9419</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-5.415</v>
+      </c>
+      <c r="O47" t="n">
+        <v>-2.6445</v>
+      </c>
+      <c r="DU47" t="n">
+        <v>3.0984</v>
+      </c>
+      <c r="DV47" t="n">
+        <v>-1.5793</v>
+      </c>
+      <c r="DW47" t="n">
+        <v>1.6931</v>
+      </c>
+      <c r="DX47" t="n">
+        <v>0.9023</v>
+      </c>
+      <c r="DY47" t="n">
+        <v>0.6194</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Giá trị giải ngân vốn đầu tư công (lũy kế từ đầu năm)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>nghìn tỷ đồng</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>463.2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>640.2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>736.4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>187.1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>254.1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>356.9351</v>
+      </c>
+      <c r="DI48" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="DJ48" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="DL48" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="DM48" t="n">
+        <v>190.6</v>
+      </c>
+      <c r="DO48" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="DP48" t="n">
+        <v>363.1</v>
+      </c>
+      <c r="DR48" t="n">
+        <v>495.9</v>
+      </c>
+      <c r="DS48" t="n">
+        <v>572</v>
+      </c>
+      <c r="DU48" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="DV48" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="DX48" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="DY48" t="n">
+        <v>221.8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>KBNN huy động qua đấu thầu TPCP theo tháng (sơ cấp, HNX)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>tỷ đồng</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>23375</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Giá trị giải ngân đầu tư công theo tháng (rời rạc)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>nghìn tỷ đồng</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="H50" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="N50" t="n">
+        <v>67</v>
+      </c>
+      <c r="O50" t="n">
+        <v>102.8351</v>
+      </c>
+      <c r="DI50" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="DJ50" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="DM50" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="DP50" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="DS50" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="DU50" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="DV50" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="DY50" t="n">
+        <v>56.2</v>
       </c>
     </row>
   </sheetData>
@@ -4207,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4463,6 +5009,36 @@
         <v>34.65</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FDI giải ngân theo quý (rời rạc)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>tỷ USD</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4474,7 +5050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AR15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4517,6 +5093,10 @@
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4720,6 +5300,26 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4899,6 +5499,492 @@
       </c>
       <c r="AN5" t="n">
         <v>-1328.11</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-741.47</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>920.0599999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng qua đêm (O/N)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 1 tuần</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 2 tuần</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng 1 tháng</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP thứ cấp 3 năm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP thứ cấp 5 năm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP thứ cấp 7 năm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP thứ cấp 10 năm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP thứ cấp 15 năm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE14" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NHNN bơm ròng/hút ròng qua OMO (kênh cầm cố)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>tỷ đồng</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
+        <v>-1438.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-6521.45</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-11729.43</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-2149.07</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-3660.43</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-3481.23</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-2561.86</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-4569.67</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-5812.08</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-13102.13</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-14187.42</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-1961.37</v>
       </c>
     </row>
   </sheetData>
@@ -4912,13 +5998,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4942,6 +6029,11 @@
           <t>2026-W28</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2026-W31</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4957,6 +6049,9 @@
       <c r="C2" t="n">
         <v>5.9</v>
       </c>
+      <c r="E2" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4972,6 +6067,9 @@
       <c r="C3" t="n">
         <v>5.9</v>
       </c>
+      <c r="E3" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4987,6 +6085,9 @@
       <c r="C4" t="n">
         <v>6.2</v>
       </c>
+      <c r="E4" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5002,6 +6103,9 @@
       <c r="C5" t="n">
         <v>7.8</v>
       </c>
+      <c r="E5" t="n">
+        <v>7.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5017,6 +6121,9 @@
       <c r="C6" t="n">
         <v>6.17</v>
       </c>
+      <c r="E6" t="n">
+        <v>6.17</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5047,6 +6154,9 @@
       <c r="C8" t="n">
         <v>4.5</v>
       </c>
+      <c r="E8" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5062,6 +6172,9 @@
       <c r="C9" t="n">
         <v>7.63</v>
       </c>
+      <c r="E9" t="n">
+        <v>7.38</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5137,6 +6250,9 @@
       <c r="C14" t="n">
         <v>7.8</v>
       </c>
+      <c r="E14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5152,6 +6268,9 @@
       <c r="C15" t="n">
         <v>9.26</v>
       </c>
+      <c r="E15" t="n">
+        <v>9.26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5167,6 +6286,9 @@
       <c r="C16" t="n">
         <v>4.5</v>
       </c>
+      <c r="E16" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5181,6 +6303,9 @@
       </c>
       <c r="C17" t="n">
         <v>268</v>
+      </c>
+      <c r="E17" t="n">
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -728,6 +728,90 @@
         <v>1059.5</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cơ cấu GDP — Nông, Lâm nghiệp &amp; Thủy sản</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cơ cấu GDP — Công nghiệp &amp; Xây dựng</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="G12" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="K12" t="n">
+        <v>37.15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cơ cấu GDP — Dịch vụ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="G13" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="K13" t="n">
+        <v>43.45</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cơ cấu GDP — Thuế sản phẩm trừ trợ cấp sản phẩm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -739,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY50"/>
+  <dimension ref="A1:DY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4478,6 +4562,66 @@
         <v>56.2</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Xuất khẩu YoY (Hải quan, theo tháng)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="K51" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="L51" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="M51" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="N51" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="O51" t="n">
+        <v>27.48</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Nhập khẩu YoY (Hải quan, theo tháng)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="L52" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="M52" t="n">
+        <v>37.47</v>
+      </c>
+      <c r="N52" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="O52" t="n">
+        <v>45.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -810,6 +810,69 @@
       </c>
       <c r="K14" t="n">
         <v>8.51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cơ cấu vốn đầu tư — Khu vực Nhà nước</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="K15" t="n">
+        <v>27.82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cơ cấu vốn đầu tư — Khu vực ngoài Nhà nước (tư nhân)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="K16" t="n">
+        <v>54.04</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cơ cấu vốn đầu tư — Khu vực FDI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="K17" t="n">
+        <v>18.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -5257,7 +5257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR15"/>
+  <dimension ref="A1:AR16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6194,6 +6194,51 @@
         <v>-1961.37</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lãi suất OMO kỳ hạn 7 ngày (bơm thanh khoản)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -2141,7 +2141,7 @@
         <v>26270</v>
       </c>
       <c r="P24" t="n">
-        <v>26252.67</v>
+        <v>26254</v>
       </c>
     </row>
     <row r="25">
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>10.38065446675492</v>
+        <v>10.6592122785923</v>
       </c>
     </row>
     <row r="40">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.612112285230998</v>
+        <v>1.655372223421629</v>
       </c>
     </row>
     <row r="41">
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>12.28</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="42">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="43">
@@ -5257,7 +5257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR16"/>
+  <dimension ref="A1:AS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5304,6 +5304,7 @@
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5527,6 +5528,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5713,6 +5719,9 @@
       <c r="AR5" t="n">
         <v>920.0599999999999</v>
       </c>
+      <c r="AS5" t="n">
+        <v>-85.26000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5761,6 +5770,9 @@
       <c r="AR6" t="n">
         <v>2.2</v>
       </c>
+      <c r="AS6" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5809,6 +5821,9 @@
       <c r="AR7" t="n">
         <v>4.55</v>
       </c>
+      <c r="AS7" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5857,6 +5872,9 @@
       <c r="AR8" t="n">
         <v>5.3</v>
       </c>
+      <c r="AS8" t="n">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5905,6 +5923,9 @@
       <c r="AR9" t="n">
         <v>6.9</v>
       </c>
+      <c r="AS9" t="n">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5953,6 +5974,9 @@
       <c r="AR10" t="n">
         <v>3.64</v>
       </c>
+      <c r="AS10" t="n">
+        <v>3.64</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6001,6 +6025,9 @@
       <c r="AR11" t="n">
         <v>4.21</v>
       </c>
+      <c r="AS11" t="n">
+        <v>4.21</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6049,6 +6076,9 @@
       <c r="AR12" t="n">
         <v>4.27</v>
       </c>
+      <c r="AS12" t="n">
+        <v>4.27</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6097,6 +6127,9 @@
       <c r="AR13" t="n">
         <v>4.41</v>
       </c>
+      <c r="AS13" t="n">
+        <v>4.41</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6145,6 +6178,9 @@
       <c r="AR14" t="n">
         <v>4.57</v>
       </c>
+      <c r="AS14" t="n">
+        <v>4.57</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6193,6 +6229,9 @@
       <c r="AR15" t="n">
         <v>-1961.37</v>
       </c>
+      <c r="AS15" t="n">
+        <v>283.71</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6236,6 +6275,9 @@
         <v>4.5</v>
       </c>
       <c r="AQ16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS16" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -6425,7 +6467,7 @@
         <v>7.63</v>
       </c>
       <c r="E9" t="n">
-        <v>7.38</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="10">
@@ -6503,7 +6545,7 @@
         <v>7.8</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="15">
@@ -6557,7 +6599,7 @@
         <v>268</v>
       </c>
       <c r="E17" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -2141,7 +2141,7 @@
         <v>26270</v>
       </c>
       <c r="P24" t="n">
-        <v>26254</v>
+        <v>26183.58</v>
       </c>
     </row>
     <row r="25">
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>10.6592122785923</v>
+        <v>10.72887492722224</v>
       </c>
     </row>
     <row r="40">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.655372223421629</v>
+        <v>1.666190810249435</v>
       </c>
     </row>
     <row r="41">
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>12.43</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="42">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="43">
@@ -5257,7 +5257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS16"/>
+  <dimension ref="A1:AT17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5305,6 +5305,7 @@
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="12" customWidth="1" min="44" max="44"/>
     <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="12" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5533,6 +5534,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5722,6 +5728,9 @@
       <c r="AS5" t="n">
         <v>-85.26000000000001</v>
       </c>
+      <c r="AT5" t="n">
+        <v>662.8200000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6279,6 +6288,57 @@
       </c>
       <c r="AS16" t="n">
         <v>4.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Số dư OMO đang lưu hành (kênh cầm cố)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>tỷ đồng</t>
+        </is>
+      </c>
+      <c r="AE17" t="n">
+        <v>217617.1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>211095.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>196090.35</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>187898.19</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>159415.82</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>192609.12</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>190047.26</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>181990.46</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>176178.38</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>163076.25</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>146020</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>144058.63</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>144342.34</v>
       </c>
     </row>
   </sheetData>
@@ -6467,7 +6527,7 @@
         <v>7.63</v>
       </c>
       <c r="E9" t="n">
-        <v>8.01</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="10">
@@ -6545,7 +6605,7 @@
         <v>7.8</v>
       </c>
       <c r="E14" t="n">
-        <v>8.48</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="15">
@@ -6599,7 +6659,7 @@
         <v>268</v>
       </c>
       <c r="E17" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY52"/>
+  <dimension ref="A1:DZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1018,6 +1018,7 @@
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
+    <col width="12" customWidth="1" min="130" max="130"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1666,6 +1667,11 @@
           <t>2025-05</t>
         </is>
       </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2143,6 +2149,9 @@
       <c r="P24" t="n">
         <v>26183.58</v>
       </c>
+      <c r="DZ24" t="n">
+        <v>26167.86</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4096,6 +4105,9 @@
       <c r="P39" t="n">
         <v>10.72887492722224</v>
       </c>
+      <c r="DZ39" t="n">
+        <v>10.73968416136957</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4111,6 +4123,9 @@
       <c r="P40" t="n">
         <v>1.666190810249435</v>
       </c>
+      <c r="DZ40" t="n">
+        <v>1.667869480820607</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4126,6 +4141,9 @@
       <c r="P41" t="n">
         <v>12.38</v>
       </c>
+      <c r="DZ41" t="n">
+        <v>11.77</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4140,6 +4158,9 @@
       </c>
       <c r="P42" t="n">
         <v>1.98</v>
+      </c>
+      <c r="DZ42" t="n">
+        <v>1.93</v>
       </c>
     </row>
     <row r="43">
@@ -5257,7 +5278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT17"/>
+  <dimension ref="A1:DR44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5306,6 +5327,82 @@
     <col width="12" customWidth="1" min="44" max="44"/>
     <col width="12" customWidth="1" min="45" max="45"/>
     <col width="12" customWidth="1" min="46" max="46"/>
+    <col width="12" customWidth="1" min="47" max="47"/>
+    <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="12" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
+    <col width="12" customWidth="1" min="57" max="57"/>
+    <col width="12" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
+    <col width="12" customWidth="1" min="63" max="63"/>
+    <col width="12" customWidth="1" min="64" max="64"/>
+    <col width="12" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
+    <col width="12" customWidth="1" min="69" max="69"/>
+    <col width="12" customWidth="1" min="70" max="70"/>
+    <col width="12" customWidth="1" min="71" max="71"/>
+    <col width="12" customWidth="1" min="72" max="72"/>
+    <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
+    <col width="12" customWidth="1" min="104" max="104"/>
+    <col width="12" customWidth="1" min="105" max="105"/>
+    <col width="12" customWidth="1" min="106" max="106"/>
+    <col width="12" customWidth="1" min="107" max="107"/>
+    <col width="12" customWidth="1" min="108" max="108"/>
+    <col width="12" customWidth="1" min="109" max="109"/>
+    <col width="12" customWidth="1" min="110" max="110"/>
+    <col width="12" customWidth="1" min="111" max="111"/>
+    <col width="12" customWidth="1" min="112" max="112"/>
+    <col width="12" customWidth="1" min="113" max="113"/>
+    <col width="12" customWidth="1" min="114" max="114"/>
+    <col width="12" customWidth="1" min="115" max="115"/>
+    <col width="12" customWidth="1" min="116" max="116"/>
+    <col width="12" customWidth="1" min="117" max="117"/>
+    <col width="12" customWidth="1" min="118" max="118"/>
+    <col width="12" customWidth="1" min="119" max="119"/>
+    <col width="12" customWidth="1" min="120" max="120"/>
+    <col width="12" customWidth="1" min="121" max="121"/>
+    <col width="12" customWidth="1" min="122" max="122"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5539,6 +5636,386 @@
           <t>2026-07-30</t>
         </is>
       </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2017-07-01</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>2017-10-01</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5641,6 +6118,9 @@
       <c r="AM3" t="n">
         <v>86.98999999999999</v>
       </c>
+      <c r="AQ3" t="n">
+        <v>91.81999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5692,6 +6172,9 @@
       <c r="AI4" t="n">
         <v>120.53</v>
       </c>
+      <c r="AN4" t="n">
+        <v>120.71</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5729,7 +6212,7 @@
         <v>-85.26000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>662.8200000000001</v>
+        <v>678.77</v>
       </c>
     </row>
     <row r="6">
@@ -5782,6 +6265,9 @@
       <c r="AS6" t="n">
         <v>1.3</v>
       </c>
+      <c r="AT6" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5833,6 +6319,9 @@
       <c r="AS7" t="n">
         <v>4.6</v>
       </c>
+      <c r="AT7" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5884,6 +6373,9 @@
       <c r="AS8" t="n">
         <v>5.7</v>
       </c>
+      <c r="AT8" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5935,6 +6427,9 @@
       <c r="AS9" t="n">
         <v>6.9</v>
       </c>
+      <c r="AT9" t="n">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5986,6 +6481,9 @@
       <c r="AS10" t="n">
         <v>3.64</v>
       </c>
+      <c r="AT10" t="n">
+        <v>3.64</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6037,6 +6535,9 @@
       <c r="AS11" t="n">
         <v>4.21</v>
       </c>
+      <c r="AT11" t="n">
+        <v>4.22</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6088,6 +6589,9 @@
       <c r="AS12" t="n">
         <v>4.27</v>
       </c>
+      <c r="AT12" t="n">
+        <v>4.27</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6139,6 +6643,9 @@
       <c r="AS13" t="n">
         <v>4.41</v>
       </c>
+      <c r="AT13" t="n">
+        <v>4.41</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6190,6 +6697,9 @@
       <c r="AS14" t="n">
         <v>4.57</v>
       </c>
+      <c r="AT14" t="n">
+        <v>4.57</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6241,6 +6751,9 @@
       <c r="AS15" t="n">
         <v>283.71</v>
       </c>
+      <c r="AT15" t="n">
+        <v>4900.21</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6289,6 +6802,9 @@
       <c r="AS16" t="n">
         <v>4.5</v>
       </c>
+      <c r="AT16" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6339,6 +6855,2244 @@
       </c>
       <c r="AS17" t="n">
         <v>144342.34</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>149242.55</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Lãi suất tiền gửi ECB (Eurozone)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Lãi suất SONIA (Anh, bám sát Bank Rate BOE)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Lãi suất liên ngân hàng qua đêm Nhật Bản</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="DI20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="DK20" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP Mỹ kỳ hạn 10 năm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP Đức kỳ hạn 10 năm (đại diện Eurozone)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CZ22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DA22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DC22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DF22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="DI22" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="DJ22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DK22" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP Nhật kỳ hạn 10 năm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CZ23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DA23" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DJ23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DK23" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP Anh kỳ hạn 10 năm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="CZ24" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="DA24" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="DB24" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="DC24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="DD24" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="DE24" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="DF24" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="DG24" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="DH24" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="DI24" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="DJ24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="DK24" t="n">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tỷ lệ thất nghiệp Mỹ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="CZ25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="DA25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="DB25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="DC25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="DD25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="DE25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="DF25" t="n">
+        <v>4</v>
+      </c>
+      <c r="DG25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="DH25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="DI25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="DJ25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="DK25" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Việc làm phi nông nghiệp Mỹ (thay đổi trong tháng)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>nghìn người</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>64</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-70</v>
+      </c>
+      <c r="E26" t="n">
+        <v>76</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-140</v>
+      </c>
+      <c r="G26" t="n">
+        <v>41</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I26" t="n">
+        <v>160</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="K26" t="n">
+        <v>214</v>
+      </c>
+      <c r="L26" t="n">
+        <v>148</v>
+      </c>
+      <c r="M26" t="n">
+        <v>129</v>
+      </c>
+      <c r="N26" t="n">
+        <v>57</v>
+      </c>
+      <c r="CZ26" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA26" t="n">
+        <v>9</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>155</v>
+      </c>
+      <c r="DC26" t="n">
+        <v>33</v>
+      </c>
+      <c r="DD26" t="n">
+        <v>134</v>
+      </c>
+      <c r="DE26" t="n">
+        <v>237</v>
+      </c>
+      <c r="DF26" t="n">
+        <v>-48</v>
+      </c>
+      <c r="DG26" t="n">
+        <v>42</v>
+      </c>
+      <c r="DH26" t="n">
+        <v>67</v>
+      </c>
+      <c r="DI26" t="n">
+        <v>108</v>
+      </c>
+      <c r="DJ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="DK26" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CPI Mỹ (YoY)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L27" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="CZ27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DA27" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DB27" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DC27" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DD27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DE27" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DF27" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="DG27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DH27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DI27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DJ27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DK27" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CPI lõi Mỹ (YoY)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CZ28" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="DA28" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="DB28" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DC28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="DD28" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="DE28" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="DF28" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DG28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DH28" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DI28" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DJ28" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DK28" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PCE Mỹ (YoY)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="CZ29" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DA29" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DC29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DE29" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="DF29" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DG29" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DH29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DI29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DJ29" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DK29" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PCE lõi Mỹ (YoY)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CZ30" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="DE30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="DF30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DI30" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DJ30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DK30" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Tăng trưởng GDP Mỹ (QoQ, theo năm)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CB31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CE31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CH31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CK31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CN31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="CQ31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="CT31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CW31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="CZ31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="DC31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DF31" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="DI31" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chỉ số sản xuất công nghiệp Mỹ (YoY)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CZ32" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="DA32" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="DB32" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="DC32" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="DD32" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="DE32" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="DF32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DG32" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DH32" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DI32" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DJ32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DK32" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP Mỹ kỳ hạn 3 tháng</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP Mỹ kỳ hạn 1 năm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP Mỹ kỳ hạn 2 năm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP Mỹ kỳ hạn 5 năm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Lợi suất TPCP Mỹ kỳ hạn 30 năm</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Tỷ lệ thất nghiệp Eurozone</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BK38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="CB38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="CC38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="CD38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="CE38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CF38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="CG38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="CH38" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Tăng trưởng GDP Eurozone (QoQ)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AU39" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CB39" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CE39" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="CH39" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chỉ số sản xuất công nghiệp Eurozone (YoY)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BT40" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="CB40" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="CC40" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="CD40" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="CE40" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="CF40" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CG40" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="CH40" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CI40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CJ40" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="CK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL40" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="CM40" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="CN40" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="CO40" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="CP40" t="n">
+        <v>-6.34</v>
+      </c>
+      <c r="CQ40" t="n">
+        <v>-5.69</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CPI Trung Quốc (YoY)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CL41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN41" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="CO41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ41" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="CR41" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CS41" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="CT41" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="CU41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CV41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CW41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CX41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CY41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CZ41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DA41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DB41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DC41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DD41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DE41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DF41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG41" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="DH41" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="DI41" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Lãi suất NHTW Trung Quốc (PBOC, proxy)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CN42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CO42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CP42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CQ42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CR42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CS42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CT42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CU42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CV42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CW42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CX42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CY42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CZ42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DA42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DB42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DC42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DD42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DE42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DF42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DG42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DH42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DI42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DJ42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DK42" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Spread lợi suất TPCP Mỹ 10 năm - 2 năm</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>điểm %</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Spread lợi suất TPCP Mỹ 10 năm - 3 tháng</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>điểm %</t>
+        </is>
+      </c>
+      <c r="W44" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -6527,7 +9281,7 @@
         <v>7.63</v>
       </c>
       <c r="E9" t="n">
-        <v>7.31</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="10">
@@ -6605,7 +9359,7 @@
         <v>7.8</v>
       </c>
       <c r="E14" t="n">
-        <v>7.3</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="15">
@@ -6659,7 +9413,7 @@
         <v>268</v>
       </c>
       <c r="E17" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5278,7 +5278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DR44"/>
+  <dimension ref="A1:FC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5403,6 +5403,43 @@
     <col width="12" customWidth="1" min="120" max="120"/>
     <col width="12" customWidth="1" min="121" max="121"/>
     <col width="12" customWidth="1" min="122" max="122"/>
+    <col width="12" customWidth="1" min="123" max="123"/>
+    <col width="12" customWidth="1" min="124" max="124"/>
+    <col width="12" customWidth="1" min="125" max="125"/>
+    <col width="12" customWidth="1" min="126" max="126"/>
+    <col width="12" customWidth="1" min="127" max="127"/>
+    <col width="12" customWidth="1" min="128" max="128"/>
+    <col width="12" customWidth="1" min="129" max="129"/>
+    <col width="12" customWidth="1" min="130" max="130"/>
+    <col width="12" customWidth="1" min="131" max="131"/>
+    <col width="12" customWidth="1" min="132" max="132"/>
+    <col width="12" customWidth="1" min="133" max="133"/>
+    <col width="12" customWidth="1" min="134" max="134"/>
+    <col width="12" customWidth="1" min="135" max="135"/>
+    <col width="12" customWidth="1" min="136" max="136"/>
+    <col width="12" customWidth="1" min="137" max="137"/>
+    <col width="12" customWidth="1" min="138" max="138"/>
+    <col width="12" customWidth="1" min="139" max="139"/>
+    <col width="12" customWidth="1" min="140" max="140"/>
+    <col width="12" customWidth="1" min="141" max="141"/>
+    <col width="12" customWidth="1" min="142" max="142"/>
+    <col width="12" customWidth="1" min="143" max="143"/>
+    <col width="12" customWidth="1" min="144" max="144"/>
+    <col width="12" customWidth="1" min="145" max="145"/>
+    <col width="12" customWidth="1" min="146" max="146"/>
+    <col width="12" customWidth="1" min="147" max="147"/>
+    <col width="12" customWidth="1" min="148" max="148"/>
+    <col width="12" customWidth="1" min="149" max="149"/>
+    <col width="12" customWidth="1" min="150" max="150"/>
+    <col width="12" customWidth="1" min="151" max="151"/>
+    <col width="12" customWidth="1" min="152" max="152"/>
+    <col width="12" customWidth="1" min="153" max="153"/>
+    <col width="12" customWidth="1" min="154" max="154"/>
+    <col width="12" customWidth="1" min="155" max="155"/>
+    <col width="12" customWidth="1" min="156" max="156"/>
+    <col width="12" customWidth="1" min="157" max="157"/>
+    <col width="12" customWidth="1" min="158" max="158"/>
+    <col width="12" customWidth="1" min="159" max="159"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6014,6 +6051,191 @@
       <c r="DR1" t="inlineStr">
         <is>
           <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="FC1" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ52"/>
+  <dimension ref="A1:DZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4706,6 +4706,582 @@
         <v>45.82</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Tăng trưởng dư nợ tín dụng toàn nền kinh tế YoY (theo tháng)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="G53" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="H53" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="I53" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="J53" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="K53" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="L53" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="M53" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="N53" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="CK53" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="CY53" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="CZ53" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="DA53" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="DB53" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="DC53" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="DJ53" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="DK53" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="DL53" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="DM53" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="DN53" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="DO53" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="DP53" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="DQ53" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="DR53" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="DS53" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="DT53" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="DU53" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="DV53" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="DW53" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="DX53" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="DY53" t="n">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Tỷ lệ Tín dụng / GDP danh nghĩa</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>133.59</v>
+      </c>
+      <c r="G54" t="n">
+        <v>140.16</v>
+      </c>
+      <c r="H54" t="n">
+        <v>142.03</v>
+      </c>
+      <c r="I54" t="n">
+        <v>146.45</v>
+      </c>
+      <c r="J54" t="n">
+        <v>146.45</v>
+      </c>
+      <c r="K54" t="n">
+        <v>149.34</v>
+      </c>
+      <c r="L54" t="n">
+        <v>149.34</v>
+      </c>
+      <c r="M54" t="n">
+        <v>151.37</v>
+      </c>
+      <c r="N54" t="n">
+        <v>153.37</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>94.94</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>95.92</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>100.42</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>102.88</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>97.73999999999999</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>98.97</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>100.57</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>102.36</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>106.33</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>101.98</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>103.21</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>103.91</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>106</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>106.79</v>
+      </c>
+      <c r="BU54" t="n">
+        <v>108.08</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>114.27</v>
+      </c>
+      <c r="BY54" t="n">
+        <v>109.13</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>109.02</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="CB54" t="n">
+        <v>112.82</v>
+      </c>
+      <c r="CC54" t="n">
+        <v>113.67</v>
+      </c>
+      <c r="CD54" t="n">
+        <v>115.29</v>
+      </c>
+      <c r="CE54" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="CF54" t="n">
+        <v>116.38</v>
+      </c>
+      <c r="CG54" t="n">
+        <v>116.84</v>
+      </c>
+      <c r="CH54" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="CI54" t="n">
+        <v>120.01</v>
+      </c>
+      <c r="CJ54" t="n">
+        <v>123.05</v>
+      </c>
+      <c r="CK54" t="n">
+        <v>111.43</v>
+      </c>
+      <c r="CL54" t="n">
+        <v>111.43</v>
+      </c>
+      <c r="CM54" t="n">
+        <v>115.03</v>
+      </c>
+      <c r="CN54" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="CO54" t="n">
+        <v>117.33</v>
+      </c>
+      <c r="CP54" t="n">
+        <v>118.78</v>
+      </c>
+      <c r="CQ54" t="n">
+        <v>118.91</v>
+      </c>
+      <c r="CR54" t="n">
+        <v>119.37</v>
+      </c>
+      <c r="CS54" t="n">
+        <v>120.54</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>121.16</v>
+      </c>
+      <c r="CU54" t="n">
+        <v>121.58</v>
+      </c>
+      <c r="CV54" t="n">
+        <v>123.94</v>
+      </c>
+      <c r="CW54" t="n">
+        <v>115.68</v>
+      </c>
+      <c r="CX54" t="n">
+        <v>116.54</v>
+      </c>
+      <c r="CY54" t="n">
+        <v>118.54</v>
+      </c>
+      <c r="CZ54" t="n">
+        <v>119.05</v>
+      </c>
+      <c r="DA54" t="n">
+        <v>119.33</v>
+      </c>
+      <c r="DB54" t="n">
+        <v>121.02</v>
+      </c>
+      <c r="DC54" t="n">
+        <v>120.81</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>121.99</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>124.12</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>126.17</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>131.49</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>117.08</v>
+      </c>
+      <c r="DJ54" t="n">
+        <v>117</v>
+      </c>
+      <c r="DK54" t="n">
+        <v>119.56</v>
+      </c>
+      <c r="DL54" t="n">
+        <v>120.26</v>
+      </c>
+      <c r="DM54" t="n">
+        <v>121.93</v>
+      </c>
+      <c r="DN54" t="n">
+        <v>125.07</v>
+      </c>
+      <c r="DO54" t="n">
+        <v>124.87</v>
+      </c>
+      <c r="DP54" t="n">
+        <v>126.51</v>
+      </c>
+      <c r="DQ54" t="n">
+        <v>128.63</v>
+      </c>
+      <c r="DR54" t="n">
+        <v>129.84</v>
+      </c>
+      <c r="DS54" t="n">
+        <v>131.85</v>
+      </c>
+      <c r="DT54" t="n">
+        <v>135.67</v>
+      </c>
+      <c r="DU54" t="n">
+        <v>122.22</v>
+      </c>
+      <c r="DV54" t="n">
+        <v>122.48</v>
+      </c>
+      <c r="DW54" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="DX54" t="n">
+        <v>128.01</v>
+      </c>
+      <c r="DY54" t="n">
+        <v>129.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4717,7 +5293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4968,6 +5544,48 @@
       </c>
       <c r="M6" t="n">
         <v>-3.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GDP danh nghĩa Việt Nam (theo năm)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>tỷ VND</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6293904.55</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7009042.13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7707200.29</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8044385.73</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8487475.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9621371.82</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10319058.87</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11510328.92</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12847571.22</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5639401</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2150,7 +2150,7 @@
         <v>26183.58</v>
       </c>
       <c r="DZ24" t="n">
-        <v>26167.86</v>
+        <v>26179.98</v>
       </c>
     </row>
     <row r="25">
@@ -5896,7 +5896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FC44"/>
+  <dimension ref="A1:FC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7054,6 +7054,9 @@
       <c r="AT5" t="n">
         <v>678.77</v>
       </c>
+      <c r="DR5" t="n">
+        <v>-312.31</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9933,6 +9936,90 @@
       </c>
       <c r="AT44" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CPI (HICP) Eurozone (YoY)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CZ45" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DA45" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DB45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DC45" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="DD45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DE45" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DF45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DH45" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DI45" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DJ45" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DK45" t="n">
+        <v>1.96</v>
       </c>
     </row>
   </sheetData>
@@ -9946,7 +10033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -9954,6 +10041,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9982,6 +10070,11 @@
           <t>2026-W31</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2026-W32</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10000,6 +10093,9 @@
       <c r="E2" t="n">
         <v>5.9</v>
       </c>
+      <c r="F2" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10036,6 +10132,9 @@
       <c r="E4" t="n">
         <v>6.2</v>
       </c>
+      <c r="F4" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10054,6 +10153,9 @@
       <c r="E5" t="n">
         <v>7.8</v>
       </c>
+      <c r="F5" t="n">
+        <v>7.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10072,6 +10174,9 @@
       <c r="E6" t="n">
         <v>6.17</v>
       </c>
+      <c r="F6" t="n">
+        <v>6.17</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10105,6 +10210,9 @@
       <c r="E8" t="n">
         <v>4.5</v>
       </c>
+      <c r="F8" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10123,6 +10231,9 @@
       <c r="E9" t="n">
         <v>7.34</v>
       </c>
+      <c r="F9" t="n">
+        <v>7.34</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10201,6 +10312,9 @@
       <c r="E14" t="n">
         <v>7.22</v>
       </c>
+      <c r="F14" t="n">
+        <v>7.22</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10219,6 +10333,9 @@
       <c r="E15" t="n">
         <v>9.26</v>
       </c>
+      <c r="F15" t="n">
+        <v>9.26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10254,6 +10371,9 @@
       </c>
       <c r="E17" t="n">
         <v>275</v>
+      </c>
+      <c r="F17" t="n">
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ54"/>
+  <dimension ref="A1:DZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5280,6 +5280,528 @@
       </c>
       <c r="DY54" t="n">
         <v>129.72</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Tổng huy động vốn toàn nền kinh tế</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>tỷ VND</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>15798887</v>
+      </c>
+      <c r="D55" t="n">
+        <v>15725450</v>
+      </c>
+      <c r="E55" t="n">
+        <v>15959293</v>
+      </c>
+      <c r="F55" t="n">
+        <v>16182630</v>
+      </c>
+      <c r="G55" t="n">
+        <v>15909571</v>
+      </c>
+      <c r="H55" t="n">
+        <v>16064674</v>
+      </c>
+      <c r="I55" t="n">
+        <v>16515887</v>
+      </c>
+      <c r="J55" t="n">
+        <v>16461627</v>
+      </c>
+      <c r="K55" t="n">
+        <v>16415112</v>
+      </c>
+      <c r="L55" t="n">
+        <v>16575580</v>
+      </c>
+      <c r="M55" t="n">
+        <v>16793661</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>7717980</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>7729722</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>7784927</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>7886700</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>7925247</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>8102385</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>8233716</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>8249223</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>8283755</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>8421336</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>8471733</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>8567206</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>8792649</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>8739395</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>8789582</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>8820899</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>8798935</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>8996217</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>9209997</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>9219381</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>9327466</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>9483045</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>9541346</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>9697185</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>10019859</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>9983024</v>
+      </c>
+      <c r="BZ55" t="n">
+        <v>9979753</v>
+      </c>
+      <c r="CA55" t="n">
+        <v>10169387</v>
+      </c>
+      <c r="CB55" t="n">
+        <v>10240129</v>
+      </c>
+      <c r="CC55" t="n">
+        <v>10312681</v>
+      </c>
+      <c r="CD55" t="n">
+        <v>10404260</v>
+      </c>
+      <c r="CE55" t="n">
+        <v>10379604</v>
+      </c>
+      <c r="CF55" t="n">
+        <v>10437766</v>
+      </c>
+      <c r="CG55" t="n">
+        <v>10549000</v>
+      </c>
+      <c r="CH55" t="n">
+        <v>10550758</v>
+      </c>
+      <c r="CI55" t="n">
+        <v>10680562</v>
+      </c>
+      <c r="CJ55" t="n">
+        <v>10945849</v>
+      </c>
+      <c r="CK55" t="n">
+        <v>10980777</v>
+      </c>
+      <c r="CL55" t="n">
+        <v>11096605</v>
+      </c>
+      <c r="CM55" t="n">
+        <v>11339315</v>
+      </c>
+      <c r="CN55" t="n">
+        <v>11327466</v>
+      </c>
+      <c r="CO55" t="n">
+        <v>11375944</v>
+      </c>
+      <c r="CP55" t="n">
+        <v>11468408</v>
+      </c>
+      <c r="CQ55" t="n">
+        <v>11394485</v>
+      </c>
+      <c r="CR55" t="n">
+        <v>11314657</v>
+      </c>
+      <c r="CS55" t="n">
+        <v>11420867</v>
+      </c>
+      <c r="CT55" t="n">
+        <v>11426633</v>
+      </c>
+      <c r="CU55" t="n">
+        <v>11553571</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>11819462</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>11748113</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>11795598</v>
+      </c>
+      <c r="CY55" t="n">
+        <v>11944562</v>
+      </c>
+      <c r="CZ55" t="n">
+        <v>11987757</v>
+      </c>
+      <c r="DA55" t="n">
+        <v>12096031</v>
+      </c>
+      <c r="DB55" t="n">
+        <v>12366810</v>
+      </c>
+      <c r="DC55" t="n">
+        <v>12299300</v>
+      </c>
+      <c r="DD55" t="n">
+        <v>12446524</v>
+      </c>
+      <c r="DE55" t="n">
+        <v>12679812</v>
+      </c>
+      <c r="DF55" t="n">
+        <v>12703788</v>
+      </c>
+      <c r="DG55" t="n">
+        <v>12855295</v>
+      </c>
+      <c r="DH55" t="n">
+        <v>13374474</v>
+      </c>
+      <c r="DI55" t="n">
+        <v>13174612</v>
+      </c>
+      <c r="DJ55" t="n">
+        <v>13160231</v>
+      </c>
+      <c r="DK55" t="n">
+        <v>13303208</v>
+      </c>
+      <c r="DL55" t="n">
+        <v>13292066</v>
+      </c>
+      <c r="DM55" t="n">
+        <v>13424014</v>
+      </c>
+      <c r="DN55" t="n">
+        <v>13724841</v>
+      </c>
+      <c r="DO55" t="n">
+        <v>13607169</v>
+      </c>
+      <c r="DP55" t="n">
+        <v>13763231</v>
+      </c>
+      <c r="DQ55" t="n">
+        <v>14034142</v>
+      </c>
+      <c r="DR55" t="n">
+        <v>14136939</v>
+      </c>
+      <c r="DS55" t="n">
+        <v>14270065</v>
+      </c>
+      <c r="DT55" t="n">
+        <v>14732270</v>
+      </c>
+      <c r="DU55" t="n">
+        <v>14621852</v>
+      </c>
+      <c r="DV55" t="n">
+        <v>14728372</v>
+      </c>
+      <c r="DW55" t="n">
+        <v>14990204</v>
+      </c>
+      <c r="DX55" t="n">
+        <v>15162767</v>
+      </c>
+      <c r="DY55" t="n">
+        <v>15344564</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Tăng trưởng huy động vốn toàn nền kinh tế YoY (theo tháng)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="D56" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="E56" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="F56" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="G56" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="H56" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="I56" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="J56" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="K56" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="L56" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="M56" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="BY56" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="BZ56" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="CA56" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="CB56" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="CC56" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="CD56" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="CE56" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="CF56" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="CG56" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="CH56" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="CI56" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="CJ56" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="CK56" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="CL56" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="CM56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CN56" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="CO56" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="CP56" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="CQ56" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="CR56" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="CS56" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="CT56" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="CU56" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="CW56" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="CX56" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="CY56" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="CZ56" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="DA56" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="DB56" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="DC56" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="DD56" t="n">
+        <v>10</v>
+      </c>
+      <c r="DE56" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="DF56" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="DG56" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="DH56" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="DI56" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="DJ56" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="DK56" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="DL56" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="DM56" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="DN56" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="DO56" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="DP56" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="DQ56" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="DR56" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="DS56" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="DT56" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="DU56" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="DV56" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="DW56" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="DX56" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="DY56" t="n">
+        <v>14.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ56"/>
+  <dimension ref="A1:DZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5802,6 +5802,1236 @@
       </c>
       <c r="DY56" t="n">
         <v>14.31</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Đóng góp vào lạm phát — nhóm Thực phẩm</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>điểm %</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BU57" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BV57" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BZ57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CA57" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CB57" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="CC57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="CD57" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="CE57" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="CF57" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CG57" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CH57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CI57" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="CJ57" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="CK57" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL57" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="CM57" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CN57" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CO57" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CP57" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CQ57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR57" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CS57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CT57" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CU57" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CV57" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CW57" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CX57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CY57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CZ57" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DA57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DB57" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DC57" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DD57" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DE57" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DF57" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DG57" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH57" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DI57" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DJ57" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DK57" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DL57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DM57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DN57" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DO57" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DP57" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DQ57" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DR57" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DS57" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DT57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DU57" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DV57" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DW57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DX57" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DY57" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Đóng góp vào lạm phát — nhóm Nhà, điện, nước</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>điểm %</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BU58" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BV58" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="BZ58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="CB58" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="CC58" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CD58" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CE58" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CF58" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CG58" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CH58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CI58" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CJ58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CK58" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="CL58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="CM58" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CN58" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CO58" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="CP58" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="CQ58" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="CR58" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="CS58" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="CT58" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="CU58" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CV58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CW58" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CX58" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CY58" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CZ58" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DA58" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DB58" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DC58" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DD58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DE58" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DF58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DG58" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DH58" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DI58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ58" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DK58" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DL58" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DM58" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN58" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DO58" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DP58" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DQ58" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DR58" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DS58" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DT58" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DU58" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DV58" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DW58" t="n">
+        <v>1</v>
+      </c>
+      <c r="DX58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DY58" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Đóng góp vào lạm phát — nhóm Y tế</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>điểm %</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BQ59" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BR59" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BS59" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BT59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BU59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BV59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BY59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BZ59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CA59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CB59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CC59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CD59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CE59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CF59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CG59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CH59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CI59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CJ59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CK59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CL59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CM59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CN59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CO59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CP59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CQ59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="CR59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CS59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CT59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CU59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CV59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CW59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CX59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CY59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CZ59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DA59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DB59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DC59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DD59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DE59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DF59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DG59" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DH59" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DI59" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="DJ59" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="DK59" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="DL59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DM59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DN59" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DO59" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DP59" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DQ59" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DR59" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DS59" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DT59" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DU59" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DV59" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DW59" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DX59" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DY59" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Đóng góp vào lạm phát — nhóm Vận tải</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>điểm %</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="BR60" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="BS60" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="BT60" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="BU60" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="BV60" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="BX60" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="BY60" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="BZ60" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="CA60" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CB60" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CC60" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CD60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CE60" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CF60" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CG60" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CH60" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CI60" t="n">
+        <v>2</v>
+      </c>
+      <c r="CJ60" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CK60" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CL60" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CM60" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CN60" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CO60" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CP60" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CQ60" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CR60" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="CS60" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CT60" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="CU60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="CV60" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="CW60" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX60" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="CY60" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="CZ60" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="DA60" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="DB60" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="DC60" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="DD60" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="DE60" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="DF60" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DG60" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DH60" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DI60" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DJ60" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DK60" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="DL60" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="DM60" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="DN60" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DO60" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DP60" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="DQ60" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="DR60" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="DS60" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="DT60" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="DU60" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="DV60" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="DW60" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="DX60" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="DY60" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Đóng góp vào lạm phát — nhóm Khác</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>điểm %</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BQ61" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BR61" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS61" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BT61" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BU61" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BV61" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BW61" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BX61" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY61" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BZ61" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="CA61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CB61" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CC61" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="CD61" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CE61" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CF61" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="CG61" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="CH61" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="CI61" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="CJ61" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="CK61" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="CL61" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="CM61" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="CN61" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="CO61" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="CP61" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="CQ61" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="CR61" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="CS61" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CT61" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CU61" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CV61" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CW61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CX61" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CY61" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CZ61" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DA61" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DB61" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DC61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="DD61" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="DE61" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DF61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DG61" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH61" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DI61" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DJ61" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="DK61" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DL61" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DM61" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN61" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="DO61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DP61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DQ61" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DR61" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DS61" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DT61" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DU61" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="DV61" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DW61" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DX61" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="DY61" t="n">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1768,6 +1768,9 @@
       <c r="O4" t="n">
         <v>14.8</v>
       </c>
+      <c r="P4" t="n">
+        <v>14.48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2150,7 +2153,7 @@
         <v>26183.58</v>
       </c>
       <c r="DZ24" t="n">
-        <v>26179.98</v>
+        <v>26160.64</v>
       </c>
     </row>
     <row r="25">
@@ -2167,6 +2170,9 @@
       <c r="O25" t="n">
         <v>28.09</v>
       </c>
+      <c r="P25" t="n">
+        <v>24.98</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2182,6 +2188,9 @@
       <c r="O26" t="n">
         <v>45.19</v>
       </c>
+      <c r="P26" t="n">
+        <v>41.42</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2197,6 +2206,9 @@
       <c r="O27" t="n">
         <v>11.7</v>
       </c>
+      <c r="P27" t="n">
+        <v>25.9</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4106,7 +4118,7 @@
         <v>10.72887492722224</v>
       </c>
       <c r="DZ39" t="n">
-        <v>10.73968416136957</v>
+        <v>10.99485360590693</v>
       </c>
     </row>
     <row r="40">
@@ -4124,7 +4136,7 @@
         <v>1.666190810249435</v>
       </c>
       <c r="DZ40" t="n">
-        <v>1.667869480820607</v>
+        <v>1.707497213125124</v>
       </c>
     </row>
     <row r="41">
@@ -4142,7 +4154,7 @@
         <v>12.38</v>
       </c>
       <c r="DZ41" t="n">
-        <v>11.77</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="42">
@@ -4160,7 +4172,7 @@
         <v>1.98</v>
       </c>
       <c r="DZ42" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="43">
@@ -7648,7 +7660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FC45"/>
+  <dimension ref="A1:FF45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7810,6 +7822,9 @@
     <col width="12" customWidth="1" min="157" max="157"/>
     <col width="12" customWidth="1" min="158" max="158"/>
     <col width="12" customWidth="1" min="159" max="159"/>
+    <col width="12" customWidth="1" min="160" max="160"/>
+    <col width="12" customWidth="1" min="161" max="161"/>
+    <col width="12" customWidth="1" min="162" max="162"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8608,6 +8623,21 @@
           <t>2026-06-16</t>
         </is>
       </c>
+      <c r="FD1" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="FE1" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="FF1" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8656,6 +8686,9 @@
       <c r="N2" t="n">
         <v>3.63</v>
       </c>
+      <c r="Y2" t="n">
+        <v>3.63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8767,6 +8800,9 @@
       <c r="AN4" t="n">
         <v>120.71</v>
       </c>
+      <c r="DR4" t="n">
+        <v>119.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8809,6 +8845,9 @@
       <c r="DR5" t="n">
         <v>-312.31</v>
       </c>
+      <c r="FF5" t="n">
+        <v>1055.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8863,6 +8902,9 @@
       <c r="AT6" t="n">
         <v>0.7</v>
       </c>
+      <c r="FF6" t="n">
+        <v>6.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8917,6 +8959,9 @@
       <c r="AT7" t="n">
         <v>4.5</v>
       </c>
+      <c r="FF7" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8971,6 +9016,9 @@
       <c r="AT8" t="n">
         <v>5.5</v>
       </c>
+      <c r="FF8" t="n">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9025,6 +9073,9 @@
       <c r="AT9" t="n">
         <v>6.9</v>
       </c>
+      <c r="FF9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9079,6 +9130,9 @@
       <c r="AT10" t="n">
         <v>3.64</v>
       </c>
+      <c r="FF10" t="n">
+        <v>3.68</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9133,6 +9187,9 @@
       <c r="AT11" t="n">
         <v>4.22</v>
       </c>
+      <c r="FF11" t="n">
+        <v>4.22</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9187,6 +9244,9 @@
       <c r="AT12" t="n">
         <v>4.27</v>
       </c>
+      <c r="FF12" t="n">
+        <v>4.27</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9241,6 +9301,9 @@
       <c r="AT13" t="n">
         <v>4.41</v>
       </c>
+      <c r="FF13" t="n">
+        <v>4.41</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9295,6 +9358,9 @@
       <c r="AT14" t="n">
         <v>4.57</v>
       </c>
+      <c r="FF14" t="n">
+        <v>4.57</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9349,6 +9415,9 @@
       <c r="AT15" t="n">
         <v>4900.21</v>
       </c>
+      <c r="FF15" t="n">
+        <v>15067.19</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9400,6 +9469,9 @@
       <c r="AT16" t="n">
         <v>4.5</v>
       </c>
+      <c r="FF16" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9454,6 +9526,9 @@
       <c r="AT17" t="n">
         <v>149242.55</v>
       </c>
+      <c r="FF17" t="n">
+        <v>187597.55</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9538,6 +9613,9 @@
       <c r="DR18" t="n">
         <v>2.25</v>
       </c>
+      <c r="FF18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9622,6 +9700,9 @@
       <c r="AS19" t="n">
         <v>3.73</v>
       </c>
+      <c r="DR19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9787,6 +9868,9 @@
       <c r="AT21" t="n">
         <v>4.68</v>
       </c>
+      <c r="DR21" t="n">
+        <v>4.75</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10783,6 +10867,9 @@
       <c r="AT33" t="n">
         <v>3.82</v>
       </c>
+      <c r="DR33" t="n">
+        <v>3.83</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10864,6 +10951,9 @@
       <c r="AT34" t="n">
         <v>4.04</v>
       </c>
+      <c r="DR34" t="n">
+        <v>4.08</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10945,6 +11035,9 @@
       <c r="AT35" t="n">
         <v>4.23</v>
       </c>
+      <c r="DR35" t="n">
+        <v>4.28</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11026,6 +11119,9 @@
       <c r="AT36" t="n">
         <v>4.38</v>
       </c>
+      <c r="DR36" t="n">
+        <v>4.45</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11107,6 +11203,9 @@
       <c r="AT37" t="n">
         <v>5.21</v>
       </c>
+      <c r="DR37" t="n">
+        <v>5.27</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -11608,6 +11707,9 @@
       <c r="AT43" t="n">
         <v>0.45</v>
       </c>
+      <c r="DR43" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -11688,6 +11790,9 @@
       </c>
       <c r="AT44" t="n">
         <v>0.86</v>
+      </c>
+      <c r="DR44" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="45">
@@ -11906,7 +12011,7 @@
         <v>7.8</v>
       </c>
       <c r="F5" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -11927,7 +12032,7 @@
         <v>6.17</v>
       </c>
       <c r="F6" t="n">
-        <v>6.17</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="7">
@@ -11984,7 +12089,7 @@
         <v>7.34</v>
       </c>
       <c r="F9" t="n">
-        <v>7.34</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="10">
@@ -12065,7 +12170,7 @@
         <v>7.22</v>
       </c>
       <c r="F14" t="n">
-        <v>7.22</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="15">
@@ -12125,7 +12230,7 @@
         <v>275</v>
       </c>
       <c r="F17" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -2153,7 +2153,7 @@
         <v>26183.58</v>
       </c>
       <c r="DZ24" t="n">
-        <v>26160.64</v>
+        <v>26156.77</v>
       </c>
     </row>
     <row r="25">
@@ -4118,7 +4118,7 @@
         <v>10.72887492722224</v>
       </c>
       <c r="DZ39" t="n">
-        <v>10.99485360590693</v>
+        <v>10.98285630114752</v>
       </c>
     </row>
     <row r="40">
@@ -4136,7 +4136,7 @@
         <v>1.666190810249435</v>
       </c>
       <c r="DZ40" t="n">
-        <v>1.707497213125124</v>
+        <v>1.705634035571701</v>
       </c>
     </row>
     <row r="41">
@@ -4154,7 +4154,7 @@
         <v>12.38</v>
       </c>
       <c r="DZ41" t="n">
-        <v>11.93</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="42">
@@ -4172,7 +4172,7 @@
         <v>1.98</v>
       </c>
       <c r="DZ42" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="43">
@@ -7660,7 +7660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FF45"/>
+  <dimension ref="A1:FG45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7825,6 +7825,7 @@
     <col width="12" customWidth="1" min="160" max="160"/>
     <col width="12" customWidth="1" min="161" max="161"/>
     <col width="12" customWidth="1" min="162" max="162"/>
+    <col width="12" customWidth="1" min="163" max="163"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8638,6 +8639,11 @@
           <t>2026-08-03</t>
         </is>
       </c>
+      <c r="FG1" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8848,6 +8854,9 @@
       <c r="FF5" t="n">
         <v>1055.9</v>
       </c>
+      <c r="FG5" t="n">
+        <v>889.8099999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8905,6 +8914,9 @@
       <c r="FF6" t="n">
         <v>6.3</v>
       </c>
+      <c r="FG6" t="n">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8962,6 +8974,9 @@
       <c r="FF7" t="n">
         <v>6.5</v>
       </c>
+      <c r="FG7" t="n">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9019,6 +9034,9 @@
       <c r="FF8" t="n">
         <v>6.4</v>
       </c>
+      <c r="FG8" t="n">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9076,6 +9094,9 @@
       <c r="FF9" t="n">
         <v>7</v>
       </c>
+      <c r="FG9" t="n">
+        <v>7.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9133,6 +9154,9 @@
       <c r="FF10" t="n">
         <v>3.68</v>
       </c>
+      <c r="FG10" t="n">
+        <v>3.68</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9190,6 +9214,9 @@
       <c r="FF11" t="n">
         <v>4.22</v>
       </c>
+      <c r="FG11" t="n">
+        <v>4.22</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9247,6 +9274,9 @@
       <c r="FF12" t="n">
         <v>4.27</v>
       </c>
+      <c r="FG12" t="n">
+        <v>4.28</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9304,6 +9334,9 @@
       <c r="FF13" t="n">
         <v>4.41</v>
       </c>
+      <c r="FG13" t="n">
+        <v>4.41</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9361,6 +9394,9 @@
       <c r="FF14" t="n">
         <v>4.57</v>
       </c>
+      <c r="FG14" t="n">
+        <v>4.57</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9418,6 +9454,9 @@
       <c r="FF15" t="n">
         <v>15067.19</v>
       </c>
+      <c r="FG15" t="n">
+        <v>7116.9</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9472,6 +9511,9 @@
       <c r="FF16" t="n">
         <v>4.5</v>
       </c>
+      <c r="FG16" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9529,6 +9571,9 @@
       <c r="FF17" t="n">
         <v>187597.55</v>
       </c>
+      <c r="FG17" t="n">
+        <v>194714.45</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9616,6 +9661,9 @@
       <c r="FF18" t="n">
         <v>2.25</v>
       </c>
+      <c r="FG18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9703,6 +9751,9 @@
       <c r="DR19" t="n">
         <v>3.73</v>
       </c>
+      <c r="FF19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9871,6 +9922,9 @@
       <c r="DR21" t="n">
         <v>4.75</v>
       </c>
+      <c r="FF21" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10870,6 +10924,9 @@
       <c r="DR33" t="n">
         <v>3.83</v>
       </c>
+      <c r="FF33" t="n">
+        <v>3.91</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10954,6 +11011,9 @@
       <c r="DR34" t="n">
         <v>4.08</v>
       </c>
+      <c r="FF34" t="n">
+        <v>4.07</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11038,6 +11098,9 @@
       <c r="DR35" t="n">
         <v>4.28</v>
       </c>
+      <c r="FF35" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11122,6 +11185,9 @@
       <c r="DR36" t="n">
         <v>4.45</v>
       </c>
+      <c r="FF36" t="n">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11206,6 +11272,9 @@
       <c r="DR37" t="n">
         <v>5.27</v>
       </c>
+      <c r="FF37" t="n">
+        <v>5.23</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -11710,6 +11779,9 @@
       <c r="DR43" t="n">
         <v>0.47</v>
       </c>
+      <c r="FF43" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -11793,6 +11865,9 @@
       </c>
       <c r="DR44" t="n">
         <v>0.92</v>
+      </c>
+      <c r="FF44" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="45">
@@ -12089,7 +12164,7 @@
         <v>7.34</v>
       </c>
       <c r="F9" t="n">
-        <v>7.54</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="10">
@@ -12170,7 +12245,7 @@
         <v>7.22</v>
       </c>
       <c r="F14" t="n">
-        <v>7.56</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="15">
@@ -12230,7 +12305,7 @@
         <v>275</v>
       </c>
       <c r="F17" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -2053,6 +2053,9 @@
       <c r="N18" t="n">
         <v>5.96</v>
       </c>
+      <c r="O18" t="n">
+        <v>8.369999999999999</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2134,6 +2137,9 @@
       <c r="P23" t="n">
         <v>9</v>
       </c>
+      <c r="DZ23" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2153,7 +2159,7 @@
         <v>26183.58</v>
       </c>
       <c r="DZ24" t="n">
-        <v>26156.77</v>
+        <v>26148.37</v>
       </c>
     </row>
     <row r="25">
@@ -2171,7 +2177,7 @@
         <v>28.09</v>
       </c>
       <c r="P25" t="n">
-        <v>24.98</v>
+        <v>25.01</v>
       </c>
     </row>
     <row r="26">
@@ -4118,7 +4124,7 @@
         <v>10.72887492722224</v>
       </c>
       <c r="DZ39" t="n">
-        <v>10.98285630114752</v>
+        <v>11.08739824201321</v>
       </c>
     </row>
     <row r="40">
@@ -4136,7 +4142,7 @@
         <v>1.666190810249435</v>
       </c>
       <c r="DZ40" t="n">
-        <v>1.705634035571701</v>
+        <v>1.721869365216013</v>
       </c>
     </row>
     <row r="41">
@@ -4154,7 +4160,7 @@
         <v>12.38</v>
       </c>
       <c r="DZ41" t="n">
-        <v>12.03</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="42">
@@ -4172,7 +4178,7 @@
         <v>1.98</v>
       </c>
       <c r="DZ42" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="43">
@@ -7660,7 +7666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG45"/>
+  <dimension ref="A1:FI45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7826,6 +7832,8 @@
     <col width="12" customWidth="1" min="161" max="161"/>
     <col width="12" customWidth="1" min="162" max="162"/>
     <col width="12" customWidth="1" min="163" max="163"/>
+    <col width="12" customWidth="1" min="164" max="164"/>
+    <col width="12" customWidth="1" min="165" max="165"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8644,6 +8652,16 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="FH1" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="FI1" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8752,6 +8770,9 @@
       <c r="AQ3" t="n">
         <v>91.81999999999999</v>
       </c>
+      <c r="FF3" t="n">
+        <v>88.90000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8857,6 +8878,9 @@
       <c r="FG5" t="n">
         <v>889.8099999999999</v>
       </c>
+      <c r="FI5" t="n">
+        <v>-118.15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8917,6 +8941,9 @@
       <c r="FG6" t="n">
         <v>6.4</v>
       </c>
+      <c r="FI6" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8977,6 +9004,9 @@
       <c r="FG7" t="n">
         <v>6.4</v>
       </c>
+      <c r="FI7" t="n">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9037,6 +9067,9 @@
       <c r="FG8" t="n">
         <v>6.4</v>
       </c>
+      <c r="FI8" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9097,6 +9130,9 @@
       <c r="FG9" t="n">
         <v>7.3</v>
       </c>
+      <c r="FI9" t="n">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9157,6 +9193,9 @@
       <c r="FG10" t="n">
         <v>3.68</v>
       </c>
+      <c r="FI10" t="n">
+        <v>3.69</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9217,6 +9256,9 @@
       <c r="FG11" t="n">
         <v>4.22</v>
       </c>
+      <c r="FI11" t="n">
+        <v>4.22</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9277,6 +9319,9 @@
       <c r="FG12" t="n">
         <v>4.28</v>
       </c>
+      <c r="FI12" t="n">
+        <v>4.29</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9337,6 +9382,9 @@
       <c r="FG13" t="n">
         <v>4.41</v>
       </c>
+      <c r="FI13" t="n">
+        <v>4.41</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9397,6 +9445,9 @@
       <c r="FG14" t="n">
         <v>4.57</v>
       </c>
+      <c r="FI14" t="n">
+        <v>4.57</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9457,6 +9508,9 @@
       <c r="FG15" t="n">
         <v>7116.9</v>
       </c>
+      <c r="FI15" t="n">
+        <v>-3211.44</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9514,6 +9568,9 @@
       <c r="FG16" t="n">
         <v>4.5</v>
       </c>
+      <c r="FI16" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9574,6 +9631,9 @@
       <c r="FG17" t="n">
         <v>194714.45</v>
       </c>
+      <c r="FI17" t="n">
+        <v>190527.26</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9664,6 +9724,9 @@
       <c r="FG18" t="n">
         <v>2.25</v>
       </c>
+      <c r="FI18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9754,6 +9817,9 @@
       <c r="FF19" t="n">
         <v>3.73</v>
       </c>
+      <c r="FG19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9925,6 +9991,9 @@
       <c r="FF21" t="n">
         <v>4.7</v>
       </c>
+      <c r="FH21" t="n">
+        <v>4.63</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10927,6 +10996,9 @@
       <c r="FF33" t="n">
         <v>3.91</v>
       </c>
+      <c r="FH33" t="n">
+        <v>3.89</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11014,6 +11086,9 @@
       <c r="FF34" t="n">
         <v>4.07</v>
       </c>
+      <c r="FH34" t="n">
+        <v>4.03</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11101,6 +11176,9 @@
       <c r="FF35" t="n">
         <v>4.25</v>
       </c>
+      <c r="FH35" t="n">
+        <v>4.18</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11188,6 +11266,9 @@
       <c r="FF36" t="n">
         <v>4.4</v>
       </c>
+      <c r="FH36" t="n">
+        <v>4.33</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11275,6 +11356,9 @@
       <c r="FF37" t="n">
         <v>5.23</v>
       </c>
+      <c r="FH37" t="n">
+        <v>5.17</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -11782,6 +11866,9 @@
       <c r="FF43" t="n">
         <v>0.45</v>
       </c>
+      <c r="FH43" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -11868,6 +11955,9 @@
       </c>
       <c r="FF44" t="n">
         <v>0.79</v>
+      </c>
+      <c r="FH44" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="45">
@@ -12164,7 +12254,7 @@
         <v>7.34</v>
       </c>
       <c r="F9" t="n">
-        <v>7.22</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="10">
@@ -12245,7 +12335,7 @@
         <v>7.22</v>
       </c>
       <c r="F14" t="n">
-        <v>8.42</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="15">
@@ -12305,7 +12395,7 @@
         <v>275</v>
       </c>
       <c r="F17" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -7666,7 +7666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FI45"/>
+  <dimension ref="A1:FJ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7834,6 +7834,7 @@
     <col width="12" customWidth="1" min="163" max="163"/>
     <col width="12" customWidth="1" min="164" max="164"/>
     <col width="12" customWidth="1" min="165" max="165"/>
+    <col width="12" customWidth="1" min="166" max="166"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8662,6 +8663,11 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="FJ1" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9727,6 +9733,9 @@
       <c r="FI18" t="n">
         <v>2.25</v>
       </c>
+      <c r="FJ18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9820,6 +9829,9 @@
       <c r="FG19" t="n">
         <v>3.73</v>
       </c>
+      <c r="FH19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10291,6 +10303,9 @@
       <c r="N25" t="n">
         <v>4.2</v>
       </c>
+      <c r="Y25" t="n">
+        <v>4.1</v>
+      </c>
       <c r="CZ25" t="n">
         <v>4.2</v>
       </c>
@@ -10374,6 +10389,9 @@
       </c>
       <c r="N26" t="n">
         <v>57</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-23</v>
       </c>
       <c r="CZ26" t="n">
         <v>53</v>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ61"/>
+  <dimension ref="A1:DZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1723,6 +1723,9 @@
       <c r="O2" t="n">
         <v>12.7</v>
       </c>
+      <c r="P2" t="n">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4219,6 +4222,9 @@
       <c r="O43" t="n">
         <v>35.5</v>
       </c>
+      <c r="P43" t="n">
+        <v>39</v>
+      </c>
       <c r="DI43" t="n">
         <v>4.4</v>
       </c>
@@ -4558,6 +4564,9 @@
       <c r="O48" t="n">
         <v>356.9351</v>
       </c>
+      <c r="P48" t="n">
+        <v>445.5</v>
+      </c>
       <c r="DI48" t="n">
         <v>31.1</v>
       </c>
@@ -4639,6 +4648,9 @@
       <c r="O50" t="n">
         <v>102.8351</v>
       </c>
+      <c r="P50" t="n">
+        <v>88.56489999999999</v>
+      </c>
       <c r="DI50" t="n">
         <v>31.1</v>
       </c>
@@ -7050,6 +7062,1161 @@
       </c>
       <c r="DY61" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FDI giải ngân (lũy kế)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>tỷ USD</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="D62" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E62" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F62" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G62" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H62" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M62" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N62" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="O62" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="P62" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="DV62" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="DX62" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="DY62" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Tong cung tien M2</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ty VND</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>19584434</v>
+      </c>
+      <c r="D63" t="n">
+        <v>19482760</v>
+      </c>
+      <c r="E63" t="n">
+        <v>19685504</v>
+      </c>
+      <c r="F63" t="n">
+        <v>19980717</v>
+      </c>
+      <c r="G63" t="n">
+        <v>18728084</v>
+      </c>
+      <c r="H63" t="n">
+        <v>18938260</v>
+      </c>
+      <c r="I63" t="n">
+        <v>19444476</v>
+      </c>
+      <c r="J63" t="n">
+        <v>19578695</v>
+      </c>
+      <c r="K63" t="n">
+        <v>19641068</v>
+      </c>
+      <c r="L63" t="n">
+        <v>19635094</v>
+      </c>
+      <c r="M63" t="n">
+        <v>19818534</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>9211848</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>9488086</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>9376631</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>9478157</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>9546608</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>9706888</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>9866484</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>9860081</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>9949135</v>
+      </c>
+      <c r="BI63" t="n">
+        <v>10083735</v>
+      </c>
+      <c r="BJ63" t="n">
+        <v>10138630</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>10274960</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>10573725</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>10758024</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>10672880</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>10755572</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>10779851</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>10928485</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>11118423</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>11163361</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>11315994</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>11485845</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>11556445</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>11730140</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>12110606</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>12202217</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>12228211</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>12349750</v>
+      </c>
+      <c r="CB63" t="n">
+        <v>12465012</v>
+      </c>
+      <c r="CC63" t="n">
+        <v>12558573</v>
+      </c>
+      <c r="CD63" t="n">
+        <v>12647703</v>
+      </c>
+      <c r="CE63" t="n">
+        <v>12692256</v>
+      </c>
+      <c r="CF63" t="n">
+        <v>12757648</v>
+      </c>
+      <c r="CG63" t="n">
+        <v>12879090</v>
+      </c>
+      <c r="CH63" t="n">
+        <v>12907567</v>
+      </c>
+      <c r="CI63" t="n">
+        <v>13040842</v>
+      </c>
+      <c r="CJ63" t="n">
+        <v>13402097</v>
+      </c>
+      <c r="CK63" t="n">
+        <v>13748740</v>
+      </c>
+      <c r="CL63" t="n">
+        <v>13644750</v>
+      </c>
+      <c r="CM63" t="n">
+        <v>13864061</v>
+      </c>
+      <c r="CN63" t="n">
+        <v>13871751</v>
+      </c>
+      <c r="CO63" t="n">
+        <v>13848264</v>
+      </c>
+      <c r="CP63" t="n">
+        <v>13908338</v>
+      </c>
+      <c r="CQ63" t="n">
+        <v>13828044</v>
+      </c>
+      <c r="CR63" t="n">
+        <v>13761019</v>
+      </c>
+      <c r="CS63" t="n">
+        <v>13832397</v>
+      </c>
+      <c r="CT63" t="n">
+        <v>13815145</v>
+      </c>
+      <c r="CU63" t="n">
+        <v>13878503</v>
+      </c>
+      <c r="CV63" t="n">
+        <v>14226792</v>
+      </c>
+      <c r="CW63" t="n">
+        <v>14339502</v>
+      </c>
+      <c r="CX63" t="n">
+        <v>14272184</v>
+      </c>
+      <c r="CY63" t="n">
+        <v>14415021</v>
+      </c>
+      <c r="CZ63" t="n">
+        <v>14470593</v>
+      </c>
+      <c r="DA63" t="n">
+        <v>14517832</v>
+      </c>
+      <c r="DB63" t="n">
+        <v>14754221</v>
+      </c>
+      <c r="DC63" t="n">
+        <v>14640943</v>
+      </c>
+      <c r="DD63" t="n">
+        <v>14801154</v>
+      </c>
+      <c r="DE63" t="n">
+        <v>15026012</v>
+      </c>
+      <c r="DF63" t="n">
+        <v>15074263</v>
+      </c>
+      <c r="DG63" t="n">
+        <v>15354119</v>
+      </c>
+      <c r="DH63" t="n">
+        <v>15998956</v>
+      </c>
+      <c r="DI63" t="n">
+        <v>15999293</v>
+      </c>
+      <c r="DJ63" t="n">
+        <v>15914067</v>
+      </c>
+      <c r="DK63" t="n">
+        <v>16012915</v>
+      </c>
+      <c r="DL63" t="n">
+        <v>16019364</v>
+      </c>
+      <c r="DM63" t="n">
+        <v>16130057</v>
+      </c>
+      <c r="DN63" t="n">
+        <v>16513106</v>
+      </c>
+      <c r="DO63" t="n">
+        <v>16401397</v>
+      </c>
+      <c r="DP63" t="n">
+        <v>16658293</v>
+      </c>
+      <c r="DQ63" t="n">
+        <v>16949072</v>
+      </c>
+      <c r="DR63" t="n">
+        <v>17107320</v>
+      </c>
+      <c r="DS63" t="n">
+        <v>17301843</v>
+      </c>
+      <c r="DT63" t="n">
+        <v>17914566</v>
+      </c>
+      <c r="DU63" t="n">
+        <v>18176926</v>
+      </c>
+      <c r="DV63" t="n">
+        <v>18157191</v>
+      </c>
+      <c r="DW63" t="n">
+        <v>18450042</v>
+      </c>
+      <c r="DX63" t="n">
+        <v>18721571</v>
+      </c>
+      <c r="DY63" t="n">
+        <v>18973143</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Tăng trưởng dư nợ tín dụng toàn nền kinh tế so cuối năm trước (YTD, theo tháng)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="G64" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="H64" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="I64" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="BI64" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BJ64" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="BK64" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL64" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BQ64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="BU64" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="BV64" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="BY64" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BZ64" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="CA64" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="CB64" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="CC64" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="CD64" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="CE64" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="CF64" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="CG64" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="CH64" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="CI64" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="CJ64" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="CK64" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CL64" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CM64" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="CN64" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="CO64" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="CP64" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="CQ64" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="CR64" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="CS64" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="CT64" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="CU64" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV64" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="CW64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CX64" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CY64" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CZ64" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DA64" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="DB64" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="DC64" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="DD64" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="DE64" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="DF64" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="DG64" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="DH64" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="DI64" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="DJ64" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="DK64" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DL64" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DM64" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="DN64" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="DO64" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="DP64" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="DQ64" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="DR64" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="DS64" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="DT64" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="DU64" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="DV64" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DW64" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="DX64" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="DY64" t="n">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Tăng trưởng huy động vốn toàn nền kinh tế so cuối năm trước (YTD, theo tháng)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="D65" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="E65" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="F65" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="G65" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="H65" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="I65" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="BJ65" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="BK65" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL65" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BR65" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BT65" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="BU65" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="BV65" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="BY65" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="BZ65" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="CA65" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CB65" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CC65" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CD65" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CE65" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="CF65" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="CG65" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="CH65" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="CI65" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="CJ65" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="CK65" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CL65" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CM65" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="CN65" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="CO65" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="CP65" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="CQ65" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="CR65" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CS65" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="CT65" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="CU65" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="CV65" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="CW65" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="CX65" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="CY65" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CZ65" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DA65" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DB65" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="DC65" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="DD65" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="DE65" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="DF65" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="DG65" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="DH65" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="DI65" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="DJ65" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="DK65" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="DL65" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="DM65" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="DN65" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DO65" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DP65" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DQ65" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="DR65" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="DS65" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="DT65" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="DU65" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="DV65" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="DW65" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DX65" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DY65" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Tăng trưởng cung tiền M2 so cuối năm trước (YTD, theo tháng)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="D66" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E66" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="F66" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="H66" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="I66" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI66" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="BJ66" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="BU66" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="BV66" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="BY66" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BZ66" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CA66" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CB66" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC66" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="CD66" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="CE66" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="CF66" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="CG66" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="CH66" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="CI66" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="CJ66" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="CK66" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CL66" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CM66" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="CN66" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CO66" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CP66" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="CQ66" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CR66" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CS66" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CT66" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CU66" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CV66" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="CW66" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="CX66" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CY66" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CZ66" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DA66" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DB66" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="DC66" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DD66" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="DE66" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="DF66" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="DG66" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="DH66" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="DI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ66" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="DK66" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DL66" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DM66" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DN66" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="DO66" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="DP66" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="DQ66" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="DR66" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="DS66" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="DT66" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="DU66" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DV66" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DW66" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="DX66" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DY66" t="n">
+        <v>5.91</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ66"/>
+  <dimension ref="A1:DZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2162,7 +2162,7 @@
         <v>26183.58</v>
       </c>
       <c r="DZ24" t="n">
-        <v>26148.37</v>
+        <v>26186.83</v>
       </c>
     </row>
     <row r="25">
@@ -4163,7 +4163,7 @@
         <v>12.38</v>
       </c>
       <c r="DZ41" t="n">
-        <v>11.98</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -8217,6 +8217,30 @@
       </c>
       <c r="DY66" t="n">
         <v>5.91</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Tổng mức bán lẻ hàng hóa và doanh thu dịch vụ tiêu dùng</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>nghìn tỷ đồng</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>638.6</v>
+      </c>
+      <c r="M67" t="n">
+        <v>646.3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>647.1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>669.1</v>
       </c>
     </row>
   </sheetData>
@@ -10054,6 +10078,9 @@
       <c r="FI5" t="n">
         <v>-118.15</v>
       </c>
+      <c r="FJ5" t="n">
+        <v>-74.68000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13321,6 +13348,9 @@
       <c r="E3" t="n">
         <v>5.9</v>
       </c>
+      <c r="F3" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13580,7 +13610,7 @@
         <v>275</v>
       </c>
       <c r="F17" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -8857,7 +8857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FJ45"/>
+  <dimension ref="A1:OF47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -9026,6 +9026,236 @@
     <col width="12" customWidth="1" min="164" max="164"/>
     <col width="12" customWidth="1" min="165" max="165"/>
     <col width="12" customWidth="1" min="166" max="166"/>
+    <col width="12" customWidth="1" min="167" max="167"/>
+    <col width="12" customWidth="1" min="168" max="168"/>
+    <col width="12" customWidth="1" min="169" max="169"/>
+    <col width="12" customWidth="1" min="170" max="170"/>
+    <col width="12" customWidth="1" min="171" max="171"/>
+    <col width="12" customWidth="1" min="172" max="172"/>
+    <col width="12" customWidth="1" min="173" max="173"/>
+    <col width="12" customWidth="1" min="174" max="174"/>
+    <col width="12" customWidth="1" min="175" max="175"/>
+    <col width="12" customWidth="1" min="176" max="176"/>
+    <col width="12" customWidth="1" min="177" max="177"/>
+    <col width="12" customWidth="1" min="178" max="178"/>
+    <col width="12" customWidth="1" min="179" max="179"/>
+    <col width="12" customWidth="1" min="180" max="180"/>
+    <col width="12" customWidth="1" min="181" max="181"/>
+    <col width="12" customWidth="1" min="182" max="182"/>
+    <col width="12" customWidth="1" min="183" max="183"/>
+    <col width="12" customWidth="1" min="184" max="184"/>
+    <col width="12" customWidth="1" min="185" max="185"/>
+    <col width="12" customWidth="1" min="186" max="186"/>
+    <col width="12" customWidth="1" min="187" max="187"/>
+    <col width="12" customWidth="1" min="188" max="188"/>
+    <col width="12" customWidth="1" min="189" max="189"/>
+    <col width="12" customWidth="1" min="190" max="190"/>
+    <col width="12" customWidth="1" min="191" max="191"/>
+    <col width="12" customWidth="1" min="192" max="192"/>
+    <col width="12" customWidth="1" min="193" max="193"/>
+    <col width="12" customWidth="1" min="194" max="194"/>
+    <col width="12" customWidth="1" min="195" max="195"/>
+    <col width="12" customWidth="1" min="196" max="196"/>
+    <col width="12" customWidth="1" min="197" max="197"/>
+    <col width="12" customWidth="1" min="198" max="198"/>
+    <col width="12" customWidth="1" min="199" max="199"/>
+    <col width="12" customWidth="1" min="200" max="200"/>
+    <col width="12" customWidth="1" min="201" max="201"/>
+    <col width="12" customWidth="1" min="202" max="202"/>
+    <col width="12" customWidth="1" min="203" max="203"/>
+    <col width="12" customWidth="1" min="204" max="204"/>
+    <col width="12" customWidth="1" min="205" max="205"/>
+    <col width="12" customWidth="1" min="206" max="206"/>
+    <col width="12" customWidth="1" min="207" max="207"/>
+    <col width="12" customWidth="1" min="208" max="208"/>
+    <col width="12" customWidth="1" min="209" max="209"/>
+    <col width="12" customWidth="1" min="210" max="210"/>
+    <col width="12" customWidth="1" min="211" max="211"/>
+    <col width="12" customWidth="1" min="212" max="212"/>
+    <col width="12" customWidth="1" min="213" max="213"/>
+    <col width="12" customWidth="1" min="214" max="214"/>
+    <col width="12" customWidth="1" min="215" max="215"/>
+    <col width="12" customWidth="1" min="216" max="216"/>
+    <col width="12" customWidth="1" min="217" max="217"/>
+    <col width="12" customWidth="1" min="218" max="218"/>
+    <col width="12" customWidth="1" min="219" max="219"/>
+    <col width="12" customWidth="1" min="220" max="220"/>
+    <col width="12" customWidth="1" min="221" max="221"/>
+    <col width="12" customWidth="1" min="222" max="222"/>
+    <col width="12" customWidth="1" min="223" max="223"/>
+    <col width="12" customWidth="1" min="224" max="224"/>
+    <col width="12" customWidth="1" min="225" max="225"/>
+    <col width="12" customWidth="1" min="226" max="226"/>
+    <col width="12" customWidth="1" min="227" max="227"/>
+    <col width="12" customWidth="1" min="228" max="228"/>
+    <col width="12" customWidth="1" min="229" max="229"/>
+    <col width="12" customWidth="1" min="230" max="230"/>
+    <col width="12" customWidth="1" min="231" max="231"/>
+    <col width="12" customWidth="1" min="232" max="232"/>
+    <col width="12" customWidth="1" min="233" max="233"/>
+    <col width="12" customWidth="1" min="234" max="234"/>
+    <col width="12" customWidth="1" min="235" max="235"/>
+    <col width="12" customWidth="1" min="236" max="236"/>
+    <col width="12" customWidth="1" min="237" max="237"/>
+    <col width="12" customWidth="1" min="238" max="238"/>
+    <col width="12" customWidth="1" min="239" max="239"/>
+    <col width="12" customWidth="1" min="240" max="240"/>
+    <col width="12" customWidth="1" min="241" max="241"/>
+    <col width="12" customWidth="1" min="242" max="242"/>
+    <col width="12" customWidth="1" min="243" max="243"/>
+    <col width="12" customWidth="1" min="244" max="244"/>
+    <col width="12" customWidth="1" min="245" max="245"/>
+    <col width="12" customWidth="1" min="246" max="246"/>
+    <col width="12" customWidth="1" min="247" max="247"/>
+    <col width="12" customWidth="1" min="248" max="248"/>
+    <col width="12" customWidth="1" min="249" max="249"/>
+    <col width="12" customWidth="1" min="250" max="250"/>
+    <col width="12" customWidth="1" min="251" max="251"/>
+    <col width="12" customWidth="1" min="252" max="252"/>
+    <col width="12" customWidth="1" min="253" max="253"/>
+    <col width="12" customWidth="1" min="254" max="254"/>
+    <col width="12" customWidth="1" min="255" max="255"/>
+    <col width="12" customWidth="1" min="256" max="256"/>
+    <col width="12" customWidth="1" min="257" max="257"/>
+    <col width="12" customWidth="1" min="258" max="258"/>
+    <col width="12" customWidth="1" min="259" max="259"/>
+    <col width="12" customWidth="1" min="260" max="260"/>
+    <col width="12" customWidth="1" min="261" max="261"/>
+    <col width="12" customWidth="1" min="262" max="262"/>
+    <col width="12" customWidth="1" min="263" max="263"/>
+    <col width="12" customWidth="1" min="264" max="264"/>
+    <col width="12" customWidth="1" min="265" max="265"/>
+    <col width="12" customWidth="1" min="266" max="266"/>
+    <col width="12" customWidth="1" min="267" max="267"/>
+    <col width="12" customWidth="1" min="268" max="268"/>
+    <col width="12" customWidth="1" min="269" max="269"/>
+    <col width="12" customWidth="1" min="270" max="270"/>
+    <col width="12" customWidth="1" min="271" max="271"/>
+    <col width="12" customWidth="1" min="272" max="272"/>
+    <col width="12" customWidth="1" min="273" max="273"/>
+    <col width="12" customWidth="1" min="274" max="274"/>
+    <col width="12" customWidth="1" min="275" max="275"/>
+    <col width="12" customWidth="1" min="276" max="276"/>
+    <col width="12" customWidth="1" min="277" max="277"/>
+    <col width="12" customWidth="1" min="278" max="278"/>
+    <col width="12" customWidth="1" min="279" max="279"/>
+    <col width="12" customWidth="1" min="280" max="280"/>
+    <col width="12" customWidth="1" min="281" max="281"/>
+    <col width="12" customWidth="1" min="282" max="282"/>
+    <col width="12" customWidth="1" min="283" max="283"/>
+    <col width="12" customWidth="1" min="284" max="284"/>
+    <col width="12" customWidth="1" min="285" max="285"/>
+    <col width="12" customWidth="1" min="286" max="286"/>
+    <col width="12" customWidth="1" min="287" max="287"/>
+    <col width="12" customWidth="1" min="288" max="288"/>
+    <col width="12" customWidth="1" min="289" max="289"/>
+    <col width="12" customWidth="1" min="290" max="290"/>
+    <col width="12" customWidth="1" min="291" max="291"/>
+    <col width="12" customWidth="1" min="292" max="292"/>
+    <col width="12" customWidth="1" min="293" max="293"/>
+    <col width="12" customWidth="1" min="294" max="294"/>
+    <col width="12" customWidth="1" min="295" max="295"/>
+    <col width="12" customWidth="1" min="296" max="296"/>
+    <col width="12" customWidth="1" min="297" max="297"/>
+    <col width="12" customWidth="1" min="298" max="298"/>
+    <col width="12" customWidth="1" min="299" max="299"/>
+    <col width="12" customWidth="1" min="300" max="300"/>
+    <col width="12" customWidth="1" min="301" max="301"/>
+    <col width="12" customWidth="1" min="302" max="302"/>
+    <col width="12" customWidth="1" min="303" max="303"/>
+    <col width="12" customWidth="1" min="304" max="304"/>
+    <col width="12" customWidth="1" min="305" max="305"/>
+    <col width="12" customWidth="1" min="306" max="306"/>
+    <col width="12" customWidth="1" min="307" max="307"/>
+    <col width="12" customWidth="1" min="308" max="308"/>
+    <col width="12" customWidth="1" min="309" max="309"/>
+    <col width="12" customWidth="1" min="310" max="310"/>
+    <col width="12" customWidth="1" min="311" max="311"/>
+    <col width="12" customWidth="1" min="312" max="312"/>
+    <col width="12" customWidth="1" min="313" max="313"/>
+    <col width="12" customWidth="1" min="314" max="314"/>
+    <col width="12" customWidth="1" min="315" max="315"/>
+    <col width="12" customWidth="1" min="316" max="316"/>
+    <col width="12" customWidth="1" min="317" max="317"/>
+    <col width="12" customWidth="1" min="318" max="318"/>
+    <col width="12" customWidth="1" min="319" max="319"/>
+    <col width="12" customWidth="1" min="320" max="320"/>
+    <col width="12" customWidth="1" min="321" max="321"/>
+    <col width="12" customWidth="1" min="322" max="322"/>
+    <col width="12" customWidth="1" min="323" max="323"/>
+    <col width="12" customWidth="1" min="324" max="324"/>
+    <col width="12" customWidth="1" min="325" max="325"/>
+    <col width="12" customWidth="1" min="326" max="326"/>
+    <col width="12" customWidth="1" min="327" max="327"/>
+    <col width="12" customWidth="1" min="328" max="328"/>
+    <col width="12" customWidth="1" min="329" max="329"/>
+    <col width="12" customWidth="1" min="330" max="330"/>
+    <col width="12" customWidth="1" min="331" max="331"/>
+    <col width="12" customWidth="1" min="332" max="332"/>
+    <col width="12" customWidth="1" min="333" max="333"/>
+    <col width="12" customWidth="1" min="334" max="334"/>
+    <col width="12" customWidth="1" min="335" max="335"/>
+    <col width="12" customWidth="1" min="336" max="336"/>
+    <col width="12" customWidth="1" min="337" max="337"/>
+    <col width="12" customWidth="1" min="338" max="338"/>
+    <col width="12" customWidth="1" min="339" max="339"/>
+    <col width="12" customWidth="1" min="340" max="340"/>
+    <col width="12" customWidth="1" min="341" max="341"/>
+    <col width="12" customWidth="1" min="342" max="342"/>
+    <col width="12" customWidth="1" min="343" max="343"/>
+    <col width="12" customWidth="1" min="344" max="344"/>
+    <col width="12" customWidth="1" min="345" max="345"/>
+    <col width="12" customWidth="1" min="346" max="346"/>
+    <col width="12" customWidth="1" min="347" max="347"/>
+    <col width="12" customWidth="1" min="348" max="348"/>
+    <col width="12" customWidth="1" min="349" max="349"/>
+    <col width="12" customWidth="1" min="350" max="350"/>
+    <col width="12" customWidth="1" min="351" max="351"/>
+    <col width="12" customWidth="1" min="352" max="352"/>
+    <col width="12" customWidth="1" min="353" max="353"/>
+    <col width="12" customWidth="1" min="354" max="354"/>
+    <col width="12" customWidth="1" min="355" max="355"/>
+    <col width="12" customWidth="1" min="356" max="356"/>
+    <col width="12" customWidth="1" min="357" max="357"/>
+    <col width="12" customWidth="1" min="358" max="358"/>
+    <col width="12" customWidth="1" min="359" max="359"/>
+    <col width="12" customWidth="1" min="360" max="360"/>
+    <col width="12" customWidth="1" min="361" max="361"/>
+    <col width="12" customWidth="1" min="362" max="362"/>
+    <col width="12" customWidth="1" min="363" max="363"/>
+    <col width="12" customWidth="1" min="364" max="364"/>
+    <col width="12" customWidth="1" min="365" max="365"/>
+    <col width="12" customWidth="1" min="366" max="366"/>
+    <col width="12" customWidth="1" min="367" max="367"/>
+    <col width="12" customWidth="1" min="368" max="368"/>
+    <col width="12" customWidth="1" min="369" max="369"/>
+    <col width="12" customWidth="1" min="370" max="370"/>
+    <col width="12" customWidth="1" min="371" max="371"/>
+    <col width="12" customWidth="1" min="372" max="372"/>
+    <col width="12" customWidth="1" min="373" max="373"/>
+    <col width="12" customWidth="1" min="374" max="374"/>
+    <col width="12" customWidth="1" min="375" max="375"/>
+    <col width="12" customWidth="1" min="376" max="376"/>
+    <col width="12" customWidth="1" min="377" max="377"/>
+    <col width="12" customWidth="1" min="378" max="378"/>
+    <col width="12" customWidth="1" min="379" max="379"/>
+    <col width="12" customWidth="1" min="380" max="380"/>
+    <col width="12" customWidth="1" min="381" max="381"/>
+    <col width="12" customWidth="1" min="382" max="382"/>
+    <col width="12" customWidth="1" min="383" max="383"/>
+    <col width="12" customWidth="1" min="384" max="384"/>
+    <col width="12" customWidth="1" min="385" max="385"/>
+    <col width="12" customWidth="1" min="386" max="386"/>
+    <col width="12" customWidth="1" min="387" max="387"/>
+    <col width="12" customWidth="1" min="388" max="388"/>
+    <col width="12" customWidth="1" min="389" max="389"/>
+    <col width="12" customWidth="1" min="390" max="390"/>
+    <col width="12" customWidth="1" min="391" max="391"/>
+    <col width="12" customWidth="1" min="392" max="392"/>
+    <col width="12" customWidth="1" min="393" max="393"/>
+    <col width="12" customWidth="1" min="394" max="394"/>
+    <col width="12" customWidth="1" min="395" max="395"/>
+    <col width="12" customWidth="1" min="396" max="396"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9859,6 +10089,1156 @@
           <t>2026-08-07</t>
         </is>
       </c>
+      <c r="FK1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="FL1" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="FM1" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="FN1" t="inlineStr">
+        <is>
+          <t>2025-01-08</t>
+        </is>
+      </c>
+      <c r="FO1" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="FP1" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="FQ1" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="FR1" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="FS1" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="FT1" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="FU1" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="FV1" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="FW1" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="FX1" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="FY1" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="FZ1" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="GA1" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="GB1" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="GC1" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="GD1" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="GE1" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="GF1" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="GG1" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="GH1" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="GI1" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="GJ1" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="GK1" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="GL1" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="GM1" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="GN1" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="GO1" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="GP1" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="GQ1" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="GR1" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="GS1" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="GT1" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="GU1" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="GV1" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="GW1" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="GX1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="GY1" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="GZ1" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="HA1" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="HB1" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="HC1" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="HD1" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="HF1" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="HG1" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="HH1" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="HI1" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="HJ1" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="HK1" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="HL1" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="HM1" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="HN1" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="HO1" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="HP1" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="HQ1" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="HR1" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="HS1" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="HT1" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="HU1" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="HV1" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="HW1" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="HX1" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="HY1" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="HZ1" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="IA1" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="IB1" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="IC1" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="ID1" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="IE1" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="IF1" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="IG1" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="IH1" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="II1" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="IJ1" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="IK1" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="IL1" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="IM1" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="IN1" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="IO1" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="IP1" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="IQ1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="IR1" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="IS1" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="IT1" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="IU1" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="IV1" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="IW1" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="IX1" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="IY1" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="IZ1" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="JA1" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="JB1" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="JC1" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="JD1" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="JE1" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="JF1" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="JG1" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="JH1" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="JI1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="JJ1" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="JK1" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="JL1" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="JM1" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="JN1" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="JO1" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="JP1" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="JQ1" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="JR1" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="JS1" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="JT1" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="JU1" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="JV1" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="JW1" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="JX1" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="JY1" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="JZ1" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="KA1" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="KB1" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="KC1" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="KD1" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="KE1" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="KF1" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="KG1" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="KH1" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="KI1" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="KJ1" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="KK1" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="KL1" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="KM1" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="KN1" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="KO1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="KP1" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="KQ1" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="KR1" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="KS1" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="KT1" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="KU1" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="KV1" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="KW1" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="KX1" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="KY1" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="KZ1" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="LA1" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="LB1" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="LC1" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="LD1" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="LE1" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="LF1" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="LG1" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="LH1" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="LI1" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="LJ1" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="LK1" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="LL1" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="LM1" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="LN1" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="LO1" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="LP1" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="LQ1" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="LR1" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="LS1" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="LT1" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="LU1" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="LV1" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="LW1" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="LX1" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="LY1" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="LZ1" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="MA1" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="MB1" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="MC1" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="MD1" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="ME1" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="MF1" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="MG1" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="MH1" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="MI1" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="MJ1" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="MK1" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="ML1" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="MM1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="MN1" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="MO1" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="MP1" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="MQ1" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="MR1" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="MS1" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="MT1" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="MU1" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="MV1" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="MW1" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="MX1" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="MY1" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="MZ1" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="NA1" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="NB1" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="NC1" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="ND1" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="NE1" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="NF1" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="NG1" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="NH1" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="NI1" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="NJ1" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="NK1" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="NL1" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="NM1" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="NN1" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="NO1" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="NP1" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="NQ1" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="NR1" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="NS1" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="NT1" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="NU1" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="NV1" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="NW1" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="NX1" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="NY1" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="NZ1" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="OA1" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="OB1" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="OC1" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="OD1" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="OE1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="OF1" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13254,6 +14634,1839 @@
       </c>
       <c r="DK45" t="n">
         <v>1.96</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Số dư tín phiếu NHNN đang lưu hành</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>tỷ đồng</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER46" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES46" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK46" t="n">
+        <v>50780</v>
+      </c>
+      <c r="FL46" t="n">
+        <v>48980</v>
+      </c>
+      <c r="FM46" t="n">
+        <v>63580</v>
+      </c>
+      <c r="FN46" t="n">
+        <v>93180</v>
+      </c>
+      <c r="FO46" t="n">
+        <v>88380</v>
+      </c>
+      <c r="FP46" t="n">
+        <v>75100</v>
+      </c>
+      <c r="FQ46" t="n">
+        <v>62300</v>
+      </c>
+      <c r="FR46" t="n">
+        <v>74250</v>
+      </c>
+      <c r="FS46" t="n">
+        <v>76.15000000000001</v>
+      </c>
+      <c r="FT46" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="FU46" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="FV46" t="n">
+        <v>32</v>
+      </c>
+      <c r="FW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK46" t="n">
+        <v>7999.3</v>
+      </c>
+      <c r="GL46" t="n">
+        <v>4999.6</v>
+      </c>
+      <c r="GM46" t="n">
+        <v>4999.5</v>
+      </c>
+      <c r="GN46" t="n">
+        <v>3999.7</v>
+      </c>
+      <c r="GO46" t="n">
+        <v>2999.7</v>
+      </c>
+      <c r="GP46" t="n">
+        <v>999.8</v>
+      </c>
+      <c r="GQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="II46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="JZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="KZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="LZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="ME46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="ML46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="MZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="ND46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="NZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="OA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="OB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="OC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="OD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="OE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="OF46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NHNN bơm ròng/hút ròng qua tín phiếu (riêng kênh tín phiếu)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>tỷ đồng</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER47" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES47" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL47" t="n">
+        <v>-1800</v>
+      </c>
+      <c r="FM47" t="n">
+        <v>14600</v>
+      </c>
+      <c r="FN47" t="n">
+        <v>29600</v>
+      </c>
+      <c r="FO47" t="n">
+        <v>-4800</v>
+      </c>
+      <c r="FP47" t="n">
+        <v>-13280</v>
+      </c>
+      <c r="FQ47" t="n">
+        <v>-12800</v>
+      </c>
+      <c r="FR47" t="n">
+        <v>11950</v>
+      </c>
+      <c r="FS47" t="n">
+        <v>-74173.85000000001</v>
+      </c>
+      <c r="FT47" t="n">
+        <v>-15.1</v>
+      </c>
+      <c r="FU47" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="FV47" t="n">
+        <v>-19.95</v>
+      </c>
+      <c r="FW47" t="n">
+        <v>-32</v>
+      </c>
+      <c r="FX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK47" t="n">
+        <v>7999.3</v>
+      </c>
+      <c r="GL47" t="n">
+        <v>-2999.7</v>
+      </c>
+      <c r="GM47" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="GN47" t="n">
+        <v>-999.8</v>
+      </c>
+      <c r="GO47" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="GP47" t="n">
+        <v>-1999.9</v>
+      </c>
+      <c r="GQ47" t="n">
+        <v>-999.8</v>
+      </c>
+      <c r="GR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="II47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="JZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="KZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="LZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="ME47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="ML47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="MZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="ND47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="NZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="OA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="OB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="OC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="OD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="OE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="OF47" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1753,6 +1753,9 @@
       <c r="O3" t="n">
         <v>51.8</v>
       </c>
+      <c r="P3" t="n">
+        <v>52.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1828,6 +1828,9 @@
       <c r="O5" t="n">
         <v>4.69</v>
       </c>
+      <c r="P5" t="n">
+        <v>4.45</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -8260,7 +8260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:AP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -8276,6 +8276,35 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8344,6 +8373,151 @@
           <t>2016</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8553,6 +8727,402 @@
       </c>
       <c r="M7" t="n">
         <v>5639401</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tăng trưởng tích lũy tài sản (đầu tư) theo phương pháp sử dụng GDP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10.245</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.015000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.485</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.112</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.283</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.651</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.159</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7.198</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.682</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.629</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9.862</v>
+      </c>
+      <c r="N8" t="n">
+        <v>30.704</v>
+      </c>
+      <c r="O8" t="n">
+        <v>21.594</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11.036</v>
+      </c>
+      <c r="T8" t="n">
+        <v>22.423</v>
+      </c>
+      <c r="U8" t="n">
+        <v>44.391</v>
+      </c>
+      <c r="V8" t="n">
+        <v>16.594</v>
+      </c>
+      <c r="W8" t="n">
+        <v>16.149</v>
+      </c>
+      <c r="X8" t="n">
+        <v>14.142</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.685</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>12.543</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>10.137</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.749</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>10.563</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>14.121</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>10.501</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10.598</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>11.076</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>25.774</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>5.344</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>5.977</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>10.595</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-4.333</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2.638</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>5.912</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9.073</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tăng trưởng tiêu dùng tư nhân (GDP theo cấu phần sử dụng)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.074</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6.697</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.313</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.383</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.536</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.526</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.983</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7.215</v>
+      </c>
+      <c r="X9" t="n">
+        <v>9.090999999999999</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5.911</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.465</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.596</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.076</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.472</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>7.103</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>7.094</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>7.259</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>8.346</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>10.801</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>9.343</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>3.129</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>10.003</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6.28</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tăng trưởng tiêu dùng chính phủ (GDP theo cấu phần sử dụng)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.548</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.611</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.796</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.835</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.835</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.535</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7.889</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9.243</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>11.534</v>
+      </c>
+      <c r="R10" t="n">
+        <v>11.019</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8.409000000000001</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7.457</v>
+      </c>
+      <c r="U10" t="n">
+        <v>12.822</v>
+      </c>
+      <c r="V10" t="n">
+        <v>10.414</v>
+      </c>
+      <c r="W10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.003</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.221</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-5.704</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.013</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>6.605</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5.378</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>7.192</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>7.774</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>8.202</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>8.497</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>8.904</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>7.522</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>7.595</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>12.284</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>4.294</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -8260,7 +8260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP10"/>
+  <dimension ref="A1:AP13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -9123,6 +9123,402 @@
       </c>
       <c r="AP10" t="n">
         <v>2.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Đóng góp của Đầu tư vào tăng trưởng GDP (điểm %)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>điểm %</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3.373</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.707</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.543</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.436</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.894</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.898</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.127</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.726</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6.113</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.032</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.921</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.836</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.336</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.553</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3.572</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.813</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.892</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3.089</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>7.362</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3.554</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-1.511</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.817</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.775</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Đóng góp của Tiêu dùng tư nhân vào tăng trưởng GDP (điểm %)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>điểm %</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.016</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4.064</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.421</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.992</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.753</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.743</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.886</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.343</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.902</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4.582</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5.651</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.666</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.712</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.807</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.936</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.976</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4.042</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>4.596</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5.955</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>5.262</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.813</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>5.674</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>3.109</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.828</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.599</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Đóng góp của Tiêu dùng chính phủ vào tăng trưởng GDP (điểm %)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>điểm %</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.456</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.626</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.239</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24928,6 +24928,9 @@
       <c r="FH21" t="n">
         <v>4.63</v>
       </c>
+      <c r="FI21" t="n">
+        <v>4.69</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25939,6 +25942,9 @@
       <c r="FH33" t="n">
         <v>3.89</v>
       </c>
+      <c r="FI33" t="n">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26029,6 +26035,9 @@
       <c r="FH34" t="n">
         <v>4.03</v>
       </c>
+      <c r="FI34" t="n">
+        <v>4.06</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26119,6 +26128,9 @@
       <c r="FH35" t="n">
         <v>4.18</v>
       </c>
+      <c r="FI35" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26209,6 +26221,9 @@
       <c r="FH36" t="n">
         <v>4.33</v>
       </c>
+      <c r="FI36" t="n">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26299,6 +26314,9 @@
       <c r="FH37" t="n">
         <v>5.17</v>
       </c>
+      <c r="FI37" t="n">
+        <v>5.22</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -26809,6 +26827,9 @@
       <c r="FH43" t="n">
         <v>0.45</v>
       </c>
+      <c r="FI43" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -26898,6 +26919,9 @@
       </c>
       <c r="FH44" t="n">
         <v>0.74</v>
+      </c>
+      <c r="FI44" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="45">

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -7457,7 +7457,7 @@
         <v>26183.58</v>
       </c>
       <c r="DZ24" t="n">
-        <v>26186.83</v>
+        <v>26033.66</v>
       </c>
     </row>
     <row r="25">
@@ -9422,7 +9422,7 @@
         <v>10.72887492722224</v>
       </c>
       <c r="DZ39" t="n">
-        <v>11.08739824201321</v>
+        <v>10.96816292088586</v>
       </c>
     </row>
     <row r="40">
@@ -9440,7 +9440,7 @@
         <v>1.666190810249435</v>
       </c>
       <c r="DZ40" t="n">
-        <v>1.721869365216013</v>
+        <v>1.703352158363742</v>
       </c>
     </row>
     <row r="41">
@@ -9458,7 +9458,7 @@
         <v>12.38</v>
       </c>
       <c r="DZ41" t="n">
-        <v>12</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="42">
@@ -20446,6 +20446,9 @@
       <c r="M28" t="n">
         <v>74.09999999999999</v>
       </c>
+      <c r="AQ28" t="n">
+        <v>79.3552</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -20487,6 +20490,9 @@
       </c>
       <c r="M29" t="n">
         <v>71.3</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>75.188</v>
       </c>
     </row>
     <row r="30">
@@ -21205,7 +21211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OF47"/>
+  <dimension ref="A1:OL47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21604,6 +21610,12 @@
     <col width="12" customWidth="1" min="394" max="394"/>
     <col width="12" customWidth="1" min="395" max="395"/>
     <col width="12" customWidth="1" min="396" max="396"/>
+    <col width="12" customWidth="1" min="397" max="397"/>
+    <col width="12" customWidth="1" min="398" max="398"/>
+    <col width="12" customWidth="1" min="399" max="399"/>
+    <col width="12" customWidth="1" min="400" max="400"/>
+    <col width="12" customWidth="1" min="401" max="401"/>
+    <col width="12" customWidth="1" min="402" max="402"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23587,6 +23599,36 @@
           <t>2026-04-02</t>
         </is>
       </c>
+      <c r="OG1" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="OH1" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="OI1" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="OJ1" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="OK1" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="OL1" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23698,6 +23740,9 @@
       <c r="FF3" t="n">
         <v>88.90000000000001</v>
       </c>
+      <c r="OJ3" t="n">
+        <v>93.26000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23755,6 +23800,9 @@
       <c r="DR4" t="n">
         <v>119.7</v>
       </c>
+      <c r="FJ4" t="n">
+        <v>119.06</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23809,6 +23857,9 @@
       <c r="FJ5" t="n">
         <v>-74.68000000000001</v>
       </c>
+      <c r="OL5" t="n">
+        <v>-577.14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23872,6 +23923,9 @@
       <c r="FI6" t="n">
         <v>4.6</v>
       </c>
+      <c r="OL6" t="n">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23935,6 +23989,9 @@
       <c r="FI7" t="n">
         <v>5.2</v>
       </c>
+      <c r="OL7" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23998,6 +24055,9 @@
       <c r="FI8" t="n">
         <v>5.9</v>
       </c>
+      <c r="OL8" t="n">
+        <v>5.15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24061,6 +24121,9 @@
       <c r="FI9" t="n">
         <v>6.9</v>
       </c>
+      <c r="OL9" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24124,6 +24187,9 @@
       <c r="FI10" t="n">
         <v>3.69</v>
       </c>
+      <c r="OL10" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24187,6 +24253,9 @@
       <c r="FI11" t="n">
         <v>4.22</v>
       </c>
+      <c r="OL11" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24250,6 +24319,9 @@
       <c r="FI12" t="n">
         <v>4.29</v>
       </c>
+      <c r="OL12" t="n">
+        <v>4.31</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24313,6 +24385,9 @@
       <c r="FI13" t="n">
         <v>4.41</v>
       </c>
+      <c r="OL13" t="n">
+        <v>4.42</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24376,6 +24451,9 @@
       <c r="FI14" t="n">
         <v>4.57</v>
       </c>
+      <c r="OL14" t="n">
+        <v>4.57</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24439,6 +24517,9 @@
       <c r="FI15" t="n">
         <v>-3211.44</v>
       </c>
+      <c r="OK15" t="n">
+        <v>-2251.18</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24499,6 +24580,9 @@
       <c r="FI16" t="n">
         <v>4.5</v>
       </c>
+      <c r="OL16" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24562,6 +24646,9 @@
       <c r="FI17" t="n">
         <v>190527.26</v>
       </c>
+      <c r="OL17" t="n">
+        <v>185332.3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24658,6 +24745,9 @@
       <c r="FJ18" t="n">
         <v>2.25</v>
       </c>
+      <c r="OL18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24754,6 +24844,9 @@
       <c r="FH19" t="n">
         <v>3.73</v>
       </c>
+      <c r="OJ19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24931,6 +25024,9 @@
       <c r="FI21" t="n">
         <v>4.69</v>
       </c>
+      <c r="OK21" t="n">
+        <v>4.68</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25399,6 +25495,9 @@
       <c r="N27" t="n">
         <v>3.46</v>
       </c>
+      <c r="Y27" t="n">
+        <v>3.3</v>
+      </c>
       <c r="CZ27" t="n">
         <v>2.94</v>
       </c>
@@ -25480,6 +25579,9 @@
       <c r="N28" t="n">
         <v>2.57</v>
       </c>
+      <c r="Y28" t="n">
+        <v>2.47</v>
+      </c>
       <c r="CZ28" t="n">
         <v>3.23</v>
       </c>
@@ -25945,6 +26047,9 @@
       <c r="FI33" t="n">
         <v>3.9</v>
       </c>
+      <c r="OK33" t="n">
+        <v>3.87</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26038,6 +26143,9 @@
       <c r="FI34" t="n">
         <v>4.06</v>
       </c>
+      <c r="OK34" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26131,6 +26239,9 @@
       <c r="FI35" t="n">
         <v>4.25</v>
       </c>
+      <c r="OK35" t="n">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26224,6 +26335,9 @@
       <c r="FI36" t="n">
         <v>4.4</v>
       </c>
+      <c r="OK36" t="n">
+        <v>4.38</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26317,6 +26431,9 @@
       <c r="FI37" t="n">
         <v>5.22</v>
       </c>
+      <c r="OK37" t="n">
+        <v>5.24</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -26830,6 +26947,9 @@
       <c r="FI43" t="n">
         <v>0.44</v>
       </c>
+      <c r="OK43" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -26923,6 +27043,9 @@
       <c r="FI44" t="n">
         <v>0.79</v>
       </c>
+      <c r="OK44" t="n">
+        <v>0.8100000000000001</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -27925,6 +28048,9 @@
       <c r="OF46" t="n">
         <v>0</v>
       </c>
+      <c r="OL46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -28838,6 +28964,9 @@
         <v>0</v>
       </c>
       <c r="OF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="OL47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28852,7 +28981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -28861,6 +28990,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28894,6 +29024,11 @@
           <t>2026-W32</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2026-W33</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28915,6 +29050,9 @@
       <c r="F2" t="n">
         <v>5.9</v>
       </c>
+      <c r="G2" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28957,6 +29095,9 @@
       <c r="F4" t="n">
         <v>6.2</v>
       </c>
+      <c r="G4" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28978,6 +29119,9 @@
       <c r="F5" t="n">
         <v>7</v>
       </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28999,6 +29143,9 @@
       <c r="F6" t="n">
         <v>6.13</v>
       </c>
+      <c r="G6" t="n">
+        <v>6.13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29035,6 +29182,9 @@
       <c r="F8" t="n">
         <v>4.5</v>
       </c>
+      <c r="G8" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29056,6 +29206,9 @@
       <c r="F9" t="n">
         <v>7.18</v>
       </c>
+      <c r="G9" t="n">
+        <v>7.75</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29137,6 +29290,9 @@
       <c r="F14" t="n">
         <v>7.6</v>
       </c>
+      <c r="G14" t="n">
+        <v>7.55</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29158,6 +29314,9 @@
       <c r="F15" t="n">
         <v>9.26</v>
       </c>
+      <c r="G15" t="n">
+        <v>9.26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29196,6 +29355,9 @@
       </c>
       <c r="F17" t="n">
         <v>282</v>
+      </c>
+      <c r="G17" t="n">
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -7457,7 +7457,7 @@
         <v>26183.58</v>
       </c>
       <c r="DZ24" t="n">
-        <v>26033.66</v>
+        <v>26119.07</v>
       </c>
     </row>
     <row r="25">
@@ -9422,7 +9422,7 @@
         <v>10.72887492722224</v>
       </c>
       <c r="DZ39" t="n">
-        <v>10.96816292088586</v>
+        <v>10.94442532196677</v>
       </c>
     </row>
     <row r="40">
@@ -9440,7 +9440,7 @@
         <v>1.666190810249435</v>
       </c>
       <c r="DZ40" t="n">
-        <v>1.703352158363742</v>
+        <v>1.699665716920005</v>
       </c>
     </row>
     <row r="41">
@@ -9458,7 +9458,7 @@
         <v>12.38</v>
       </c>
       <c r="DZ41" t="n">
-        <v>14.42</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="42">
@@ -9476,7 +9476,7 @@
         <v>1.98</v>
       </c>
       <c r="DZ42" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="43">
@@ -15960,6 +15960,9 @@
       </c>
       <c r="N74" t="n">
         <v>83.09099999999999</v>
+      </c>
+      <c r="O74" t="n">
+        <v>86318</v>
       </c>
       <c r="Q74" t="n">
         <v>27.125</v>
@@ -21211,7 +21214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OL47"/>
+  <dimension ref="A1:OQ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21616,6 +21619,11 @@
     <col width="12" customWidth="1" min="400" max="400"/>
     <col width="12" customWidth="1" min="401" max="401"/>
     <col width="12" customWidth="1" min="402" max="402"/>
+    <col width="12" customWidth="1" min="403" max="403"/>
+    <col width="12" customWidth="1" min="404" max="404"/>
+    <col width="12" customWidth="1" min="405" max="405"/>
+    <col width="12" customWidth="1" min="406" max="406"/>
+    <col width="12" customWidth="1" min="407" max="407"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23629,6 +23637,31 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="OM1" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="ON1" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="OO1" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="OP1" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="OQ1" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23803,6 +23836,9 @@
       <c r="FJ4" t="n">
         <v>119.06</v>
       </c>
+      <c r="OM4" t="n">
+        <v>118.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23860,6 +23896,9 @@
       <c r="OL5" t="n">
         <v>-577.14</v>
       </c>
+      <c r="OQ5" t="n">
+        <v>-769.09</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23926,6 +23965,9 @@
       <c r="OL6" t="n">
         <v>4.4</v>
       </c>
+      <c r="OQ6" t="n">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23992,6 +24034,9 @@
       <c r="OL7" t="n">
         <v>4.8</v>
       </c>
+      <c r="OQ7" t="n">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24058,6 +24103,9 @@
       <c r="OL8" t="n">
         <v>5.15</v>
       </c>
+      <c r="OQ8" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24124,6 +24172,9 @@
       <c r="OL9" t="n">
         <v>6.5</v>
       </c>
+      <c r="OQ9" t="n">
+        <v>7.03</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24190,6 +24241,9 @@
       <c r="OL10" t="n">
         <v>3.7</v>
       </c>
+      <c r="OQ10" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24256,6 +24310,9 @@
       <c r="OL11" t="n">
         <v>4.25</v>
       </c>
+      <c r="OQ11" t="n">
+        <v>4.24</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24322,6 +24379,9 @@
       <c r="OL12" t="n">
         <v>4.31</v>
       </c>
+      <c r="OQ12" t="n">
+        <v>4.31</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24388,6 +24448,9 @@
       <c r="OL13" t="n">
         <v>4.42</v>
       </c>
+      <c r="OQ13" t="n">
+        <v>4.45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24454,6 +24517,9 @@
       <c r="OL14" t="n">
         <v>4.57</v>
       </c>
+      <c r="OQ14" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24520,6 +24586,9 @@
       <c r="OK15" t="n">
         <v>-2251.18</v>
       </c>
+      <c r="OQ15" t="n">
+        <v>304.63</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24583,6 +24652,9 @@
       <c r="OL16" t="n">
         <v>4.5</v>
       </c>
+      <c r="OQ16" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24649,6 +24721,9 @@
       <c r="OL17" t="n">
         <v>185332.3</v>
       </c>
+      <c r="OQ17" t="n">
+        <v>180990.24</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24748,6 +24823,9 @@
       <c r="OL18" t="n">
         <v>2.25</v>
       </c>
+      <c r="OQ18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24847,6 +24925,9 @@
       <c r="OJ19" t="n">
         <v>3.73</v>
       </c>
+      <c r="OP19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25027,6 +25108,9 @@
       <c r="OK21" t="n">
         <v>4.68</v>
       </c>
+      <c r="OP21" t="n">
+        <v>4.72</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25918,6 +26002,9 @@
       <c r="N32" t="n">
         <v>1.14</v>
       </c>
+      <c r="Y32" t="n">
+        <v>1.08</v>
+      </c>
       <c r="CZ32" t="n">
         <v>-0.92</v>
       </c>
@@ -26050,6 +26137,9 @@
       <c r="OK33" t="n">
         <v>3.87</v>
       </c>
+      <c r="OP33" t="n">
+        <v>3.87</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26146,6 +26236,9 @@
       <c r="OK34" t="n">
         <v>4</v>
       </c>
+      <c r="OP34" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26242,6 +26335,9 @@
       <c r="OK35" t="n">
         <v>4.2</v>
       </c>
+      <c r="OP35" t="n">
+        <v>4.19</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26338,6 +26434,9 @@
       <c r="OK36" t="n">
         <v>4.38</v>
       </c>
+      <c r="OP36" t="n">
+        <v>4.38</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26434,6 +26533,9 @@
       <c r="OK37" t="n">
         <v>5.24</v>
       </c>
+      <c r="OP37" t="n">
+        <v>5.31</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -26950,6 +27052,9 @@
       <c r="OK43" t="n">
         <v>0.48</v>
       </c>
+      <c r="OP43" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -27046,6 +27151,9 @@
       <c r="OK44" t="n">
         <v>0.8100000000000001</v>
       </c>
+      <c r="OP44" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -28051,6 +28159,9 @@
       <c r="OL46" t="n">
         <v>0</v>
       </c>
+      <c r="OQ46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -28967,6 +29078,9 @@
         <v>0</v>
       </c>
       <c r="OL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="OQ47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28981,7 +29095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -28991,6 +29105,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29029,6 +29144,11 @@
           <t>2026-W33</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2026-W34</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29053,6 +29173,9 @@
       <c r="G2" t="n">
         <v>5.9</v>
       </c>
+      <c r="H2" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29098,6 +29221,9 @@
       <c r="G4" t="n">
         <v>6.2</v>
       </c>
+      <c r="H4" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29122,6 +29248,9 @@
       <c r="G5" t="n">
         <v>7</v>
       </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29146,6 +29275,9 @@
       <c r="G6" t="n">
         <v>6.13</v>
       </c>
+      <c r="H6" t="n">
+        <v>6.13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29185,6 +29317,9 @@
       <c r="G8" t="n">
         <v>4.5</v>
       </c>
+      <c r="H8" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29209,6 +29344,9 @@
       <c r="G9" t="n">
         <v>7.75</v>
       </c>
+      <c r="H9" t="n">
+        <v>7.76</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29293,6 +29431,9 @@
       <c r="G14" t="n">
         <v>7.55</v>
       </c>
+      <c r="H14" t="n">
+        <v>7.05</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29317,6 +29458,9 @@
       <c r="G15" t="n">
         <v>9.26</v>
       </c>
+      <c r="H15" t="n">
+        <v>9.26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29358,6 +29502,9 @@
       </c>
       <c r="G17" t="n">
         <v>288</v>
+      </c>
+      <c r="H17" t="n">
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -7369,6 +7369,9 @@
       <c r="M19" t="n">
         <v>5.86</v>
       </c>
+      <c r="O19" t="n">
+        <v>4.24</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7457,7 +7460,7 @@
         <v>26183.58</v>
       </c>
       <c r="DZ24" t="n">
-        <v>26119.07</v>
+        <v>26053.43</v>
       </c>
     </row>
     <row r="25">
@@ -7511,7 +7514,7 @@
         <v>11.7</v>
       </c>
       <c r="P27" t="n">
-        <v>25.9</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -7609,6 +7612,9 @@
       <c r="O31" t="n">
         <v>4.5</v>
       </c>
+      <c r="P31" t="n">
+        <v>4.63</v>
+      </c>
       <c r="BM31" t="n">
         <v>3.25</v>
       </c>
@@ -7855,6 +7861,9 @@
       <c r="O32" t="n">
         <v>34.7</v>
       </c>
+      <c r="P32" t="n">
+        <v>38.1</v>
+      </c>
       <c r="DU32" t="n">
         <v>4.3</v>
       </c>
@@ -7909,6 +7918,9 @@
       <c r="N33" t="n">
         <v>19703851</v>
       </c>
+      <c r="O33" t="n">
+        <v>20150411</v>
+      </c>
       <c r="AO33" t="n">
         <v>6390566</v>
       </c>
@@ -9422,7 +9434,7 @@
         <v>10.72887492722224</v>
       </c>
       <c r="DZ39" t="n">
-        <v>10.94442532196677</v>
+        <v>11.21954394258017</v>
       </c>
     </row>
     <row r="40">
@@ -9440,7 +9452,7 @@
         <v>1.666190810249435</v>
       </c>
       <c r="DZ40" t="n">
-        <v>1.699665716920005</v>
+        <v>1.742391549824577</v>
       </c>
     </row>
     <row r="41">
@@ -9458,7 +9470,7 @@
         <v>12.38</v>
       </c>
       <c r="DZ41" t="n">
-        <v>11.77</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="42">
@@ -9607,6 +9619,9 @@
       <c r="O44" t="n">
         <v>9.890000000000001</v>
       </c>
+      <c r="P44" t="n">
+        <v>3.4</v>
+      </c>
       <c r="DU44" t="n">
         <v>4.3</v>
       </c>
@@ -10069,6 +10084,9 @@
       <c r="N53" t="n">
         <v>18.23</v>
       </c>
+      <c r="O53" t="n">
+        <v>17.41</v>
+      </c>
       <c r="BA53" t="n">
         <v>14.99</v>
       </c>
@@ -10339,6 +10357,9 @@
       <c r="N54" t="n">
         <v>153.37</v>
       </c>
+      <c r="O54" t="n">
+        <v>156.84</v>
+      </c>
       <c r="AO54" t="n">
         <v>91.18000000000001</v>
       </c>
@@ -10651,6 +10672,9 @@
       <c r="M55" t="n">
         <v>16793661</v>
       </c>
+      <c r="O55" t="n">
+        <v>17440361</v>
+      </c>
       <c r="AZ55" t="n">
         <v>7717980</v>
       </c>
@@ -10930,6 +10954,9 @@
       <c r="M56" t="n">
         <v>10.76</v>
       </c>
+      <c r="O56" t="n">
+        <v>10.39</v>
+      </c>
       <c r="BL56" t="n">
         <v>13.92</v>
       </c>
@@ -11179,6 +11206,9 @@
       <c r="O57" t="n">
         <v>1.64</v>
       </c>
+      <c r="P57" t="n">
+        <v>1.56</v>
+      </c>
       <c r="BM57" t="n">
         <v>3.67</v>
       </c>
@@ -11425,6 +11455,9 @@
       <c r="O58" t="n">
         <v>1.35</v>
       </c>
+      <c r="P58" t="n">
+        <v>1.26</v>
+      </c>
       <c r="BM58" t="n">
         <v>1.18</v>
       </c>
@@ -11671,6 +11704,9 @@
       <c r="O59" t="n">
         <v>0.06</v>
       </c>
+      <c r="P59" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="BM59" t="n">
         <v>0.17</v>
       </c>
@@ -11917,6 +11953,9 @@
       <c r="O60" t="n">
         <v>0.51</v>
       </c>
+      <c r="P60" t="n">
+        <v>0.35</v>
+      </c>
       <c r="BM60" t="n">
         <v>0.73</v>
       </c>
@@ -12163,6 +12202,9 @@
       <c r="O61" t="n">
         <v>1.12</v>
       </c>
+      <c r="P61" t="n">
+        <v>1.21</v>
+      </c>
       <c r="BM61" t="n">
         <v>0.68</v>
       </c>
@@ -12457,6 +12499,9 @@
       <c r="M63" t="n">
         <v>19818534</v>
       </c>
+      <c r="O63" t="n">
+        <v>20414616</v>
+      </c>
       <c r="AZ63" t="n">
         <v>9211848</v>
       </c>
@@ -12730,6 +12775,9 @@
       <c r="N64" t="n">
         <v>4.72</v>
       </c>
+      <c r="O64" t="n">
+        <v>7.09</v>
+      </c>
       <c r="BA64" t="n">
         <v>1.9</v>
       </c>
@@ -13006,6 +13054,9 @@
       <c r="M65" t="n">
         <v>1.68</v>
       </c>
+      <c r="O65" t="n">
+        <v>5.6</v>
+      </c>
       <c r="BA65" t="n">
         <v>0.15</v>
       </c>
@@ -13281,6 +13332,9 @@
       </c>
       <c r="M66" t="n">
         <v>1.92</v>
+      </c>
+      <c r="O66" t="n">
+        <v>4.99</v>
       </c>
       <c r="BA66" t="n">
         <v>3</v>
@@ -21214,7 +21268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OQ47"/>
+  <dimension ref="A1:OS47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21624,6 +21678,8 @@
     <col width="12" customWidth="1" min="405" max="405"/>
     <col width="12" customWidth="1" min="406" max="406"/>
     <col width="12" customWidth="1" min="407" max="407"/>
+    <col width="12" customWidth="1" min="408" max="408"/>
+    <col width="12" customWidth="1" min="409" max="409"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23662,6 +23718,16 @@
           <t>2026-08-18</t>
         </is>
       </c>
+      <c r="OR1" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="OS1" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23776,6 +23842,9 @@
       <c r="OJ3" t="n">
         <v>93.26000000000001</v>
       </c>
+      <c r="OQ3" t="n">
+        <v>95.29000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23899,6 +23968,9 @@
       <c r="OQ5" t="n">
         <v>-769.09</v>
       </c>
+      <c r="OS5" t="n">
+        <v>-617.34</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23968,6 +24040,9 @@
       <c r="OQ6" t="n">
         <v>4.9</v>
       </c>
+      <c r="OS6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24037,6 +24112,9 @@
       <c r="OQ7" t="n">
         <v>5.4</v>
       </c>
+      <c r="OS7" t="n">
+        <v>3.55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24106,6 +24184,9 @@
       <c r="OQ8" t="n">
         <v>6</v>
       </c>
+      <c r="OS8" t="n">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24175,6 +24256,9 @@
       <c r="OQ9" t="n">
         <v>7.03</v>
       </c>
+      <c r="OS9" t="n">
+        <v>7.03</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24244,6 +24328,9 @@
       <c r="OQ10" t="n">
         <v>3.7</v>
       </c>
+      <c r="OS10" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24313,6 +24400,9 @@
       <c r="OQ11" t="n">
         <v>4.24</v>
       </c>
+      <c r="OS11" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24382,6 +24472,9 @@
       <c r="OQ12" t="n">
         <v>4.31</v>
       </c>
+      <c r="OS12" t="n">
+        <v>4.31</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24451,6 +24544,9 @@
       <c r="OQ13" t="n">
         <v>4.45</v>
       </c>
+      <c r="OS13" t="n">
+        <v>4.45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24520,6 +24616,9 @@
       <c r="OQ14" t="n">
         <v>4.58</v>
       </c>
+      <c r="OS14" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24589,6 +24688,9 @@
       <c r="OQ15" t="n">
         <v>304.63</v>
       </c>
+      <c r="OS15" t="n">
+        <v>1224.14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24655,6 +24757,9 @@
       <c r="OQ16" t="n">
         <v>4.5</v>
       </c>
+      <c r="OR16" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24724,6 +24829,9 @@
       <c r="OQ17" t="n">
         <v>180990.24</v>
       </c>
+      <c r="OS17" t="n">
+        <v>180833.95</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24826,6 +24934,9 @@
       <c r="OQ18" t="n">
         <v>2.25</v>
       </c>
+      <c r="OS18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24928,6 +25039,9 @@
       <c r="OP19" t="n">
         <v>3.73</v>
       </c>
+      <c r="OQ19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25111,6 +25225,9 @@
       <c r="OP21" t="n">
         <v>4.72</v>
       </c>
+      <c r="OR21" t="n">
+        <v>4.65</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -26140,6 +26257,9 @@
       <c r="OP33" t="n">
         <v>3.87</v>
       </c>
+      <c r="OR33" t="n">
+        <v>3.86</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26239,6 +26359,9 @@
       <c r="OP34" t="n">
         <v>4</v>
       </c>
+      <c r="OR34" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26338,6 +26461,9 @@
       <c r="OP35" t="n">
         <v>4.19</v>
       </c>
+      <c r="OR35" t="n">
+        <v>4.19</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26437,6 +26563,9 @@
       <c r="OP36" t="n">
         <v>4.38</v>
       </c>
+      <c r="OR36" t="n">
+        <v>4.35</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26536,6 +26665,9 @@
       <c r="OP37" t="n">
         <v>5.31</v>
       </c>
+      <c r="OR37" t="n">
+        <v>5.19</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -27055,6 +27187,9 @@
       <c r="OP43" t="n">
         <v>0.53</v>
       </c>
+      <c r="OR43" t="n">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -27154,6 +27289,9 @@
       <c r="OP44" t="n">
         <v>0.85</v>
       </c>
+      <c r="OR44" t="n">
+        <v>0.79</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -27202,6 +27340,9 @@
       <c r="N45" t="n">
         <v>2.73</v>
       </c>
+      <c r="Y45" t="n">
+        <v>2.93</v>
+      </c>
       <c r="CZ45" t="n">
         <v>2.58</v>
       </c>
@@ -28162,6 +28303,9 @@
       <c r="OQ46" t="n">
         <v>0</v>
       </c>
+      <c r="OS46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -29081,6 +29225,9 @@
         <v>0</v>
       </c>
       <c r="OQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="OS47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29345,7 +29492,7 @@
         <v>7.75</v>
       </c>
       <c r="H9" t="n">
-        <v>7.76</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="10">
@@ -29504,7 +29651,7 @@
         <v>288</v>
       </c>
       <c r="H17" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -7460,7 +7460,7 @@
         <v>26183.58</v>
       </c>
       <c r="DZ24" t="n">
-        <v>26053.43</v>
+        <v>26059.91</v>
       </c>
     </row>
     <row r="25">
@@ -9434,7 +9434,7 @@
         <v>10.72887492722224</v>
       </c>
       <c r="DZ39" t="n">
-        <v>11.21954394258017</v>
+        <v>11.30550484838355</v>
       </c>
     </row>
     <row r="40">
@@ -9452,7 +9452,7 @@
         <v>1.666190810249435</v>
       </c>
       <c r="DZ40" t="n">
-        <v>1.742391549824577</v>
+        <v>1.755741250726291</v>
       </c>
     </row>
     <row r="41">
@@ -9470,7 +9470,7 @@
         <v>12.38</v>
       </c>
       <c r="DZ41" t="n">
-        <v>14.11</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="42">
@@ -9488,7 +9488,7 @@
         <v>1.98</v>
       </c>
       <c r="DZ42" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="43">
@@ -21268,7 +21268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OS47"/>
+  <dimension ref="A1:OY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21680,6 +21680,12 @@
     <col width="12" customWidth="1" min="407" max="407"/>
     <col width="12" customWidth="1" min="408" max="408"/>
     <col width="12" customWidth="1" min="409" max="409"/>
+    <col width="12" customWidth="1" min="410" max="410"/>
+    <col width="12" customWidth="1" min="411" max="411"/>
+    <col width="12" customWidth="1" min="412" max="412"/>
+    <col width="12" customWidth="1" min="413" max="413"/>
+    <col width="12" customWidth="1" min="414" max="414"/>
+    <col width="12" customWidth="1" min="415" max="415"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23728,6 +23734,36 @@
           <t>2026-08-20</t>
         </is>
       </c>
+      <c r="OT1" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="OU1" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="OV1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="OW1" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="OX1" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="OY1" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23908,6 +23944,9 @@
       <c r="OM4" t="n">
         <v>118.9</v>
       </c>
+      <c r="OT4" t="n">
+        <v>118.06</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23971,6 +24010,9 @@
       <c r="OS5" t="n">
         <v>-617.34</v>
       </c>
+      <c r="OX5" t="n">
+        <v>276.68</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24043,6 +24085,9 @@
       <c r="OS6" t="n">
         <v>3</v>
       </c>
+      <c r="OX6" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24115,6 +24160,9 @@
       <c r="OS7" t="n">
         <v>3.55</v>
       </c>
+      <c r="OX7" t="n">
+        <v>6.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24187,6 +24235,9 @@
       <c r="OS8" t="n">
         <v>5.6</v>
       </c>
+      <c r="OX8" t="n">
+        <v>6.35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24259,6 +24310,9 @@
       <c r="OS9" t="n">
         <v>7.03</v>
       </c>
+      <c r="OX9" t="n">
+        <v>7.05</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24331,6 +24385,9 @@
       <c r="OS10" t="n">
         <v>3.7</v>
       </c>
+      <c r="OX10" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24403,6 +24460,9 @@
       <c r="OS11" t="n">
         <v>4.25</v>
       </c>
+      <c r="OX11" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24475,6 +24535,9 @@
       <c r="OS12" t="n">
         <v>4.31</v>
       </c>
+      <c r="OX12" t="n">
+        <v>4.32</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24547,6 +24610,9 @@
       <c r="OS13" t="n">
         <v>4.45</v>
       </c>
+      <c r="OX13" t="n">
+        <v>4.45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24619,6 +24685,9 @@
       <c r="OS14" t="n">
         <v>4.58</v>
       </c>
+      <c r="OX14" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24691,6 +24760,9 @@
       <c r="OS15" t="n">
         <v>1224.14</v>
       </c>
+      <c r="OX15" t="n">
+        <v>6481.27</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24832,6 +24904,9 @@
       <c r="OS17" t="n">
         <v>180833.95</v>
       </c>
+      <c r="OX17" t="n">
+        <v>188070.84</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24937,6 +25012,9 @@
       <c r="OS18" t="n">
         <v>2.25</v>
       </c>
+      <c r="OY18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25042,6 +25120,9 @@
       <c r="OQ19" t="n">
         <v>3.73</v>
       </c>
+      <c r="OW19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25228,6 +25309,9 @@
       <c r="OR21" t="n">
         <v>4.65</v>
       </c>
+      <c r="OW21" t="n">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25867,6 +25951,9 @@
       <c r="N29" t="n">
         <v>3.67</v>
       </c>
+      <c r="Y29" t="n">
+        <v>3.7</v>
+      </c>
       <c r="CZ29" t="n">
         <v>2.59</v>
       </c>
@@ -25951,6 +26038,9 @@
       <c r="N30" t="n">
         <v>3.29</v>
       </c>
+      <c r="Y30" t="n">
+        <v>3.34</v>
+      </c>
       <c r="CZ30" t="n">
         <v>2.81</v>
       </c>
@@ -26260,6 +26350,9 @@
       <c r="OR33" t="n">
         <v>3.86</v>
       </c>
+      <c r="OW33" t="n">
+        <v>3.87</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26362,6 +26455,9 @@
       <c r="OR34" t="n">
         <v>4</v>
       </c>
+      <c r="OW34" t="n">
+        <v>4.04</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26464,6 +26560,9 @@
       <c r="OR35" t="n">
         <v>4.19</v>
       </c>
+      <c r="OW35" t="n">
+        <v>4.24</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26566,6 +26665,9 @@
       <c r="OR36" t="n">
         <v>4.35</v>
       </c>
+      <c r="OW36" t="n">
+        <v>4.41</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26668,6 +26770,9 @@
       <c r="OR37" t="n">
         <v>5.19</v>
       </c>
+      <c r="OW37" t="n">
+        <v>5.23</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -27190,6 +27295,9 @@
       <c r="OR43" t="n">
         <v>0.46</v>
       </c>
+      <c r="OW43" t="n">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -27292,6 +27400,9 @@
       <c r="OR44" t="n">
         <v>0.79</v>
       </c>
+      <c r="OW44" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -28306,6 +28417,9 @@
       <c r="OS46" t="n">
         <v>0</v>
       </c>
+      <c r="OX46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -29228,6 +29342,9 @@
         <v>0</v>
       </c>
       <c r="OS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="OX47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29242,7 +29359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -29253,6 +29370,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29296,6 +29414,11 @@
           <t>2026-W34</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2026-W35</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29323,6 +29446,9 @@
       <c r="H2" t="n">
         <v>5.9</v>
       </c>
+      <c r="I2" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29371,6 +29497,9 @@
       <c r="H4" t="n">
         <v>6.2</v>
       </c>
+      <c r="I4" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29398,6 +29527,9 @@
       <c r="H5" t="n">
         <v>7</v>
       </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29425,6 +29557,9 @@
       <c r="H6" t="n">
         <v>6.13</v>
       </c>
+      <c r="I6" t="n">
+        <v>6.13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29467,6 +29602,9 @@
       <c r="H8" t="n">
         <v>4.5</v>
       </c>
+      <c r="I8" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29494,6 +29632,9 @@
       <c r="H9" t="n">
         <v>7.52</v>
       </c>
+      <c r="I9" t="n">
+        <v>7.86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29581,6 +29722,9 @@
       <c r="H14" t="n">
         <v>7.05</v>
       </c>
+      <c r="I14" t="n">
+        <v>8.77</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29608,6 +29752,9 @@
       <c r="H15" t="n">
         <v>9.26</v>
       </c>
+      <c r="I15" t="n">
+        <v>8.949999999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29652,6 +29799,9 @@
       </c>
       <c r="H17" t="n">
         <v>295</v>
+      </c>
+      <c r="I17" t="n">
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -7460,7 +7460,7 @@
         <v>26183.58</v>
       </c>
       <c r="DZ24" t="n">
-        <v>26059.91</v>
+        <v>26044.82</v>
       </c>
     </row>
     <row r="25">
@@ -9434,7 +9434,7 @@
         <v>10.72887492722224</v>
       </c>
       <c r="DZ39" t="n">
-        <v>11.30550484838355</v>
+        <v>11.29118768979197</v>
       </c>
     </row>
     <row r="40">
@@ -9452,7 +9452,7 @@
         <v>1.666190810249435</v>
       </c>
       <c r="DZ40" t="n">
-        <v>1.755741250726291</v>
+        <v>1.753517800622156</v>
       </c>
     </row>
     <row r="41">
@@ -9470,7 +9470,7 @@
         <v>12.38</v>
       </c>
       <c r="DZ41" t="n">
-        <v>12.18</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="42">
@@ -9488,7 +9488,7 @@
         <v>1.98</v>
       </c>
       <c r="DZ42" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="43">
@@ -21268,7 +21268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OY47"/>
+  <dimension ref="A1:PA47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21686,6 +21686,8 @@
     <col width="12" customWidth="1" min="413" max="413"/>
     <col width="12" customWidth="1" min="414" max="414"/>
     <col width="12" customWidth="1" min="415" max="415"/>
+    <col width="12" customWidth="1" min="416" max="416"/>
+    <col width="12" customWidth="1" min="417" max="417"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23764,6 +23766,16 @@
           <t>2026-08-26</t>
         </is>
       </c>
+      <c r="OZ1" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="PA1" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23881,6 +23893,9 @@
       <c r="OQ3" t="n">
         <v>95.29000000000001</v>
       </c>
+      <c r="OX3" t="n">
+        <v>88.23999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24013,6 +24028,9 @@
       <c r="OX5" t="n">
         <v>276.68</v>
       </c>
+      <c r="OZ5" t="n">
+        <v>212.09</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24088,6 +24106,9 @@
       <c r="OX6" t="n">
         <v>2.5</v>
       </c>
+      <c r="OZ6" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24163,6 +24184,9 @@
       <c r="OX7" t="n">
         <v>6.3</v>
       </c>
+      <c r="OZ7" t="n">
+        <v>6.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24238,6 +24262,9 @@
       <c r="OX8" t="n">
         <v>6.35</v>
       </c>
+      <c r="OZ8" t="n">
+        <v>6.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24313,6 +24340,9 @@
       <c r="OX9" t="n">
         <v>7.05</v>
       </c>
+      <c r="OZ9" t="n">
+        <v>6.55</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24388,6 +24418,9 @@
       <c r="OX10" t="n">
         <v>3.7</v>
       </c>
+      <c r="OZ10" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24463,6 +24496,9 @@
       <c r="OX11" t="n">
         <v>4.26</v>
       </c>
+      <c r="OZ11" t="n">
+        <v>4.27</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24538,6 +24574,9 @@
       <c r="OX12" t="n">
         <v>4.32</v>
       </c>
+      <c r="OZ12" t="n">
+        <v>4.32</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24613,6 +24652,9 @@
       <c r="OX13" t="n">
         <v>4.45</v>
       </c>
+      <c r="OZ13" t="n">
+        <v>4.45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24688,6 +24730,9 @@
       <c r="OX14" t="n">
         <v>4.58</v>
       </c>
+      <c r="OZ14" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24763,6 +24808,9 @@
       <c r="OX15" t="n">
         <v>6481.27</v>
       </c>
+      <c r="OZ15" t="n">
+        <v>9596.25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24907,6 +24955,9 @@
       <c r="OX17" t="n">
         <v>188070.84</v>
       </c>
+      <c r="OZ17" t="n">
+        <v>200982.4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25015,6 +25066,9 @@
       <c r="OY18" t="n">
         <v>2.25</v>
       </c>
+      <c r="PA18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25123,6 +25177,9 @@
       <c r="OW19" t="n">
         <v>3.73</v>
       </c>
+      <c r="OY19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25312,6 +25369,9 @@
       <c r="OW21" t="n">
         <v>4.7</v>
       </c>
+      <c r="OZ21" t="n">
+        <v>4.67</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -26353,6 +26413,9 @@
       <c r="OW33" t="n">
         <v>3.87</v>
       </c>
+      <c r="OZ33" t="n">
+        <v>3.84</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26458,6 +26521,9 @@
       <c r="OW34" t="n">
         <v>4.04</v>
       </c>
+      <c r="OZ34" t="n">
+        <v>4.04</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26563,6 +26629,9 @@
       <c r="OW35" t="n">
         <v>4.24</v>
       </c>
+      <c r="OZ35" t="n">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26668,6 +26737,9 @@
       <c r="OW36" t="n">
         <v>4.41</v>
       </c>
+      <c r="OZ36" t="n">
+        <v>4.38</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26773,6 +26845,9 @@
       <c r="OW37" t="n">
         <v>5.23</v>
       </c>
+      <c r="OZ37" t="n">
+        <v>5.19</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -27298,6 +27373,9 @@
       <c r="OW43" t="n">
         <v>0.46</v>
       </c>
+      <c r="OZ43" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -27403,6 +27481,9 @@
       <c r="OW44" t="n">
         <v>0.83</v>
       </c>
+      <c r="OZ44" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -28420,6 +28501,9 @@
       <c r="OX46" t="n">
         <v>0</v>
       </c>
+      <c r="OZ46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -29345,6 +29429,9 @@
         <v>0</v>
       </c>
       <c r="OX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="OZ47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29633,7 +29720,7 @@
         <v>7.52</v>
       </c>
       <c r="I9" t="n">
-        <v>7.86</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="10">
@@ -29723,7 +29810,7 @@
         <v>7.05</v>
       </c>
       <c r="I14" t="n">
-        <v>8.77</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="15">
@@ -29753,7 +29840,7 @@
         <v>9.26</v>
       </c>
       <c r="I15" t="n">
-        <v>8.949999999999999</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -29801,7 +29888,7 @@
         <v>295</v>
       </c>
       <c r="I17" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29894,4 +29895,4566 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Ma</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ky</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Trang thai</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Va tu ky</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Tong tai san (ty)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>VCSH (ty)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>NII (ty)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Tien gui KH (ty)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Liquid Assets (ty)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Gap lai suat rong &lt;=1nam (ty)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Gap lai suat/TTS (%)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Gap thanh khoan rong &lt;=1thang (ty)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Gap thanh khoan/TTS (%)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Stress NII +100bp (ty)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Stress NII +100bp/NII (%)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Che phu rut -10% tien gui (lan)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Nguon (tieu de)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Nguon (url)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Cap nhat luc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>183753.294</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14356.754</v>
+      </c>
+      <c r="G2" t="n">
+        <v>832.067</v>
+      </c>
+      <c r="H2" t="n">
+        <v>89748.55100000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>52951.186</v>
+      </c>
+      <c r="J2" t="n">
+        <v>58964.887</v>
+      </c>
+      <c r="K2" t="n">
+        <v>32.089</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-6979.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-3.798</v>
+      </c>
+      <c r="N2" t="n">
+        <v>196</v>
+      </c>
+      <c r="O2" t="n">
+        <v>23.556</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-an-bnh29042025-000000bo-co-ti-chnh-qu-1-2025.pdf</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-08-31T09:54:52+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>204916.735</v>
+      </c>
+      <c r="F3" t="n">
+        <v>15373.082</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1504.021</v>
+      </c>
+      <c r="H3" t="n">
+        <v>123056.541</v>
+      </c>
+      <c r="I3" t="n">
+        <v>52527.126</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.269</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00012345679012345679ngn-hng-tmcp-an-bnh04092025-000000bo-co-ti-chnh-bn-nin-2025_1_0945.pdf</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-31T11:41:33+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220494.731</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16800.695</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1708.898</v>
+      </c>
+      <c r="H4" t="n">
+        <v>133411.372</v>
+      </c>
+      <c r="I4" t="n">
+        <v>47661.015</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-2072.081999999995</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>124</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7.256</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.572</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604250_Bao_cao_tai_chinh_nam_2025_1775705238.pdf</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:05:32+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>891674.563</v>
+      </c>
+      <c r="F5" t="n">
+        <v>87074.577</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6358.865</v>
+      </c>
+      <c r="H5" t="n">
+        <v>550375.02</v>
+      </c>
+      <c r="I5" t="n">
+        <v>148662.648</v>
+      </c>
+      <c r="J5" t="n">
+        <v>252303.897</v>
+      </c>
+      <c r="K5" t="n">
+        <v>28.296</v>
+      </c>
+      <c r="L5" t="n">
+        <v>13417.335</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1419</v>
+      </c>
+      <c r="O5" t="n">
+        <v>22.315</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.701</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ACB_Baocaotaichinh_Q1_2025_Hopnhat_13052025091456.pdf</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-08-31T09:55:57+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>933541.42</v>
+      </c>
+      <c r="F6" t="n">
+        <v>87210.629</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6683.848</v>
+      </c>
+      <c r="H6" t="n">
+        <v>567406.86</v>
+      </c>
+      <c r="I6" t="n">
+        <v>137553.297</v>
+      </c>
+      <c r="J6" t="n">
+        <v>85041.65799999997</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-198166.713</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-21.227</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1288</v>
+      </c>
+      <c r="O6" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.424</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ACB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_19092025164217.pdf</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-08-31T11:43:25+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ACB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:05:37+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BAB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>175365.541</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12075.66</v>
+      </c>
+      <c r="G8" t="n">
+        <v>873.981</v>
+      </c>
+      <c r="H8" t="n">
+        <v>124794.49</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20918.596</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19828.909</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11.307</v>
+      </c>
+      <c r="L8" t="n">
+        <v>12897.777</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7.355</v>
+      </c>
+      <c r="N8" t="n">
+        <v>274</v>
+      </c>
+      <c r="O8" t="n">
+        <v>31.351</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BAB_25Q1_BCTC_HN_07052025141647.pdf</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-08-31T09:57:27+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BAB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>184957.884</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12204.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>892.223</v>
+      </c>
+      <c r="H9" t="n">
+        <v>131084.67</v>
+      </c>
+      <c r="I9" t="n">
+        <v>27025.886</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18047.83</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9.757999999999999</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10385.428</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.615</v>
+      </c>
+      <c r="N9" t="n">
+        <v>303</v>
+      </c>
+      <c r="O9" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.062</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-bc-30072025-000000bo-co-ti-chnh-qu-2-2025_3_0910.pdf</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-08-31T11:44:48+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BAB</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>195820.302</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13308.904</v>
+      </c>
+      <c r="G10" t="n">
+        <v>979.295</v>
+      </c>
+      <c r="H10" t="n">
+        <v>127023.635</v>
+      </c>
+      <c r="I10" t="n">
+        <v>28133.503</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1734.546</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604687_Bao_cao_tai_chinh_nam_2025_1774883201.pdf</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:08:17+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:01:27+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-08-31T11:50:13+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:08:21+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BVB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>110118.131</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6219.211</v>
+      </c>
+      <c r="G14" t="n">
+        <v>504.791</v>
+      </c>
+      <c r="H14" t="n">
+        <v>71012.33</v>
+      </c>
+      <c r="I14" t="n">
+        <v>18208.379</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-2093.93</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1.902</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>67</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13.273</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.564</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2025-2/2025-04-29/no-name-1745876078.pdf</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:02:43+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BVB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>115509.397</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6919.239</v>
+      </c>
+      <c r="G15" t="n">
+        <v>643.806</v>
+      </c>
+      <c r="H15" t="n">
+        <v>68796.48299999999</v>
+      </c>
+      <c r="I15" t="n">
+        <v>22013.106</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-11704.532</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-10.133</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-4.349</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-bn-vit15082025-000000bo-co-ti-chnh-bn-nin-2025_5_1133.pdf</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026-08-31T11:53:16+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BVB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>133047.699</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7460.484</v>
+      </c>
+      <c r="G16" t="n">
+        <v>814.849</v>
+      </c>
+      <c r="H16" t="n">
+        <v>71413.689</v>
+      </c>
+      <c r="I16" t="n">
+        <v>37002.367</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-13892.442</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-10.442</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.181</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_603502_Bao_cao_tai_chinh_nam_2025_1776046380.pdf</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:11:30+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CTG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2469863.401</v>
+      </c>
+      <c r="F17" t="n">
+        <v>153982.172</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15475.215</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1621227.454</v>
+      </c>
+      <c r="I17" t="n">
+        <v>431140.071</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>148564.507</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6.015</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_Baocaotaichinh_Q1_2025_Hopnhat_23052025140616.pdf</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:05:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CTG</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2609788.006</v>
+      </c>
+      <c r="F18" t="n">
+        <v>163826.196</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15842.616</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1719957.759</v>
+      </c>
+      <c r="I18" t="n">
+        <v>454034.621</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-32156.772</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.232</v>
+      </c>
+      <c r="L18" t="n">
+        <v>411358.605</v>
+      </c>
+      <c r="M18" t="n">
+        <v>15.762</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-503</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-3.175</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_03102025145719.pdf</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2026-08-31T11:55:46+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CTG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2767699.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>179655.005</v>
+      </c>
+      <c r="G19" t="n">
+        <v>17959.696</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1793732.057</v>
+      </c>
+      <c r="I19" t="n">
+        <v>524296.557</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-32156.77299999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1.162</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-71057.747</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-2.567</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-503</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-2.801</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.923</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_HK_20260331_-_CTG_-_BCTC_hop_nhat_kiem_toan_nam_2025__18062026104622.pdf</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:14:15+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EIB</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>251132.546</v>
+      </c>
+      <c r="F20" t="n">
+        <v>25757.442</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1354.384</v>
+      </c>
+      <c r="H20" t="n">
+        <v>175759.164</v>
+      </c>
+      <c r="I20" t="n">
+        <v>32750.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-22896.225</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-9.117000000000001</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-39057.023</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-15.552</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-195</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-14.398</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.863</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/EIB_Baocaotaichinh_Q1_2025_Hopnhat_22052025162515.pdf</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:06:41+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EIB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>256441.971</v>
+      </c>
+      <c r="F21" t="n">
+        <v>26067.006</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1469.401</v>
+      </c>
+      <c r="H21" t="n">
+        <v>177345.265</v>
+      </c>
+      <c r="I21" t="n">
+        <v>35038.121</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5410.181</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.976</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/EIB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025085527.pdf</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2026-08-31T11:57:38+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EIB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>273270.407</v>
+      </c>
+      <c r="F22" t="n">
+        <v>26006.343</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1690.894</v>
+      </c>
+      <c r="H22" t="n">
+        <v>177303.877</v>
+      </c>
+      <c r="I22" t="n">
+        <v>50842.748</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7930.371999999999</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.902</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.868</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_EIB_-_BCTC_hop_nhat_nam_2025_da_kiem_toan_1774925122.pdf</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:16:37+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HDB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:08:58+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HDB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:01:17+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>HDB</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:18:56+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KLB</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>97164.45</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6834.212</v>
+      </c>
+      <c r="G26" t="n">
+        <v>849.086</v>
+      </c>
+      <c r="H26" t="n">
+        <v>70989.97199999999</v>
+      </c>
+      <c r="I26" t="n">
+        <v>18386.133</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-3996.194</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-4.113</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014864567_VI_BAO_CAO_TAI_CHINH_QUY_I_06052025105844.2025_HOP_NHAT</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:10:19+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KLB</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>97630.48299999999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>7246.143</v>
+      </c>
+      <c r="G27" t="n">
+        <v>883.946</v>
+      </c>
+      <c r="H27" t="n">
+        <v>73173.554</v>
+      </c>
+      <c r="I27" t="n">
+        <v>17449.438</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>33012.88</v>
+      </c>
+      <c r="M27" t="n">
+        <v>33.814</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-kin-long28082025-000000bo-co-ti-chnh-bn-nin-2025_1_0929.pdf</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:03:05+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>KLB</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103302.689</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8416.503000000001</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1056.67</v>
+      </c>
+      <c r="H28" t="n">
+        <v>72010.409</v>
+      </c>
+      <c r="I28" t="n">
+        <v>22569.94</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2230.823</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.134</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_KLB_-_BCTC_KiemToan_2025_Hop_nhat_1774928715.pdf</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:20:50+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LPB</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:13:34+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LPB</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:07:34+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LPB</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:22:06+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MBB</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1156917.195</v>
+      </c>
+      <c r="F32" t="n">
+        <v>123676.548</v>
+      </c>
+      <c r="G32" t="n">
+        <v>11692.184</v>
+      </c>
+      <c r="H32" t="n">
+        <v>722622.45</v>
+      </c>
+      <c r="I32" t="n">
+        <v>84084.52099999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>7749.506</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L32" t="n">
+        <v>183923.188</v>
+      </c>
+      <c r="M32" t="n">
+        <v>15.898</v>
+      </c>
+      <c r="N32" t="n">
+        <v>65</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00012345679012345679ngn-hng-tmcp-qun-i24042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:15:17+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MBB</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1289644.328</v>
+      </c>
+      <c r="F33" t="n">
+        <v>127803.65</v>
+      </c>
+      <c r="G33" t="n">
+        <v>12372.117</v>
+      </c>
+      <c r="H33" t="n">
+        <v>783291.9080000001</v>
+      </c>
+      <c r="I33" t="n">
+        <v>116595.397</v>
+      </c>
+      <c r="J33" t="n">
+        <v>40113.92999999999</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-27</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-0.218</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.489</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MBB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025091521.pdf</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:10:05+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MBB</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1615763.927</v>
+      </c>
+      <c r="F34" t="n">
+        <v>142022.525</v>
+      </c>
+      <c r="G34" t="n">
+        <v>14555.292</v>
+      </c>
+      <c r="H34" t="n">
+        <v>921368.132</v>
+      </c>
+      <c r="I34" t="n">
+        <v>256383.938</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-119953.924</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-7.424</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-338533.023</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-20.952</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-1506</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-10.347</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MBB_Baocaotaichinh_2025_Kiemtoan_Hopnhat_1780022210.pdf</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:24:23+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MSB</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>314727.148</v>
+      </c>
+      <c r="F35" t="n">
+        <v>38020.647</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2503.785</v>
+      </c>
+      <c r="H35" t="n">
+        <v>163035.139</v>
+      </c>
+      <c r="I35" t="n">
+        <v>53049.641</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-16352.815</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-5.196</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-71627.23300000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-22.759</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-257</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-10.264</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3.254</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-hng-hi-vit-nam28042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:17:02+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MSB</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>341331.296</v>
+      </c>
+      <c r="F36" t="n">
+        <v>39312.119</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2584.839</v>
+      </c>
+      <c r="H36" t="n">
+        <v>174429.9</v>
+      </c>
+      <c r="I36" t="n">
+        <v>64784.029</v>
+      </c>
+      <c r="J36" t="n">
+        <v>88375.88399999999</v>
+      </c>
+      <c r="K36" t="n">
+        <v>25.892</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-78086.85799999999</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-22.877</v>
+      </c>
+      <c r="N36" t="n">
+        <v>774</v>
+      </c>
+      <c r="O36" t="n">
+        <v>29.944</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3.714</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MSB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025092910.pdf</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:12:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MSB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>407673.941</v>
+      </c>
+      <c r="F37" t="n">
+        <v>42446.058</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3043.554</v>
+      </c>
+      <c r="H37" t="n">
+        <v>196671.626</v>
+      </c>
+      <c r="I37" t="n">
+        <v>85247.459</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-36336.33499999999</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-8.913</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-94852.075</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-23.267</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-330</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-10.843</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MSB_HK_20260330_-_MSB_-_BCTC_hop_nhat_kiem_toan_nam_2025__18062026110209.pdf</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:26:11+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>262251.025</v>
+      </c>
+      <c r="F38" t="n">
+        <v>20213.631</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2112.162</v>
+      </c>
+      <c r="H38" t="n">
+        <v>176385.625</v>
+      </c>
+      <c r="I38" t="n">
+        <v>53623.62</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1044.137999999999</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-26051.455</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-9.933999999999999</v>
+      </c>
+      <c r="N38" t="n">
+        <v>224</v>
+      </c>
+      <c r="O38" t="n">
+        <v>10.605</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-nam-28042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:18:34+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>314798.083</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21239.816</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2122.128</v>
+      </c>
+      <c r="H39" t="n">
+        <v>196932.046</v>
+      </c>
+      <c r="I39" t="n">
+        <v>88326.624</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-7342.066000000003</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-2.332</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-12907.955</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>140</v>
+      </c>
+      <c r="O39" t="n">
+        <v>6.597</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4.485</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NAB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025093916.pdf</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:14:18+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>418333.322</v>
+      </c>
+      <c r="F40" t="n">
+        <v>23430.767</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2327.558</v>
+      </c>
+      <c r="H40" t="n">
+        <v>177810.693</v>
+      </c>
+      <c r="I40" t="n">
+        <v>170154.001</v>
+      </c>
+      <c r="J40" t="n">
+        <v>506013.917</v>
+      </c>
+      <c r="K40" t="n">
+        <v>120.96</v>
+      </c>
+      <c r="L40" t="n">
+        <v>206015.022</v>
+      </c>
+      <c r="M40" t="n">
+        <v>49.247</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1841</v>
+      </c>
+      <c r="O40" t="n">
+        <v>79.096</v>
+      </c>
+      <c r="P40" t="n">
+        <v>9.569000000000001</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NAB_Baocaotaichinh_2025_Kiemtoan_Hopnhat_1780023595.pdf</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:28:37+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NVB</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>130882.914</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6243.613</v>
+      </c>
+      <c r="G41" t="n">
+        <v>504.861</v>
+      </c>
+      <c r="H41" t="n">
+        <v>102527.917</v>
+      </c>
+      <c r="I41" t="n">
+        <v>21312.588</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4928.864</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.766</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-4695.431</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-3.588</v>
+      </c>
+      <c r="N41" t="n">
+        <v>102</v>
+      </c>
+      <c r="O41" t="n">
+        <v>20.204</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.079</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NVB_25Q1_BCTC_HN_09052025064513.pdf</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:20:53+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NVB</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>144053.644</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6555.077</v>
+      </c>
+      <c r="G42" t="n">
+        <v>757.676</v>
+      </c>
+      <c r="H42" t="n">
+        <v>115244.771</v>
+      </c>
+      <c r="I42" t="n">
+        <v>25035.067</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-58074.064</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-40.314</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-319</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-42.102</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.172</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-quc-dn27082025-000000bo-co-ti-chnh-bn-nin-2025_1_0915.pdf</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:16:11+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NVB</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>163614.988</v>
+      </c>
+      <c r="F43" t="n">
+        <v>13592.924</v>
+      </c>
+      <c r="G43" t="n">
+        <v>423.627</v>
+      </c>
+      <c r="H43" t="n">
+        <v>127403.437</v>
+      </c>
+      <c r="I43" t="n">
+        <v>38989.537</v>
+      </c>
+      <c r="J43" t="n">
+        <v>44447.072</v>
+      </c>
+      <c r="K43" t="n">
+        <v>27.166</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>682</v>
+      </c>
+      <c r="O43" t="n">
+        <v>160.991</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604185_Bao_cao_tai_chinh_nam_2025_1774532924.pdf</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:30:26+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OCB</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:23:58+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>OCB</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:23:24+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OCB</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:30:30+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PGB</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>73551.58199999999</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5242.581</v>
+      </c>
+      <c r="G47" t="n">
+        <v>458.27</v>
+      </c>
+      <c r="H47" t="n">
+        <v>46717.488</v>
+      </c>
+      <c r="I47" t="n">
+        <v>22839.31</v>
+      </c>
+      <c r="J47" t="n">
+        <v>4980.354</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6.771</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>35</v>
+      </c>
+      <c r="O47" t="n">
+        <v>7.637</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4.889</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2025-2/2025-04-18/no-name-1744937049.pdf</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:25:19+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PGB</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>78533.89999999999</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6177.553</v>
+      </c>
+      <c r="G48" t="n">
+        <v>471.899</v>
+      </c>
+      <c r="H48" t="n">
+        <v>46726.281</v>
+      </c>
+      <c r="I48" t="n">
+        <v>24930.12</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1419.186</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1.807</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-3100.088</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-3.947</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="P48" t="n">
+        <v>5.335</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất Quý 2 năm 2025</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-08-19/no-name-1755541972.pdf</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:25:04+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PGB</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>88840.17200000001</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6545.253</v>
+      </c>
+      <c r="G49" t="n">
+        <v>481.771</v>
+      </c>
+      <c r="H49" t="n">
+        <v>48460.417</v>
+      </c>
+      <c r="I49" t="n">
+        <v>31153.789</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-448.712</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.505</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-7944.858999999999</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-8.943</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-20</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-4.151</v>
+      </c>
+      <c r="P49" t="n">
+        <v>6.429</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-02/no-name-1775069400.pdf</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:31:51+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SGB</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>33506.33</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4172.432</v>
+      </c>
+      <c r="G50" t="n">
+        <v>217.861</v>
+      </c>
+      <c r="H50" t="n">
+        <v>24539.598</v>
+      </c>
+      <c r="I50" t="n">
+        <v>9035.235999999999</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-8415.234000000002</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-25.115</v>
+      </c>
+      <c r="L50" t="n">
+        <v>5121.561</v>
+      </c>
+      <c r="M50" t="n">
+        <v>15.285</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-102</v>
+      </c>
+      <c r="O50" t="n">
+        <v>-46.819</v>
+      </c>
+      <c r="P50" t="n">
+        <v>3.682</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014834796_VI_BaoCaotaiChinh_HopNhat_Q1_2025_26042025110134.pdf</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:26:54+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SGB</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>35140.737</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4234.018</v>
+      </c>
+      <c r="G51" t="n">
+        <v>233.402</v>
+      </c>
+      <c r="H51" t="n">
+        <v>25595.19</v>
+      </c>
+      <c r="I51" t="n">
+        <v>10508.501</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1423.367</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1633.754</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.649</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-14</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-5.998</v>
+      </c>
+      <c r="P51" t="n">
+        <v>4.106</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00019753086419753087ngn-hng-tmcp-si-gn-cng-thng14082025-000000bo-co-ti-chnh-bn-nin-2025_1_1022.pdf</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:26:51+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SGB</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>35377.029</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4194.143</v>
+      </c>
+      <c r="G52" t="n">
+        <v>65.943</v>
+      </c>
+      <c r="H52" t="n">
+        <v>26326.61</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9373.537</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3391.897</v>
+      </c>
+      <c r="K52" t="n">
+        <v>9.587999999999999</v>
+      </c>
+      <c r="L52" t="n">
+        <v>838.0600000000001</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.369</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-7</v>
+      </c>
+      <c r="O52" t="n">
+        <v>-10.615</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604675_Bao_cao_tai_chinh_nam_2025_1776046299.pdf</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:33:44+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SHB</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:28:16+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SHB</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>825718.9790000001</v>
+      </c>
+      <c r="F54" t="n">
+        <v>63267.914</v>
+      </c>
+      <c r="G54" t="n">
+        <v>9160.064</v>
+      </c>
+      <c r="H54" t="n">
+        <v>561718.311</v>
+      </c>
+      <c r="I54" t="n">
+        <v>139362.736</v>
+      </c>
+      <c r="J54" t="n">
+        <v>101052.076</v>
+      </c>
+      <c r="K54" t="n">
+        <v>12.238</v>
+      </c>
+      <c r="L54" t="n">
+        <v>7001.849</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1186</v>
+      </c>
+      <c r="O54" t="n">
+        <v>12.948</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.481</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250903_-_SHB_-_Bao_Cao_Tai_Chinh_Hop_Nhat_Soat_Xet_Ban_nien_30.6.2025_1756910753.pdf</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:28:17+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SHB</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:34:56+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SSB</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>333746.268</v>
+      </c>
+      <c r="F56" t="n">
+        <v>38599.606</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2450.482</v>
+      </c>
+      <c r="H56" t="n">
+        <v>160043.132</v>
+      </c>
+      <c r="I56" t="n">
+        <v>83940.10000000001</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>24719.945</v>
+      </c>
+      <c r="M56" t="n">
+        <v>7.407</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>5.245</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SSB_23052025144847.pdf</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:31:02+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SSB</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>379013.742</v>
+      </c>
+      <c r="F57" t="n">
+        <v>39487.97</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2464.389</v>
+      </c>
+      <c r="H57" t="n">
+        <v>166648.051</v>
+      </c>
+      <c r="I57" t="n">
+        <v>117396.389</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>26000.343</v>
+      </c>
+      <c r="M57" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>7.045</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250905_-_SSB_-_Bao_cao_tai_chinh_hop_nhat_soat_xet_ban_nien_2025_va_Giai_trinh_bien_dong_LNST_signed_1757323427.pdf</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:30:19+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SSB</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>396443.131</v>
+      </c>
+      <c r="F58" t="n">
+        <v>40372.594</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2451.866</v>
+      </c>
+      <c r="H58" t="n">
+        <v>191807.215</v>
+      </c>
+      <c r="I58" t="n">
+        <v>116960.044</v>
+      </c>
+      <c r="J58" t="n">
+        <v>25542.62000000001</v>
+      </c>
+      <c r="K58" t="n">
+        <v>6.443</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1371.248</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="N58" t="n">
+        <v>568</v>
+      </c>
+      <c r="O58" t="n">
+        <v>23.166</v>
+      </c>
+      <c r="P58" t="n">
+        <v>6.098</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260312_-_SSB_-_BCTC_hop_nhat_kiem_toan_nam_2025_kem_Giai_trinh_bien_dong_LNST_signed_1773310402.pdf</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:36:28+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STB</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>757093.326</v>
+      </c>
+      <c r="F59" t="n">
+        <v>57862.377</v>
+      </c>
+      <c r="G59" t="n">
+        <v>6863.173</v>
+      </c>
+      <c r="H59" t="n">
+        <v>585569.336</v>
+      </c>
+      <c r="I59" t="n">
+        <v>100730.034</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>8816.550999999999</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-si-gn-thng-tn26042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:34:12+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STB</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>807339.224</v>
+      </c>
+      <c r="F60" t="n">
+        <v>59821.207</v>
+      </c>
+      <c r="G60" t="n">
+        <v>6585.077</v>
+      </c>
+      <c r="H60" t="n">
+        <v>624314.777</v>
+      </c>
+      <c r="I60" t="n">
+        <v>125819.938</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-70865.32000000001</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-8.778</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2.015</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/STB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025100208.pdf</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:33:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STB</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>917119.803</v>
+      </c>
+      <c r="F61" t="n">
+        <v>59866.744</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5358.002</v>
+      </c>
+      <c r="H61" t="n">
+        <v>618341.672</v>
+      </c>
+      <c r="I61" t="n">
+        <v>195970.826</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-147426.407</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-16.075</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>3.169</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_STB_-_BCTC_Hop_nhat_nam_2025_da_kiem_toan__1774863040.pdf</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:38:47+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TCB</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>989215.993</v>
+      </c>
+      <c r="F62" t="n">
+        <v>153952.665</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8305.393</v>
+      </c>
+      <c r="H62" t="n">
+        <v>531583.052</v>
+      </c>
+      <c r="I62" t="n">
+        <v>148372.369</v>
+      </c>
+      <c r="J62" t="n">
+        <v>12025.473</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-28602.92</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-2.891</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-470</v>
+      </c>
+      <c r="O62" t="n">
+        <v>-5.659</v>
+      </c>
+      <c r="P62" t="n">
+        <v>2.791</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00001234567901234568ngn-hng-tmcp-k-thng-vit-nam21042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:35:54+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TCB</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1037645.395</v>
+      </c>
+      <c r="F63" t="n">
+        <v>161827.229</v>
+      </c>
+      <c r="G63" t="n">
+        <v>9137.075999999999</v>
+      </c>
+      <c r="H63" t="n">
+        <v>545078.843</v>
+      </c>
+      <c r="I63" t="n">
+        <v>132997.785</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-64704.99100000001</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-6.236</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025101639.pdf</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:36:30+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TCB</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1192344.137</v>
+      </c>
+      <c r="F64" t="n">
+        <v>179501.442</v>
+      </c>
+      <c r="G64" t="n">
+        <v>10787.979</v>
+      </c>
+      <c r="H64" t="n">
+        <v>618911.535</v>
+      </c>
+      <c r="I64" t="n">
+        <v>201481.905</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-95355.82799999998</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-7.997</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-31183.875</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-2.615</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="O64" t="n">
+        <v>-9.27</v>
+      </c>
+      <c r="P64" t="n">
+        <v>3.255</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260317_-_TCB_-_Techcombank-VAS-bao_cao_tai_chinh_hop_nhat-YE25_1773755161.pdf</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:41:25+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TPB</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:40:47+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TPB</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:42:52+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TPB</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>505901.57</v>
+      </c>
+      <c r="F67" t="n">
+        <v>46048.761</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3598.599</v>
+      </c>
+      <c r="H67" t="n">
+        <v>279050.251</v>
+      </c>
+      <c r="I67" t="n">
+        <v>125552.772</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1.704</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>4.499</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_TPB_-_BCTC_hop_nhat_2025_da_kiem_toan_kem_giai_trinh_chenh_lech_LNST_signed_1774952109.pdf</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:43:30+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>VAB</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>129046.444409199</v>
+      </c>
+      <c r="F68" t="n">
+        <v>9151.860456363</v>
+      </c>
+      <c r="G68" t="n">
+        <v>612.5349521319999</v>
+      </c>
+      <c r="H68" t="n">
+        <v>93896.377376687</v>
+      </c>
+      <c r="I68" t="n">
+        <v>19187.7140786</v>
+      </c>
+      <c r="J68" t="n">
+        <v>26350.65</v>
+      </c>
+      <c r="K68" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>167</v>
+      </c>
+      <c r="O68" t="n">
+        <v>27.264</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2.043</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014787653_VI_BaoCaoTaiChinh_Q1_2025_18042025134138.pdf</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:42:19+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VAB</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:46:28+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>VAB</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>140485.531667485</v>
+      </c>
+      <c r="F70" t="n">
+        <v>10155.027138318</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1608.289139551</v>
+      </c>
+      <c r="H70" t="n">
+        <v>99079.937892602</v>
+      </c>
+      <c r="I70" t="n">
+        <v>23789.312582522</v>
+      </c>
+      <c r="J70" t="n">
+        <v>9801.561999999998</v>
+      </c>
+      <c r="K70" t="n">
+        <v>6.977</v>
+      </c>
+      <c r="L70" t="n">
+        <v>11145.647</v>
+      </c>
+      <c r="M70" t="n">
+        <v>7.934</v>
+      </c>
+      <c r="N70" t="n">
+        <v>114</v>
+      </c>
+      <c r="O70" t="n">
+        <v>7.088</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_VAB_BCTC_hop_nhat_da_kiem_toan_Nam_2025_1775054500.pdf</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:45:19+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VBB</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>174377.72</v>
+      </c>
+      <c r="F71" t="n">
+        <v>8897.989</v>
+      </c>
+      <c r="G71" t="n">
+        <v>702.5119999999999</v>
+      </c>
+      <c r="H71" t="n">
+        <v>103017.174</v>
+      </c>
+      <c r="I71" t="n">
+        <v>49825.872</v>
+      </c>
+      <c r="J71" t="n">
+        <v>14256.841</v>
+      </c>
+      <c r="K71" t="n">
+        <v>8.176</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>51</v>
+      </c>
+      <c r="O71" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="P71" t="n">
+        <v>4.837</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/1_vbb_2025_5_7_121b03c_vi_baocaotaichinh_hopnhat_q1_20251_16052025112437.pdf</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:44:04+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VBB</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>178670.984</v>
+      </c>
+      <c r="F72" t="n">
+        <v>9073.486999999999</v>
+      </c>
+      <c r="G72" t="n">
+        <v>687.4059999999999</v>
+      </c>
+      <c r="H72" t="n">
+        <v>104208.415</v>
+      </c>
+      <c r="I72" t="n">
+        <v>45431.683</v>
+      </c>
+      <c r="J72" t="n">
+        <v>16300.747</v>
+      </c>
+      <c r="K72" t="n">
+        <v>9.122999999999999</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-3955.115</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-2.214</v>
+      </c>
+      <c r="N72" t="n">
+        <v>143</v>
+      </c>
+      <c r="O72" t="n">
+        <v>20.803</v>
+      </c>
+      <c r="P72" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-vit-nam-thng-tn05082025-000000bo-co-ti-chnh-bn-nin-2025_1_1517.pdf</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:48:36+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VBB</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>196771.033</v>
+      </c>
+      <c r="F73" t="n">
+        <v>12431.567</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1108.674</v>
+      </c>
+      <c r="H73" t="n">
+        <v>101449.573</v>
+      </c>
+      <c r="I73" t="n">
+        <v>56200.61</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-8211.225</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-4.173</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_603183_Bao_cao_tai_chinh_nam_2025_1776046427.pdf</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:48:14+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>VCB</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:46:39+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VCB</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2217636.6</v>
+      </c>
+      <c r="F75" t="n">
+        <v>213749.422</v>
+      </c>
+      <c r="G75" t="n">
+        <v>14160.192</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1586682.675</v>
+      </c>
+      <c r="I75" t="n">
+        <v>485017.633</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-43033.196</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-487</v>
+      </c>
+      <c r="O75" t="n">
+        <v>-3.439</v>
+      </c>
+      <c r="P75" t="n">
+        <v>3.057</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025111259.pdf</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:50:26+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>VCB</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2442279.166</v>
+      </c>
+      <c r="F76" t="n">
+        <v>224558.726</v>
+      </c>
+      <c r="G76" t="n">
+        <v>16266.825</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1672534.846</v>
+      </c>
+      <c r="I76" t="n">
+        <v>575462.635</v>
+      </c>
+      <c r="J76" t="n">
+        <v>819.975</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>7</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="P76" t="n">
+        <v>3.441</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_VCB_-_BCTC_hop_nhat_kiem_toan_nam_2025_1774870712.pdf</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:50:20+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>VIB</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>495727.377</v>
+      </c>
+      <c r="F77" t="n">
+        <v>43643.267</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3737.109</v>
+      </c>
+      <c r="H77" t="n">
+        <v>282298.036</v>
+      </c>
+      <c r="I77" t="n">
+        <v>109632.918</v>
+      </c>
+      <c r="J77" t="n">
+        <v>60162.859</v>
+      </c>
+      <c r="K77" t="n">
+        <v>12.136</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>370</v>
+      </c>
+      <c r="O77" t="n">
+        <v>9.901</v>
+      </c>
+      <c r="P77" t="n">
+        <v>3.884</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-07-29/no-name-1753727617.pdf</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>2026-08-31T10:48:45+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>VIB</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>530909.024</v>
+      </c>
+      <c r="F78" t="n">
+        <v>43627.741</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3968.694</v>
+      </c>
+      <c r="H78" t="n">
+        <v>304392.951</v>
+      </c>
+      <c r="I78" t="n">
+        <v>104990.528</v>
+      </c>
+      <c r="J78" t="n">
+        <v>50291.15800000001</v>
+      </c>
+      <c r="K78" t="n">
+        <v>9.473000000000001</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-74107.53099999999</v>
+      </c>
+      <c r="M78" t="n">
+        <v>-13.959</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-130</v>
+      </c>
+      <c r="O78" t="n">
+        <v>-3.276</v>
+      </c>
+      <c r="P78" t="n">
+        <v>3.449</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-quc-t-vit-nam06082025-000000bo-co-ti-chnh-hp-nht-bn-nin_1_0929.pdf</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>2026-08-31T12:52:16+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>VIB</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>556098.441</v>
+      </c>
+      <c r="F79" t="n">
+        <v>46904.739</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4213.631</v>
+      </c>
+      <c r="H79" t="n">
+        <v>294577.661</v>
+      </c>
+      <c r="I79" t="n">
+        <v>116961.762</v>
+      </c>
+      <c r="J79" t="n">
+        <v>26608.905</v>
+      </c>
+      <c r="K79" t="n">
+        <v>4.785</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-278</v>
+      </c>
+      <c r="O79" t="n">
+        <v>-6.598</v>
+      </c>
+      <c r="P79" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260302_-_VIB_-_BCTC_hop_nhat_kiem_toan_2025_1772443477.pdf</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>2026-08-31T01:52:28+07:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR56"/>
+  <dimension ref="A1:AR58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6163,6 +6163,48 @@
       </c>
       <c r="AR56" t="n">
         <v>2.005</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Rủi ro lãi suất hệ thống NH niêm yết (ΔNII/NII khi LS +100bp)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>2.929</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-0.341</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Rủi ro thanh khoản hệ thống NH niêm yết (che phủ rút -10% tiền gửi)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>259.6</v>
+      </c>
+      <c r="H58" t="n">
+        <v>275.1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>350.3</v>
       </c>
     </row>
   </sheetData>
@@ -30192,7 +30234,7 @@
         <v>47661.015</v>
       </c>
       <c r="J4" t="n">
-        <v>-2072.081999999995</v>
+        <v>-2072.081999999999</v>
       </c>
       <c r="K4" t="n">
         <v>-0.9399999999999999</v>
@@ -30328,7 +30370,7 @@
         <v>137553.297</v>
       </c>
       <c r="J6" t="n">
-        <v>85041.65799999997</v>
+        <v>85041.658</v>
       </c>
       <c r="K6" t="n">
         <v>9.109999999999999</v>
@@ -30688,7 +30730,7 @@
         <v>18208.379</v>
       </c>
       <c r="J14" t="n">
-        <v>-2093.93</v>
+        <v>-2093.930000000001</v>
       </c>
       <c r="K14" t="n">
         <v>-1.902</v>
@@ -31846,7 +31888,7 @@
         <v>-5.196</v>
       </c>
       <c r="L35" t="n">
-        <v>-71627.23300000001</v>
+        <v>-71627.23299999999</v>
       </c>
       <c r="M35" t="n">
         <v>-22.759</v>
@@ -31976,7 +32018,7 @@
         <v>85247.459</v>
       </c>
       <c r="J37" t="n">
-        <v>-36336.33499999999</v>
+        <v>-36336.335</v>
       </c>
       <c r="K37" t="n">
         <v>-8.913</v>
@@ -32044,7 +32086,7 @@
         <v>53623.62</v>
       </c>
       <c r="J38" t="n">
-        <v>1044.137999999999</v>
+        <v>1044.137999999998</v>
       </c>
       <c r="K38" t="n">
         <v>0.398</v>
@@ -32112,7 +32154,7 @@
         <v>88326.624</v>
       </c>
       <c r="J39" t="n">
-        <v>-7342.066000000003</v>
+        <v>-7342.066000000001</v>
       </c>
       <c r="K39" t="n">
         <v>-2.332</v>
@@ -32384,7 +32426,7 @@
         <v>38989.537</v>
       </c>
       <c r="J43" t="n">
-        <v>44447.072</v>
+        <v>44447.07199999999</v>
       </c>
       <c r="K43" t="n">
         <v>27.166</v>
@@ -32654,7 +32696,7 @@
         <v>31153.789</v>
       </c>
       <c r="J49" t="n">
-        <v>-448.712</v>
+        <v>-448.7119999999998</v>
       </c>
       <c r="K49" t="n">
         <v>-0.505</v>
@@ -32722,7 +32764,7 @@
         <v>9035.235999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>-8415.234000000002</v>
+        <v>-8415.234</v>
       </c>
       <c r="K50" t="n">
         <v>-25.115</v>
@@ -33582,7 +33624,7 @@
         <v>201481.905</v>
       </c>
       <c r="J64" t="n">
-        <v>-95355.82799999998</v>
+        <v>-95355.82799999999</v>
       </c>
       <c r="K64" t="n">
         <v>-7.997</v>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -29945,7 +29945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:AH79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -29967,6 +29967,21 @@
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30012,55 +30027,130 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Cho vay KH (ty)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>LDR (%)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Liquid Assets (ty)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Gap thanh khoan rong &lt;=1thang (ty)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Gap thanh khoan/TTS &lt;=1thang (%)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Gap thanh khoan/TTS &lt;=3thang (%)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Gap thanh khoan/TTS &lt;=1nam (%)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Short-term Funding (ty)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Long-term Assets (ty)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ST Funding/LT Assets (%)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>NSFR proxy (%)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>LMI (%)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Che phu rut -10% tien gui (lan)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>Gap lai suat rong &lt;=1nam (ty)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Gap lai suat/TTS (%)</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Gap thanh khoan rong &lt;=1thang (ty)</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Gap thanh khoan/TTS (%)</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Gap lai suat/TTS &lt;=1thang (%)</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Gap lai suat/TTS &lt;=3thang (%)</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Gap lai suat/TTS &lt;=1nam (%)</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>RSA (ty)</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>RSL (ty)</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>RSA/RSL (%)</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Stress NII +100bp (ty)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Stress NII +100bp/NII (%)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Che phu rut -10% tien gui (lan)</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Stress NII +100bp/VCSH (%)</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Nguon (tieu de)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Nguon (url)</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Cap nhat luc</t>
         </is>
@@ -30095,13 +30185,13 @@
         <v>89748.55100000001</v>
       </c>
       <c r="I2" t="n">
+        <v>96332.82399999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>107.336</v>
+      </c>
+      <c r="K2" t="n">
         <v>52951.186</v>
-      </c>
-      <c r="J2" t="n">
-        <v>58964.887</v>
-      </c>
-      <c r="K2" t="n">
-        <v>32.089</v>
       </c>
       <c r="L2" t="n">
         <v>-6979.3</v>
@@ -30110,25 +30200,46 @@
         <v>-3.798</v>
       </c>
       <c r="N2" t="n">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-20.242</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="V2" t="n">
+        <v>58964.887</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.734</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6.136</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>32.089</v>
+      </c>
+      <c r="AC2" t="n">
         <v>196</v>
       </c>
-      <c r="O2" t="n">
+      <c r="AD2" t="n">
         <v>23.556</v>
       </c>
-      <c r="P2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AE2" t="n">
+        <v>1.365</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-an-bnh29042025-000000bo-co-ti-chnh-qu-1-2025.pdf</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>2026-08-31T09:54:52+07:00</t>
         </is>
@@ -30163,14 +30274,14 @@
         <v>123056.541</v>
       </c>
       <c r="I3" t="n">
+        <v>112744.398</v>
+      </c>
+      <c r="J3" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="K3" t="n">
         <v>52527.126</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
@@ -30183,20 +30294,41 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
+      <c r="U3" t="n">
         <v>4.269</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00012345679012345679ngn-hng-tmcp-an-bnh04092025-000000bo-co-ti-chnh-bn-nin-2025_1_0945.pdf</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>2026-08-31T11:41:33+07:00</t>
         </is>
@@ -30231,40 +30363,61 @@
         <v>133411.372</v>
       </c>
       <c r="I4" t="n">
+        <v>112691.295</v>
+      </c>
+      <c r="J4" t="n">
+        <v>84.46899999999999</v>
+      </c>
+      <c r="K4" t="n">
         <v>47661.015</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.572</v>
+      </c>
+      <c r="V4" t="n">
         <v>-2072.081999999999</v>
       </c>
-      <c r="K4" t="n">
+      <c r="W4" t="n">
+        <v>-6.467</v>
+      </c>
+      <c r="X4" t="n">
+        <v>25.695</v>
+      </c>
+      <c r="Y4" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="AC4" t="n">
         <v>124</v>
       </c>
-      <c r="O4" t="n">
+      <c r="AD4" t="n">
         <v>7.256</v>
       </c>
-      <c r="P4" t="n">
-        <v>3.572</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AE4" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604250_Bao_cao_tai_chinh_nam_2025_1775705238.pdf</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>2026-08-31T01:05:32+07:00</t>
         </is>
@@ -30299,13 +30452,13 @@
         <v>550375.02</v>
       </c>
       <c r="I5" t="n">
+        <v>592430.7610000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>107.641</v>
+      </c>
+      <c r="K5" t="n">
         <v>148662.648</v>
-      </c>
-      <c r="J5" t="n">
-        <v>252303.897</v>
-      </c>
-      <c r="K5" t="n">
-        <v>28.296</v>
       </c>
       <c r="L5" t="n">
         <v>13417.335</v>
@@ -30314,25 +30467,61 @@
         <v>1.505</v>
       </c>
       <c r="N5" t="n">
+        <v>-20.863</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-19.401</v>
+      </c>
+      <c r="P5" t="n">
+        <v>557773.9669999999</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>336448.561</v>
+      </c>
+      <c r="R5" t="n">
+        <v>165.783</v>
+      </c>
+      <c r="S5" t="n">
+        <v>105.199</v>
+      </c>
+      <c r="T5" t="n">
+        <v>95.05800000000001</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.701</v>
+      </c>
+      <c r="V5" t="n">
+        <v>252303.897</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-8.601000000000001</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>28.296</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1419</v>
       </c>
-      <c r="O5" t="n">
+      <c r="AD5" t="n">
         <v>22.315</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.701</v>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AE5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ACB_Baocaotaichinh_Q1_2025_Hopnhat_13052025091456.pdf</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>2026-08-31T09:55:57+07:00</t>
         </is>
@@ -30367,13 +30556,13 @@
         <v>567406.86</v>
       </c>
       <c r="I6" t="n">
+        <v>627669.3959999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>110.621</v>
+      </c>
+      <c r="K6" t="n">
         <v>137553.297</v>
-      </c>
-      <c r="J6" t="n">
-        <v>85041.658</v>
-      </c>
-      <c r="K6" t="n">
-        <v>9.109999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>-198166.713</v>
@@ -30382,25 +30571,61 @@
         <v>-21.227</v>
       </c>
       <c r="N6" t="n">
+        <v>-20.982</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-14.681</v>
+      </c>
+      <c r="P6" t="n">
+        <v>796199.0429999999</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>281026.686</v>
+      </c>
+      <c r="R6" t="n">
+        <v>283.318</v>
+      </c>
+      <c r="S6" t="n">
+        <v>48.872</v>
+      </c>
+      <c r="T6" t="n">
+        <v>204.618</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.424</v>
+      </c>
+      <c r="V6" t="n">
+        <v>85041.658</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-9.567</v>
+      </c>
+      <c r="X6" t="n">
+        <v>29.286</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1288</v>
       </c>
-      <c r="O6" t="n">
+      <c r="AD6" t="n">
         <v>19.27</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.424</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AE6" t="n">
+        <v>1.477</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ACB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_19092025164217.pdf</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>2026-08-31T11:43:25+07:00</t>
         </is>
@@ -30422,7 +30647,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2026-08-31T01:05:37+07:00</t>
         </is>
@@ -30457,13 +30682,13 @@
         <v>124794.49</v>
       </c>
       <c r="I8" t="n">
+        <v>109795.253</v>
+      </c>
+      <c r="J8" t="n">
+        <v>87.98099999999999</v>
+      </c>
+      <c r="K8" t="n">
         <v>20918.596</v>
-      </c>
-      <c r="J8" t="n">
-        <v>19828.909</v>
-      </c>
-      <c r="K8" t="n">
-        <v>11.307</v>
       </c>
       <c r="L8" t="n">
         <v>12897.777</v>
@@ -30472,25 +30697,61 @@
         <v>7.355</v>
       </c>
       <c r="N8" t="n">
+        <v>-2.203</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-18.719</v>
+      </c>
+      <c r="P8" t="n">
+        <v>133289.881</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>211012.517</v>
+      </c>
+      <c r="R8" t="n">
+        <v>63.167</v>
+      </c>
+      <c r="S8" t="n">
+        <v>83.773</v>
+      </c>
+      <c r="T8" t="n">
+        <v>119.37</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="V8" t="n">
+        <v>19828.909</v>
+      </c>
+      <c r="W8" t="n">
+        <v>6.184</v>
+      </c>
+      <c r="X8" t="n">
+        <v>26.223</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>11.307</v>
+      </c>
+      <c r="AC8" t="n">
         <v>274</v>
       </c>
-      <c r="O8" t="n">
+      <c r="AD8" t="n">
         <v>31.351</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.676</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AE8" t="n">
+        <v>2.269</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BAB_25Q1_BCTC_HN_07052025141647.pdf</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2026-08-31T09:57:27+07:00</t>
         </is>
@@ -30525,13 +30786,13 @@
         <v>131084.67</v>
       </c>
       <c r="I9" t="n">
+        <v>113650.615</v>
+      </c>
+      <c r="J9" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="K9" t="n">
         <v>27025.886</v>
-      </c>
-      <c r="J9" t="n">
-        <v>18047.83</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9.757999999999999</v>
       </c>
       <c r="L9" t="n">
         <v>10385.428</v>
@@ -30540,25 +30801,61 @@
         <v>5.615</v>
       </c>
       <c r="N9" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-19.675</v>
+      </c>
+      <c r="P9" t="n">
+        <v>172753.881</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>224291.614</v>
+      </c>
+      <c r="R9" t="n">
+        <v>77.02200000000001</v>
+      </c>
+      <c r="S9" t="n">
+        <v>83.10599999999999</v>
+      </c>
+      <c r="T9" t="n">
+        <v>120.328</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.062</v>
+      </c>
+      <c r="V9" t="n">
+        <v>18047.83</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.753</v>
+      </c>
+      <c r="X9" t="n">
+        <v>28.506</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.757999999999999</v>
+      </c>
+      <c r="AC9" t="n">
         <v>303</v>
       </c>
-      <c r="O9" t="n">
+      <c r="AD9" t="n">
         <v>33.96</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.062</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AE9" t="n">
+        <v>2.483</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-bc-30072025-000000bo-co-ti-chnh-qu-2-2025_3_0910.pdf</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>2026-08-31T11:44:48+07:00</t>
         </is>
@@ -30593,13 +30890,13 @@
         <v>127023.635</v>
       </c>
       <c r="I10" t="n">
+        <v>124840.777</v>
+      </c>
+      <c r="J10" t="n">
+        <v>98.282</v>
+      </c>
+      <c r="K10" t="n">
         <v>28133.503</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1734.546</v>
@@ -30608,25 +30905,61 @@
         <v>0.886</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-5.328</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-20.325</v>
       </c>
       <c r="P10" t="n">
+        <v>27833.54</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>278509.821</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9.994</v>
+      </c>
+      <c r="S10" t="n">
+        <v>85.13500000000001</v>
+      </c>
+      <c r="T10" t="n">
+        <v>117.461</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.215</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604687_Bao_cao_tai_chinh_nam_2025_1774883201.pdf</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>2026-08-31T01:08:17+07:00</t>
         </is>
@@ -30648,7 +30981,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>2026-08-31T10:01:27+07:00</t>
         </is>
@@ -30670,7 +31003,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>2026-08-31T11:50:13+07:00</t>
         </is>
@@ -30692,7 +31025,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>2026-08-31T01:08:21+07:00</t>
         </is>
@@ -30727,40 +31060,61 @@
         <v>71012.33</v>
       </c>
       <c r="I14" t="n">
+        <v>69732.34299999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>98.19799999999999</v>
+      </c>
+      <c r="K14" t="n">
         <v>18208.379</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.564</v>
+      </c>
+      <c r="V14" t="n">
         <v>-2093.930000000001</v>
       </c>
-      <c r="K14" t="n">
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11.222</v>
+      </c>
+      <c r="Y14" t="n">
         <v>-1.902</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="AC14" t="n">
         <v>67</v>
       </c>
-      <c r="O14" t="n">
+      <c r="AD14" t="n">
         <v>13.273</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.564</v>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="AE14" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="AF14" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-2/2025-04-29/no-name-1745876078.pdf</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="AH14" t="inlineStr">
         <is>
           <t>2026-08-31T10:02:43+07:00</t>
         </is>
@@ -30795,40 +31149,61 @@
         <v>68796.48299999999</v>
       </c>
       <c r="I15" t="n">
+        <v>71475.694</v>
+      </c>
+      <c r="J15" t="n">
+        <v>103.894</v>
+      </c>
+      <c r="K15" t="n">
         <v>22013.106</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V15" t="n">
         <v>-11704.532</v>
       </c>
-      <c r="K15" t="n">
+      <c r="W15" t="n">
+        <v>-2.599</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9.491</v>
+      </c>
+      <c r="Y15" t="n">
         <v>-10.133</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="AC15" t="n">
         <v>-28</v>
       </c>
-      <c r="O15" t="n">
+      <c r="AD15" t="n">
         <v>-4.349</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="AE15" t="n">
+        <v>-0.405</v>
+      </c>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-bn-vit15082025-000000bo-co-ti-chnh-bn-nin-2025_5_1133.pdf</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="AH15" t="inlineStr">
         <is>
           <t>2026-08-31T11:53:16+07:00</t>
         </is>
@@ -30863,13 +31238,13 @@
         <v>71413.689</v>
       </c>
       <c r="I16" t="n">
+        <v>76601.368</v>
+      </c>
+      <c r="J16" t="n">
+        <v>107.264</v>
+      </c>
+      <c r="K16" t="n">
         <v>37002.367</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>-13892.442</v>
@@ -30878,25 +31253,61 @@
         <v>-10.442</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-21.325</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-26.587</v>
       </c>
       <c r="P16" t="n">
+        <v>120596.378</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>45595.207</v>
+      </c>
+      <c r="R16" t="n">
+        <v>264.494</v>
+      </c>
+      <c r="S16" t="n">
+        <v>19.122</v>
+      </c>
+      <c r="T16" t="n">
+        <v>522.96</v>
+      </c>
+      <c r="U16" t="n">
         <v>5.181</v>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_603502_Bao_cao_tai_chinh_nam_2025_1776046380.pdf</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="AH16" t="inlineStr">
         <is>
           <t>2026-08-31T01:11:30+07:00</t>
         </is>
@@ -30931,13 +31342,13 @@
         <v>1621227.454</v>
       </c>
       <c r="I17" t="n">
+        <v>1762190.229</v>
+      </c>
+      <c r="J17" t="n">
+        <v>108.695</v>
+      </c>
+      <c r="K17" t="n">
         <v>431140.071</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>148564.507</v>
@@ -30946,25 +31357,61 @@
         <v>6.015</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>12.335</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>16.751</v>
       </c>
       <c r="P17" t="n">
+        <v>1858786.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>965780.137</v>
+      </c>
+      <c r="R17" t="n">
+        <v>192.465</v>
+      </c>
+      <c r="S17" t="n">
+        <v>63.273</v>
+      </c>
+      <c r="T17" t="n">
+        <v>158.046</v>
+      </c>
+      <c r="U17" t="n">
         <v>2.659</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_Baocaotaichinh_Q1_2025_Hopnhat_23052025140616.pdf</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>2026-08-31T10:05:00+07:00</t>
         </is>
@@ -30999,13 +31446,13 @@
         <v>1719957.759</v>
       </c>
       <c r="I18" t="n">
+        <v>1865914.07</v>
+      </c>
+      <c r="J18" t="n">
+        <v>108.486</v>
+      </c>
+      <c r="K18" t="n">
         <v>454034.621</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-32156.772</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-1.232</v>
       </c>
       <c r="L18" t="n">
         <v>411358.605</v>
@@ -31014,25 +31461,61 @@
         <v>15.762</v>
       </c>
       <c r="N18" t="n">
+        <v>20.335</v>
+      </c>
+      <c r="O18" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="P18" t="n">
+        <v>551097.197</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>696419.642</v>
+      </c>
+      <c r="R18" t="n">
+        <v>79.133</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="T18" t="n">
+        <v>627.439</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-32156.772</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-13.059</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-7.841</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-1.232</v>
+      </c>
+      <c r="AC18" t="n">
         <v>-503</v>
       </c>
-      <c r="O18" t="n">
+      <c r="AD18" t="n">
         <v>-3.175</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q18" t="inlineStr">
+      <c r="AE18" t="n">
+        <v>-0.307</v>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_03102025145719.pdf</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>2026-08-31T11:55:46+07:00</t>
         </is>
@@ -31067,13 +31550,13 @@
         <v>1793732.057</v>
       </c>
       <c r="I19" t="n">
+        <v>1957462.503</v>
+      </c>
+      <c r="J19" t="n">
+        <v>109.128</v>
+      </c>
+      <c r="K19" t="n">
         <v>524296.557</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-32156.77299999999</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-1.162</v>
       </c>
       <c r="L19" t="n">
         <v>-71057.747</v>
@@ -31082,25 +31565,61 @@
         <v>-2.567</v>
       </c>
       <c r="N19" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-2.622</v>
+      </c>
+      <c r="P19" t="n">
+        <v>54223.523</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>289409.671</v>
+      </c>
+      <c r="R19" t="n">
+        <v>18.736</v>
+      </c>
+      <c r="S19" t="n">
+        <v>62.639</v>
+      </c>
+      <c r="T19" t="n">
+        <v>159.646</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.923</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-32156.77299999999</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-12.314</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-7.394</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-1.162</v>
+      </c>
+      <c r="AC19" t="n">
         <v>-503</v>
       </c>
-      <c r="O19" t="n">
+      <c r="AD19" t="n">
         <v>-2.801</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.923</v>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="AE19" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_HK_20260331_-_CTG_-_BCTC_hop_nhat_kiem_toan_nam_2025__18062026104622.pdf</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="AH19" t="inlineStr">
         <is>
           <t>2026-08-31T01:14:15+07:00</t>
         </is>
@@ -31135,13 +31654,13 @@
         <v>175759.164</v>
       </c>
       <c r="I20" t="n">
+        <v>178533.424</v>
+      </c>
+      <c r="J20" t="n">
+        <v>101.578</v>
+      </c>
+      <c r="K20" t="n">
         <v>32750.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-22896.225</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-9.117000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>-39057.023</v>
@@ -31150,25 +31669,61 @@
         <v>-15.552</v>
       </c>
       <c r="N20" t="n">
+        <v>-15.086</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-19.921</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-37879.928</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-12107.945</v>
+      </c>
+      <c r="R20" t="n">
+        <v>312.852</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-112.571</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-88.833</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.863</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-22896.225</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-11.948</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-4.564</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-9.117000000000001</v>
+      </c>
+      <c r="AC20" t="n">
         <v>-195</v>
       </c>
-      <c r="O20" t="n">
+      <c r="AD20" t="n">
         <v>-14.398</v>
       </c>
-      <c r="P20" t="n">
-        <v>1.863</v>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="AE20" t="n">
+        <v>-0.757</v>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/EIB_Baocaotaichinh_Q1_2025_Hopnhat_22052025162515.pdf</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="AH20" t="inlineStr">
         <is>
           <t>2026-08-31T10:06:41+07:00</t>
         </is>
@@ -31203,13 +31758,13 @@
         <v>177345.265</v>
       </c>
       <c r="I21" t="n">
+        <v>180736.493</v>
+      </c>
+      <c r="J21" t="n">
+        <v>101.912</v>
+      </c>
+      <c r="K21" t="n">
         <v>35038.121</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>5410.181</v>
@@ -31218,25 +31773,61 @@
         <v>2.11</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.812</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.812</v>
       </c>
       <c r="P21" t="n">
+        <v>7211.802</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>31185.847</v>
+      </c>
+      <c r="R21" t="n">
+        <v>23.125</v>
+      </c>
+      <c r="S21" t="n">
+        <v>91.31399999999999</v>
+      </c>
+      <c r="T21" t="n">
+        <v>109.513</v>
+      </c>
+      <c r="U21" t="n">
         <v>1.976</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/EIB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025085527.pdf</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="AH21" t="inlineStr">
         <is>
           <t>2026-08-31T11:57:38+07:00</t>
         </is>
@@ -31271,13 +31862,13 @@
         <v>177303.877</v>
       </c>
       <c r="I22" t="n">
+        <v>181901.791</v>
+      </c>
+      <c r="J22" t="n">
+        <v>102.593</v>
+      </c>
+      <c r="K22" t="n">
         <v>50842.748</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>7930.371999999999</v>
@@ -31286,25 +31877,61 @@
         <v>2.902</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.902</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.902</v>
       </c>
       <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>276301.578</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>109.412</v>
+      </c>
+      <c r="T22" t="n">
+        <v>91.39700000000001</v>
+      </c>
+      <c r="U22" t="n">
         <v>2.868</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_EIB_-_BCTC_hop_nhat_nam_2025_da_kiem_toan_1774925122.pdf</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="AH22" t="inlineStr">
         <is>
           <t>2026-08-31T01:16:37+07:00</t>
         </is>
@@ -31326,7 +31953,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="AH23" t="inlineStr">
         <is>
           <t>2026-08-31T10:08:58+07:00</t>
         </is>
@@ -31348,7 +31975,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="AH24" t="inlineStr">
         <is>
           <t>2026-08-31T12:01:17+07:00</t>
         </is>
@@ -31370,7 +31997,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="AH25" t="inlineStr">
         <is>
           <t>2026-08-31T01:18:56+07:00</t>
         </is>
@@ -31405,13 +32032,13 @@
         <v>70989.97199999999</v>
       </c>
       <c r="I26" t="n">
+        <v>66941.239</v>
+      </c>
+      <c r="J26" t="n">
+        <v>94.297</v>
+      </c>
+      <c r="K26" t="n">
         <v>18386.133</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>-3996.194</v>
@@ -31420,25 +32047,61 @@
         <v>-4.113</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>-6.805</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>-8.526</v>
       </c>
       <c r="P26" t="n">
+        <v>104163.524</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>26868.875</v>
+      </c>
+      <c r="R26" t="n">
+        <v>387.674</v>
+      </c>
+      <c r="S26" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="T26" t="n">
+        <v>234.304</v>
+      </c>
+      <c r="U26" t="n">
         <v>2.59</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014864567_VI_BAO_CAO_TAI_CHINH_QUY_I_06052025105844.2025_HOP_NHAT</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="AH26" t="inlineStr">
         <is>
           <t>2026-08-31T10:10:19+07:00</t>
         </is>
@@ -31473,13 +32136,13 @@
         <v>73173.554</v>
       </c>
       <c r="I27" t="n">
+        <v>68416.125</v>
+      </c>
+      <c r="J27" t="n">
+        <v>93.498</v>
+      </c>
+      <c r="K27" t="n">
         <v>17449.438</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>33012.88</v>
@@ -31488,25 +32151,61 @@
         <v>33.814</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>51.74</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>91.782</v>
       </c>
       <c r="P27" t="n">
+        <v>89484.34</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>110077.689</v>
+      </c>
+      <c r="R27" t="n">
+        <v>81.292</v>
+      </c>
+      <c r="S27" t="n">
+        <v>89.99299999999999</v>
+      </c>
+      <c r="T27" t="n">
+        <v>111.12</v>
+      </c>
+      <c r="U27" t="n">
         <v>2.385</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-kin-long28082025-000000bo-co-ti-chnh-bn-nin-2025_1_0929.pdf</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="AH27" t="inlineStr">
         <is>
           <t>2026-08-31T12:03:05+07:00</t>
         </is>
@@ -31541,13 +32240,13 @@
         <v>72010.409</v>
       </c>
       <c r="I28" t="n">
+        <v>70413.492</v>
+      </c>
+      <c r="J28" t="n">
+        <v>97.782</v>
+      </c>
+      <c r="K28" t="n">
         <v>22569.94</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>2230.823</v>
@@ -31556,25 +32255,61 @@
         <v>2.16</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.141</v>
       </c>
       <c r="P28" t="n">
+        <v>91470.00999999999</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>114585.831</v>
+      </c>
+      <c r="R28" t="n">
+        <v>79.827</v>
+      </c>
+      <c r="S28" t="n">
+        <v>93.134</v>
+      </c>
+      <c r="T28" t="n">
+        <v>107.372</v>
+      </c>
+      <c r="U28" t="n">
         <v>3.134</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_KLB_-_BCTC_KiemToan_2025_Hop_nhat_1774928715.pdf</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="AH28" t="inlineStr">
         <is>
           <t>2026-08-31T01:20:50+07:00</t>
         </is>
@@ -31596,7 +32331,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="AH29" t="inlineStr">
         <is>
           <t>2026-08-31T10:13:34+07:00</t>
         </is>
@@ -31618,7 +32353,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="AH30" t="inlineStr">
         <is>
           <t>2026-08-31T12:07:34+07:00</t>
         </is>
@@ -31640,7 +32375,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="AH31" t="inlineStr">
         <is>
           <t>2026-08-31T01:22:06+07:00</t>
         </is>
@@ -31675,13 +32410,13 @@
         <v>722622.45</v>
       </c>
       <c r="I32" t="n">
+        <v>786486.9790000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>108.838</v>
+      </c>
+      <c r="K32" t="n">
         <v>84084.52099999999</v>
-      </c>
-      <c r="J32" t="n">
-        <v>7749.506</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.67</v>
       </c>
       <c r="L32" t="n">
         <v>183923.188</v>
@@ -31690,25 +32425,61 @@
         <v>15.898</v>
       </c>
       <c r="N32" t="n">
+        <v>29.941</v>
+      </c>
+      <c r="O32" t="n">
+        <v>30.821</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1028104.739</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>430822.448</v>
+      </c>
+      <c r="R32" t="n">
+        <v>238.638</v>
+      </c>
+      <c r="S32" t="n">
+        <v>42.936</v>
+      </c>
+      <c r="T32" t="n">
+        <v>232.902</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="V32" t="n">
+        <v>7749.506</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AC32" t="n">
         <v>65</v>
       </c>
-      <c r="O32" t="n">
+      <c r="AD32" t="n">
         <v>0.556</v>
       </c>
-      <c r="P32" t="n">
-        <v>1.164</v>
-      </c>
-      <c r="Q32" t="inlineStr">
+      <c r="AE32" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00012345679012345679ngn-hng-tmcp-qun-i24042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="AH32" t="inlineStr">
         <is>
           <t>2026-08-31T10:15:17+07:00</t>
         </is>
@@ -31743,40 +32514,61 @@
         <v>783291.9080000001</v>
       </c>
       <c r="I33" t="n">
+        <v>867340.209</v>
+      </c>
+      <c r="J33" t="n">
+        <v>110.73</v>
+      </c>
+      <c r="K33" t="n">
         <v>116595.397</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.489</v>
+      </c>
+      <c r="V33" t="n">
         <v>40113.92999999999</v>
       </c>
-      <c r="K33" t="n">
+      <c r="W33" t="n">
+        <v>-13.994</v>
+      </c>
+      <c r="X33" t="n">
+        <v>-0.129</v>
+      </c>
+      <c r="Y33" t="n">
         <v>3.11</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="AC33" t="n">
         <v>-27</v>
       </c>
-      <c r="O33" t="n">
+      <c r="AD33" t="n">
         <v>-0.218</v>
       </c>
-      <c r="P33" t="n">
-        <v>1.489</v>
-      </c>
-      <c r="Q33" t="inlineStr">
+      <c r="AE33" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="AF33" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MBB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025091521.pdf</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="AH33" t="inlineStr">
         <is>
           <t>2026-08-31T12:10:05+07:00</t>
         </is>
@@ -31811,13 +32603,13 @@
         <v>921368.132</v>
       </c>
       <c r="I34" t="n">
+        <v>1070868.777</v>
+      </c>
+      <c r="J34" t="n">
+        <v>116.226</v>
+      </c>
+      <c r="K34" t="n">
         <v>256383.938</v>
-      </c>
-      <c r="J34" t="n">
-        <v>-119953.924</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-7.424</v>
       </c>
       <c r="L34" t="n">
         <v>-338533.023</v>
@@ -31826,25 +32618,61 @@
         <v>-20.952</v>
       </c>
       <c r="N34" t="n">
+        <v>-20.942</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-20.941</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-338524.137</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6161.861</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-5493.862</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2401.255</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4.164</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="V34" t="n">
+        <v>-119953.924</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-12.629</v>
+      </c>
+      <c r="X34" t="n">
+        <v>-12.579</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>-7.424</v>
+      </c>
+      <c r="AC34" t="n">
         <v>-1506</v>
       </c>
-      <c r="O34" t="n">
+      <c r="AD34" t="n">
         <v>-10.347</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.783</v>
-      </c>
-      <c r="Q34" t="inlineStr">
+      <c r="AE34" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AF34" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MBB_Baocaotaichinh_2025_Kiemtoan_Hopnhat_1780022210.pdf</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="AH34" t="inlineStr">
         <is>
           <t>2026-08-31T01:24:23+07:00</t>
         </is>
@@ -31879,13 +32707,13 @@
         <v>163035.139</v>
       </c>
       <c r="I35" t="n">
+        <v>189399.835</v>
+      </c>
+      <c r="J35" t="n">
+        <v>116.171</v>
+      </c>
+      <c r="K35" t="n">
         <v>53049.641</v>
-      </c>
-      <c r="J35" t="n">
-        <v>-16352.815</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-5.196</v>
       </c>
       <c r="L35" t="n">
         <v>-71627.23299999999</v>
@@ -31894,25 +32722,61 @@
         <v>-22.759</v>
       </c>
       <c r="N35" t="n">
+        <v>-25.233</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-24.502</v>
+      </c>
+      <c r="P35" t="n">
+        <v>276686.358</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>394789.834</v>
+      </c>
+      <c r="R35" t="n">
+        <v>70.084</v>
+      </c>
+      <c r="S35" t="n">
+        <v>79.72499999999999</v>
+      </c>
+      <c r="T35" t="n">
+        <v>125.431</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.254</v>
+      </c>
+      <c r="V35" t="n">
+        <v>-16352.815</v>
+      </c>
+      <c r="W35" t="n">
+        <v>-17.398</v>
+      </c>
+      <c r="X35" t="n">
+        <v>-10.814</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>-5.196</v>
+      </c>
+      <c r="AC35" t="n">
         <v>-257</v>
       </c>
-      <c r="O35" t="n">
+      <c r="AD35" t="n">
         <v>-10.264</v>
       </c>
-      <c r="P35" t="n">
-        <v>3.254</v>
-      </c>
-      <c r="Q35" t="inlineStr">
+      <c r="AE35" t="n">
+        <v>-0.676</v>
+      </c>
+      <c r="AF35" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-hng-hi-vit-nam28042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="AH35" t="inlineStr">
         <is>
           <t>2026-08-31T10:17:02+07:00</t>
         </is>
@@ -31947,13 +32811,13 @@
         <v>174429.9</v>
       </c>
       <c r="I36" t="n">
+        <v>197740.711</v>
+      </c>
+      <c r="J36" t="n">
+        <v>113.364</v>
+      </c>
+      <c r="K36" t="n">
         <v>64784.029</v>
-      </c>
-      <c r="J36" t="n">
-        <v>88375.88399999999</v>
-      </c>
-      <c r="K36" t="n">
-        <v>25.892</v>
       </c>
       <c r="L36" t="n">
         <v>-78086.85799999999</v>
@@ -31962,25 +32826,61 @@
         <v>-22.877</v>
       </c>
       <c r="N36" t="n">
+        <v>-22.572</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-23.29</v>
+      </c>
+      <c r="P36" t="n">
+        <v>159661.452</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>199526.501</v>
+      </c>
+      <c r="R36" t="n">
+        <v>80.02</v>
+      </c>
+      <c r="S36" t="n">
+        <v>59.974</v>
+      </c>
+      <c r="T36" t="n">
+        <v>166.74</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.714</v>
+      </c>
+      <c r="V36" t="n">
+        <v>88375.88399999999</v>
+      </c>
+      <c r="W36" t="n">
+        <v>14.654</v>
+      </c>
+      <c r="X36" t="n">
+        <v>23.289</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>25.892</v>
+      </c>
+      <c r="AC36" t="n">
         <v>774</v>
       </c>
-      <c r="O36" t="n">
+      <c r="AD36" t="n">
         <v>29.944</v>
       </c>
-      <c r="P36" t="n">
-        <v>3.714</v>
-      </c>
-      <c r="Q36" t="inlineStr">
+      <c r="AE36" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MSB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025092910.pdf</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="AH36" t="inlineStr">
         <is>
           <t>2026-08-31T12:12:00+07:00</t>
         </is>
@@ -32015,13 +32915,13 @@
         <v>196671.626</v>
       </c>
       <c r="I37" t="n">
+        <v>202358.24</v>
+      </c>
+      <c r="J37" t="n">
+        <v>102.891</v>
+      </c>
+      <c r="K37" t="n">
         <v>85247.459</v>
-      </c>
-      <c r="J37" t="n">
-        <v>-36336.335</v>
-      </c>
-      <c r="K37" t="n">
-        <v>-8.913</v>
       </c>
       <c r="L37" t="n">
         <v>-94852.075</v>
@@ -32030,25 +32930,61 @@
         <v>-23.267</v>
       </c>
       <c r="N37" t="n">
+        <v>-24.07</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-24.069</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-95923.317</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>58081.342</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-165.153</v>
+      </c>
+      <c r="S37" t="n">
+        <v>74.715</v>
+      </c>
+      <c r="T37" t="n">
+        <v>133.841</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="V37" t="n">
+        <v>-36336.335</v>
+      </c>
+      <c r="W37" t="n">
+        <v>7.502</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-12.367</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-8.913</v>
+      </c>
+      <c r="AC37" t="n">
         <v>-330</v>
       </c>
-      <c r="O37" t="n">
+      <c r="AD37" t="n">
         <v>-10.843</v>
       </c>
-      <c r="P37" t="n">
-        <v>4.335</v>
-      </c>
-      <c r="Q37" t="inlineStr">
+      <c r="AE37" t="n">
+        <v>-0.777</v>
+      </c>
+      <c r="AF37" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MSB_HK_20260330_-_MSB_-_BCTC_hop_nhat_kiem_toan_nam_2025__18062026110209.pdf</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="AH37" t="inlineStr">
         <is>
           <t>2026-08-31T01:26:11+07:00</t>
         </is>
@@ -32083,13 +33019,13 @@
         <v>176385.625</v>
       </c>
       <c r="I38" t="n">
+        <v>175538.745</v>
+      </c>
+      <c r="J38" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="K38" t="n">
         <v>53623.62</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1044.137999999998</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.398</v>
       </c>
       <c r="L38" t="n">
         <v>-26051.455</v>
@@ -32098,25 +33034,61 @@
         <v>-9.933999999999999</v>
       </c>
       <c r="N38" t="n">
+        <v>-15.63</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-22.381</v>
+      </c>
+      <c r="P38" t="n">
+        <v>91004.68700000001</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>83359.379</v>
+      </c>
+      <c r="R38" t="n">
+        <v>109.172</v>
+      </c>
+      <c r="S38" t="n">
+        <v>26.663</v>
+      </c>
+      <c r="T38" t="n">
+        <v>375.058</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1044.137999999998</v>
+      </c>
+      <c r="W38" t="n">
+        <v>-0.302</v>
+      </c>
+      <c r="X38" t="n">
+        <v>20.497</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="AC38" t="n">
         <v>224</v>
       </c>
-      <c r="O38" t="n">
+      <c r="AD38" t="n">
         <v>10.605</v>
       </c>
-      <c r="P38" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Q38" t="inlineStr">
+      <c r="AE38" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-nam-28042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="AH38" t="inlineStr">
         <is>
           <t>2026-08-31T10:18:34+07:00</t>
         </is>
@@ -32151,13 +33123,13 @@
         <v>196932.046</v>
       </c>
       <c r="I39" t="n">
+        <v>190329.454</v>
+      </c>
+      <c r="J39" t="n">
+        <v>96.64700000000001</v>
+      </c>
+      <c r="K39" t="n">
         <v>88326.624</v>
-      </c>
-      <c r="J39" t="n">
-        <v>-7342.066000000001</v>
-      </c>
-      <c r="K39" t="n">
-        <v>-2.332</v>
       </c>
       <c r="L39" t="n">
         <v>-12907.955</v>
@@ -32166,25 +33138,61 @@
         <v>-4.1</v>
       </c>
       <c r="N39" t="n">
+        <v>-10.602</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-19.04</v>
+      </c>
+      <c r="P39" t="n">
+        <v>290582.199</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>380985.584</v>
+      </c>
+      <c r="R39" t="n">
+        <v>76.271</v>
+      </c>
+      <c r="S39" t="n">
+        <v>83.40900000000001</v>
+      </c>
+      <c r="T39" t="n">
+        <v>119.891</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4.485</v>
+      </c>
+      <c r="V39" t="n">
+        <v>-7342.066000000001</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X39" t="n">
+        <v>14.227</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>-2.332</v>
+      </c>
+      <c r="AC39" t="n">
         <v>140</v>
       </c>
-      <c r="O39" t="n">
+      <c r="AD39" t="n">
         <v>6.597</v>
       </c>
-      <c r="P39" t="n">
-        <v>4.485</v>
-      </c>
-      <c r="Q39" t="inlineStr">
+      <c r="AE39" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="AF39" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NAB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025093916.pdf</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="AH39" t="inlineStr">
         <is>
           <t>2026-08-31T12:14:18+07:00</t>
         </is>
@@ -32219,13 +33227,13 @@
         <v>177810.693</v>
       </c>
       <c r="I40" t="n">
+        <v>195333.034</v>
+      </c>
+      <c r="J40" t="n">
+        <v>109.854</v>
+      </c>
+      <c r="K40" t="n">
         <v>170154.001</v>
-      </c>
-      <c r="J40" t="n">
-        <v>506013.917</v>
-      </c>
-      <c r="K40" t="n">
-        <v>120.96</v>
       </c>
       <c r="L40" t="n">
         <v>206015.022</v>
@@ -32234,25 +33242,61 @@
         <v>49.247</v>
       </c>
       <c r="N40" t="n">
+        <v>49.247</v>
+      </c>
+      <c r="O40" t="n">
+        <v>66.14100000000001</v>
+      </c>
+      <c r="P40" t="n">
+        <v>370449.062</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>118214.803</v>
+      </c>
+      <c r="R40" t="n">
+        <v>313.369</v>
+      </c>
+      <c r="S40" t="n">
+        <v>40.506</v>
+      </c>
+      <c r="T40" t="n">
+        <v>246.876</v>
+      </c>
+      <c r="U40" t="n">
+        <v>9.569000000000001</v>
+      </c>
+      <c r="V40" t="n">
+        <v>506013.917</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.513</v>
+      </c>
+      <c r="X40" t="n">
+        <v>17.344</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>120.96</v>
+      </c>
+      <c r="AC40" t="n">
         <v>1841</v>
       </c>
-      <c r="O40" t="n">
+      <c r="AD40" t="n">
         <v>79.096</v>
       </c>
-      <c r="P40" t="n">
-        <v>9.569000000000001</v>
-      </c>
-      <c r="Q40" t="inlineStr">
+      <c r="AE40" t="n">
+        <v>7.857</v>
+      </c>
+      <c r="AF40" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NAB_Baocaotaichinh_2025_Kiemtoan_Hopnhat_1780023595.pdf</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="AH40" t="inlineStr">
         <is>
           <t>2026-08-31T01:28:37+07:00</t>
         </is>
@@ -32287,13 +33331,13 @@
         <v>102527.917</v>
       </c>
       <c r="I41" t="n">
+        <v>76816.268</v>
+      </c>
+      <c r="J41" t="n">
+        <v>74.922</v>
+      </c>
+      <c r="K41" t="n">
         <v>21312.588</v>
-      </c>
-      <c r="J41" t="n">
-        <v>4928.864</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3.766</v>
       </c>
       <c r="L41" t="n">
         <v>-4695.431</v>
@@ -32302,25 +33346,61 @@
         <v>-3.588</v>
       </c>
       <c r="N41" t="n">
+        <v>-9.178000000000001</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-15.711</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-11315.656</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>22019.159</v>
+      </c>
+      <c r="R41" t="n">
+        <v>-51.39</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-8.853999999999999</v>
+      </c>
+      <c r="T41" t="n">
+        <v>-1129.444</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.079</v>
+      </c>
+      <c r="V41" t="n">
+        <v>4928.864</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="X41" t="n">
+        <v>19.343</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>3.766</v>
+      </c>
+      <c r="AC41" t="n">
         <v>102</v>
       </c>
-      <c r="O41" t="n">
+      <c r="AD41" t="n">
         <v>20.204</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.079</v>
-      </c>
-      <c r="Q41" t="inlineStr">
+      <c r="AE41" t="n">
+        <v>1.634</v>
+      </c>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NVB_25Q1_BCTC_HN_09052025064513.pdf</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="AH41" t="inlineStr">
         <is>
           <t>2026-08-31T10:20:53+07:00</t>
         </is>
@@ -32355,40 +33435,61 @@
         <v>115244.771</v>
       </c>
       <c r="I42" t="n">
+        <v>85556.842</v>
+      </c>
+      <c r="J42" t="n">
+        <v>74.239</v>
+      </c>
+      <c r="K42" t="n">
         <v>25035.067</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.172</v>
+      </c>
+      <c r="V42" t="n">
         <v>-58074.064</v>
       </c>
-      <c r="K42" t="n">
+      <c r="W42" t="n">
+        <v>-2.971</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="Y42" t="n">
         <v>-40.314</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
+      <c r="AC42" t="n">
         <v>-319</v>
       </c>
-      <c r="O42" t="n">
+      <c r="AD42" t="n">
         <v>-42.102</v>
       </c>
-      <c r="P42" t="n">
-        <v>2.172</v>
-      </c>
-      <c r="Q42" t="inlineStr">
+      <c r="AE42" t="n">
+        <v>-4.866</v>
+      </c>
+      <c r="AF42" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="AG42" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-quc-dn27082025-000000bo-co-ti-chnh-bn-nin-2025_1_0915.pdf</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="AH42" t="inlineStr">
         <is>
           <t>2026-08-31T12:16:11+07:00</t>
         </is>
@@ -32423,40 +33524,61 @@
         <v>127403.437</v>
       </c>
       <c r="I43" t="n">
+        <v>96302.761</v>
+      </c>
+      <c r="J43" t="n">
+        <v>75.589</v>
+      </c>
+      <c r="K43" t="n">
         <v>38989.537</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V43" t="n">
         <v>44447.07199999999</v>
       </c>
-      <c r="K43" t="n">
+      <c r="W43" t="n">
+        <v>41.067</v>
+      </c>
+      <c r="X43" t="n">
+        <v>41.435</v>
+      </c>
+      <c r="Y43" t="n">
         <v>27.166</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
+      <c r="AC43" t="n">
         <v>682</v>
       </c>
-      <c r="O43" t="n">
+      <c r="AD43" t="n">
         <v>160.991</v>
       </c>
-      <c r="P43" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="Q43" t="inlineStr">
+      <c r="AE43" t="n">
+        <v>5.017</v>
+      </c>
+      <c r="AF43" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="AG43" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604185_Bao_cao_tai_chinh_nam_2025_1774532924.pdf</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="AH43" t="inlineStr">
         <is>
           <t>2026-08-31T01:30:26+07:00</t>
         </is>
@@ -32478,7 +33600,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="AH44" t="inlineStr">
         <is>
           <t>2026-08-31T10:23:58+07:00</t>
         </is>
@@ -32500,7 +33622,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="AH45" t="inlineStr">
         <is>
           <t>2026-08-31T12:23:24+07:00</t>
         </is>
@@ -32522,7 +33644,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="AH46" t="inlineStr">
         <is>
           <t>2026-08-31T01:30:30+07:00</t>
         </is>
@@ -32557,40 +33679,61 @@
         <v>46717.488</v>
       </c>
       <c r="I47" t="n">
+        <v>44869.685</v>
+      </c>
+      <c r="J47" t="n">
+        <v>96.045</v>
+      </c>
+      <c r="K47" t="n">
         <v>22839.31</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4.889</v>
+      </c>
+      <c r="V47" t="n">
         <v>4980.354</v>
       </c>
-      <c r="K47" t="n">
+      <c r="W47" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="Y47" t="n">
         <v>6.771</v>
       </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
+      <c r="AC47" t="n">
         <v>35</v>
       </c>
-      <c r="O47" t="n">
+      <c r="AD47" t="n">
         <v>7.637</v>
       </c>
-      <c r="P47" t="n">
-        <v>4.889</v>
-      </c>
-      <c r="Q47" t="inlineStr">
+      <c r="AE47" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="AG47" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-2/2025-04-18/no-name-1744937049.pdf</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="AH47" t="inlineStr">
         <is>
           <t>2026-08-31T10:25:19+07:00</t>
         </is>
@@ -32625,13 +33768,13 @@
         <v>46726.281</v>
       </c>
       <c r="I48" t="n">
+        <v>44897.652</v>
+      </c>
+      <c r="J48" t="n">
+        <v>96.087</v>
+      </c>
+      <c r="K48" t="n">
         <v>24930.12</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1419.186</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1.807</v>
       </c>
       <c r="L48" t="n">
         <v>-3100.088</v>
@@ -32640,25 +33783,61 @@
         <v>-3.947</v>
       </c>
       <c r="N48" t="n">
+        <v>-10.264</v>
+      </c>
+      <c r="O48" t="n">
+        <v>-10.259</v>
+      </c>
+      <c r="P48" t="n">
+        <v>27412.477</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>30537.859</v>
+      </c>
+      <c r="R48" t="n">
+        <v>89.76600000000001</v>
+      </c>
+      <c r="S48" t="n">
+        <v>61.336</v>
+      </c>
+      <c r="T48" t="n">
+        <v>163.036</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5.335</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1419.186</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.807</v>
+      </c>
+      <c r="AC48" t="n">
         <v>4</v>
       </c>
-      <c r="O48" t="n">
+      <c r="AD48" t="n">
         <v>0.848</v>
       </c>
-      <c r="P48" t="n">
-        <v>5.335</v>
-      </c>
-      <c r="Q48" t="inlineStr">
+      <c r="AE48" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AF48" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 2 năm 2025</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="AG48" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-08-19/no-name-1755541972.pdf</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="AH48" t="inlineStr">
         <is>
           <t>2026-08-31T12:25:04+07:00</t>
         </is>
@@ -32693,13 +33872,13 @@
         <v>48460.417</v>
       </c>
       <c r="I49" t="n">
+        <v>45781.147</v>
+      </c>
+      <c r="J49" t="n">
+        <v>94.471</v>
+      </c>
+      <c r="K49" t="n">
         <v>31153.789</v>
-      </c>
-      <c r="J49" t="n">
-        <v>-448.7119999999998</v>
-      </c>
-      <c r="K49" t="n">
-        <v>-0.505</v>
       </c>
       <c r="L49" t="n">
         <v>-7944.858999999999</v>
@@ -32708,25 +33887,61 @@
         <v>-8.943</v>
       </c>
       <c r="N49" t="n">
+        <v>-7.796</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-11.351</v>
+      </c>
+      <c r="P49" t="n">
+        <v>477294.919</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>10940.595</v>
+      </c>
+      <c r="R49" t="n">
+        <v>4362.605</v>
+      </c>
+      <c r="S49" t="n">
+        <v>83.438</v>
+      </c>
+      <c r="T49" t="n">
+        <v>119.849</v>
+      </c>
+      <c r="U49" t="n">
+        <v>6.429</v>
+      </c>
+      <c r="V49" t="n">
+        <v>-448.7119999999998</v>
+      </c>
+      <c r="W49" t="n">
+        <v>-8.398</v>
+      </c>
+      <c r="X49" t="n">
+        <v>-0.622</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>-0.505</v>
+      </c>
+      <c r="AC49" t="n">
         <v>-20</v>
       </c>
-      <c r="O49" t="n">
+      <c r="AD49" t="n">
         <v>-4.151</v>
       </c>
-      <c r="P49" t="n">
-        <v>6.429</v>
-      </c>
-      <c r="Q49" t="inlineStr">
+      <c r="AE49" t="n">
+        <v>-0.306</v>
+      </c>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="AG49" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-02/no-name-1775069400.pdf</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="AH49" t="inlineStr">
         <is>
           <t>2026-08-31T01:31:51+07:00</t>
         </is>
@@ -32761,13 +33976,13 @@
         <v>24539.598</v>
       </c>
       <c r="I50" t="n">
+        <v>20683.652</v>
+      </c>
+      <c r="J50" t="n">
+        <v>84.28700000000001</v>
+      </c>
+      <c r="K50" t="n">
         <v>9035.235999999999</v>
-      </c>
-      <c r="J50" t="n">
-        <v>-8415.234</v>
-      </c>
-      <c r="K50" t="n">
-        <v>-25.115</v>
       </c>
       <c r="L50" t="n">
         <v>5121.561</v>
@@ -32776,25 +33991,46 @@
         <v>15.285</v>
       </c>
       <c r="N50" t="n">
+        <v>22.732</v>
+      </c>
+      <c r="O50" t="n">
+        <v>45.463</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3.682</v>
+      </c>
+      <c r="V50" t="n">
+        <v>-8415.234</v>
+      </c>
+      <c r="W50" t="n">
+        <v>-5.98</v>
+      </c>
+      <c r="X50" t="n">
+        <v>-26.824</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>-25.115</v>
+      </c>
+      <c r="AC50" t="n">
         <v>-102</v>
       </c>
-      <c r="O50" t="n">
+      <c r="AD50" t="n">
         <v>-46.819</v>
       </c>
-      <c r="P50" t="n">
-        <v>3.682</v>
-      </c>
-      <c r="Q50" t="inlineStr">
+      <c r="AE50" t="n">
+        <v>-2.445</v>
+      </c>
+      <c r="AF50" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="AG50" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014834796_VI_BaoCaotaiChinh_HopNhat_Q1_2025_26042025110134.pdf</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="AH50" t="inlineStr">
         <is>
           <t>2026-08-31T10:26:54+07:00</t>
         </is>
@@ -32829,13 +34065,13 @@
         <v>25595.19</v>
       </c>
       <c r="I51" t="n">
+        <v>20050.378</v>
+      </c>
+      <c r="J51" t="n">
+        <v>78.337</v>
+      </c>
+      <c r="K51" t="n">
         <v>10508.501</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1423.367</v>
-      </c>
-      <c r="K51" t="n">
-        <v>4.05</v>
       </c>
       <c r="L51" t="n">
         <v>1633.754</v>
@@ -32844,25 +34080,61 @@
         <v>4.649</v>
       </c>
       <c r="N51" t="n">
+        <v>17.592</v>
+      </c>
+      <c r="O51" t="n">
+        <v>46.83</v>
+      </c>
+      <c r="P51" t="n">
+        <v>37088.709</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>36477.346</v>
+      </c>
+      <c r="R51" t="n">
+        <v>101.676</v>
+      </c>
+      <c r="S51" t="n">
+        <v>57.343</v>
+      </c>
+      <c r="T51" t="n">
+        <v>174.388</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4.106</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1423.367</v>
+      </c>
+      <c r="W51" t="n">
+        <v>4.526</v>
+      </c>
+      <c r="X51" t="n">
+        <v>-0.509</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AC51" t="n">
         <v>-14</v>
       </c>
-      <c r="O51" t="n">
+      <c r="AD51" t="n">
         <v>-5.998</v>
       </c>
-      <c r="P51" t="n">
-        <v>4.106</v>
-      </c>
-      <c r="Q51" t="inlineStr">
+      <c r="AE51" t="n">
+        <v>-0.331</v>
+      </c>
+      <c r="AF51" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="AG51" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00019753086419753087ngn-hng-tmcp-si-gn-cng-thng14082025-000000bo-co-ti-chnh-bn-nin-2025_1_1022.pdf</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="AH51" t="inlineStr">
         <is>
           <t>2026-08-31T12:26:51+07:00</t>
         </is>
@@ -32897,13 +34169,13 @@
         <v>26326.61</v>
       </c>
       <c r="I52" t="n">
+        <v>21736.612</v>
+      </c>
+      <c r="J52" t="n">
+        <v>82.565</v>
+      </c>
+      <c r="K52" t="n">
         <v>9373.537</v>
-      </c>
-      <c r="J52" t="n">
-        <v>3391.897</v>
-      </c>
-      <c r="K52" t="n">
-        <v>9.587999999999999</v>
       </c>
       <c r="L52" t="n">
         <v>838.0600000000001</v>
@@ -32912,25 +34184,46 @@
         <v>2.369</v>
       </c>
       <c r="N52" t="n">
+        <v>-1.011</v>
+      </c>
+      <c r="O52" t="n">
+        <v>-10.746</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="V52" t="n">
+        <v>3391.897</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="X52" t="n">
+        <v>-2.329</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>9.587999999999999</v>
+      </c>
+      <c r="AC52" t="n">
         <v>-7</v>
       </c>
-      <c r="O52" t="n">
+      <c r="AD52" t="n">
         <v>-10.615</v>
       </c>
-      <c r="P52" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="Q52" t="inlineStr">
+      <c r="AE52" t="n">
+        <v>-0.167</v>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="AG52" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604675_Bao_cao_tai_chinh_nam_2025_1776046299.pdf</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="AH52" t="inlineStr">
         <is>
           <t>2026-08-31T01:33:44+07:00</t>
         </is>
@@ -32952,7 +34245,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="AH53" t="inlineStr">
         <is>
           <t>2026-08-31T10:28:16+07:00</t>
         </is>
@@ -32987,13 +34280,13 @@
         <v>561718.311</v>
       </c>
       <c r="I54" t="n">
+        <v>584806.6360000001</v>
+      </c>
+      <c r="J54" t="n">
+        <v>104.11</v>
+      </c>
+      <c r="K54" t="n">
         <v>139362.736</v>
-      </c>
-      <c r="J54" t="n">
-        <v>101052.076</v>
-      </c>
-      <c r="K54" t="n">
-        <v>12.238</v>
       </c>
       <c r="L54" t="n">
         <v>7001.849</v>
@@ -33002,25 +34295,61 @@
         <v>0.848</v>
       </c>
       <c r="N54" t="n">
+        <v>-3.937</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-11.95</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-16796.302</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>320985.483</v>
+      </c>
+      <c r="R54" t="n">
+        <v>-5.233</v>
+      </c>
+      <c r="S54" t="n">
+        <v>66.04300000000001</v>
+      </c>
+      <c r="T54" t="n">
+        <v>151.417</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2.481</v>
+      </c>
+      <c r="V54" t="n">
+        <v>101052.076</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>12.238</v>
+      </c>
+      <c r="AC54" t="n">
         <v>1186</v>
       </c>
-      <c r="O54" t="n">
+      <c r="AD54" t="n">
         <v>12.948</v>
       </c>
-      <c r="P54" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="Q54" t="inlineStr">
+      <c r="AE54" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AF54" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="AG54" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250903_-_SHB_-_Bao_Cao_Tai_Chinh_Hop_Nhat_Soat_Xet_Ban_nien_30.6.2025_1756910753.pdf</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="AH54" t="inlineStr">
         <is>
           <t>2026-08-31T12:28:17+07:00</t>
         </is>
@@ -33042,7 +34371,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="AH55" t="inlineStr">
         <is>
           <t>2026-08-31T01:34:56+07:00</t>
         </is>
@@ -33077,13 +34406,13 @@
         <v>160043.132</v>
       </c>
       <c r="I56" t="n">
+        <v>209845.503</v>
+      </c>
+      <c r="J56" t="n">
+        <v>131.118</v>
+      </c>
+      <c r="K56" t="n">
         <v>83940.10000000001</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>24719.945</v>
@@ -33092,25 +34421,61 @@
         <v>7.407</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>9.519</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>-2.311</v>
       </c>
       <c r="P56" t="n">
+        <v>83.80500000000001</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>176395.92</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="S56" t="n">
+        <v>114.404</v>
+      </c>
+      <c r="T56" t="n">
+        <v>87.41</v>
+      </c>
+      <c r="U56" t="n">
         <v>5.245</v>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="AG56" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SSB_23052025144847.pdf</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="AH56" t="inlineStr">
         <is>
           <t>2026-08-31T10:31:02+07:00</t>
         </is>
@@ -33145,13 +34510,13 @@
         <v>166648.051</v>
       </c>
       <c r="I57" t="n">
+        <v>217398.122</v>
+      </c>
+      <c r="J57" t="n">
+        <v>130.453</v>
+      </c>
+      <c r="K57" t="n">
         <v>117396.389</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>26000.343</v>
@@ -33160,25 +34525,46 @@
         <v>6.86</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.419</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
+        <v>-1.845</v>
+      </c>
+      <c r="U57" t="n">
         <v>7.045</v>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="AG57" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250905_-_SSB_-_Bao_cao_tai_chinh_hop_nhat_soat_xet_ban_nien_2025_va_Giai_trinh_bien_dong_LNST_signed_1757323427.pdf</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="AH57" t="inlineStr">
         <is>
           <t>2026-08-31T12:30:19+07:00</t>
         </is>
@@ -33213,13 +34599,13 @@
         <v>191807.215</v>
       </c>
       <c r="I58" t="n">
+        <v>233780.41</v>
+      </c>
+      <c r="J58" t="n">
+        <v>121.883</v>
+      </c>
+      <c r="K58" t="n">
         <v>116960.044</v>
-      </c>
-      <c r="J58" t="n">
-        <v>25542.62000000001</v>
-      </c>
-      <c r="K58" t="n">
-        <v>6.443</v>
       </c>
       <c r="L58" t="n">
         <v>1371.248</v>
@@ -33228,25 +34614,61 @@
         <v>0.346</v>
       </c>
       <c r="N58" t="n">
+        <v>5.467</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1049.962</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>8485.277</v>
+      </c>
+      <c r="R58" t="n">
+        <v>12.374</v>
+      </c>
+      <c r="S58" t="n">
+        <v>601.513</v>
+      </c>
+      <c r="T58" t="n">
+        <v>16.625</v>
+      </c>
+      <c r="U58" t="n">
+        <v>6.098</v>
+      </c>
+      <c r="V58" t="n">
+        <v>25542.62000000001</v>
+      </c>
+      <c r="W58" t="n">
+        <v>16.854</v>
+      </c>
+      <c r="X58" t="n">
+        <v>20.183</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>6.443</v>
+      </c>
+      <c r="AC58" t="n">
         <v>568</v>
       </c>
-      <c r="O58" t="n">
+      <c r="AD58" t="n">
         <v>23.166</v>
       </c>
-      <c r="P58" t="n">
-        <v>6.098</v>
-      </c>
-      <c r="Q58" t="inlineStr">
+      <c r="AE58" t="n">
+        <v>1.407</v>
+      </c>
+      <c r="AF58" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="AG58" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260312_-_SSB_-_BCTC_hop_nhat_kiem_toan_nam_2025_kem_Giai_trinh_bien_dong_LNST_signed_1773310402.pdf</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="AH58" t="inlineStr">
         <is>
           <t>2026-08-31T01:36:28+07:00</t>
         </is>
@@ -33281,13 +34703,13 @@
         <v>585569.336</v>
       </c>
       <c r="I59" t="n">
+        <v>553760.8419999999</v>
+      </c>
+      <c r="J59" t="n">
+        <v>94.568</v>
+      </c>
+      <c r="K59" t="n">
         <v>100730.034</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>8816.550999999999</v>
@@ -33296,25 +34718,46 @@
         <v>1.165</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.202</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
+        <v>1.202</v>
+      </c>
+      <c r="U59" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="AG59" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-si-gn-thng-tn26042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="AH59" t="inlineStr">
         <is>
           <t>2026-08-31T10:34:12+07:00</t>
         </is>
@@ -33349,13 +34792,13 @@
         <v>624314.777</v>
       </c>
       <c r="I60" t="n">
+        <v>577041.997</v>
+      </c>
+      <c r="J60" t="n">
+        <v>92.428</v>
+      </c>
+      <c r="K60" t="n">
         <v>125819.938</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>-70865.32000000001</v>
@@ -33364,25 +34807,61 @@
         <v>-8.778</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>-11.204</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>-21.918</v>
       </c>
       <c r="P60" t="n">
+        <v>747518.017</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1027194.659</v>
+      </c>
+      <c r="R60" t="n">
+        <v>72.773</v>
+      </c>
+      <c r="S60" t="n">
+        <v>80.223</v>
+      </c>
+      <c r="T60" t="n">
+        <v>124.652</v>
+      </c>
+      <c r="U60" t="n">
         <v>2.015</v>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="AG60" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/STB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025100208.pdf</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="AH60" t="inlineStr">
         <is>
           <t>2026-08-31T12:33:00+07:00</t>
         </is>
@@ -33417,13 +34896,13 @@
         <v>618341.672</v>
       </c>
       <c r="I61" t="n">
+        <v>606336.3909999999</v>
+      </c>
+      <c r="J61" t="n">
+        <v>98.05800000000001</v>
+      </c>
+      <c r="K61" t="n">
         <v>195970.826</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>-147426.407</v>
@@ -33432,25 +34911,61 @@
         <v>-16.075</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>-18.767</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>-27.515</v>
       </c>
       <c r="P61" t="n">
+        <v>854290.316</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1114189.719</v>
+      </c>
+      <c r="R61" t="n">
+        <v>76.67400000000001</v>
+      </c>
+      <c r="S61" t="n">
+        <v>82.57899999999999</v>
+      </c>
+      <c r="T61" t="n">
+        <v>121.097</v>
+      </c>
+      <c r="U61" t="n">
         <v>3.169</v>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="AG61" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_STB_-_BCTC_Hop_nhat_nam_2025_da_kiem_toan__1774863040.pdf</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="AH61" t="inlineStr">
         <is>
           <t>2026-08-31T01:38:47+07:00</t>
         </is>
@@ -33485,13 +35000,13 @@
         <v>531583.052</v>
       </c>
       <c r="I62" t="n">
+        <v>655007.208</v>
+      </c>
+      <c r="J62" t="n">
+        <v>123.218</v>
+      </c>
+      <c r="K62" t="n">
         <v>148372.369</v>
-      </c>
-      <c r="J62" t="n">
-        <v>12025.473</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1.216</v>
       </c>
       <c r="L62" t="n">
         <v>-28602.92</v>
@@ -33500,25 +35015,61 @@
         <v>-2.891</v>
       </c>
       <c r="N62" t="n">
+        <v>-6.045</v>
+      </c>
+      <c r="O62" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="P62" t="n">
+        <v>537576.323</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>492843.989</v>
+      </c>
+      <c r="R62" t="n">
+        <v>109.076</v>
+      </c>
+      <c r="S62" t="n">
+        <v>91.639</v>
+      </c>
+      <c r="T62" t="n">
+        <v>109.123</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2.791</v>
+      </c>
+      <c r="V62" t="n">
+        <v>12025.473</v>
+      </c>
+      <c r="W62" t="n">
+        <v>4.396</v>
+      </c>
+      <c r="X62" t="n">
+        <v>-6.833</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="AC62" t="n">
         <v>-470</v>
       </c>
-      <c r="O62" t="n">
+      <c r="AD62" t="n">
         <v>-5.659</v>
       </c>
-      <c r="P62" t="n">
-        <v>2.791</v>
-      </c>
-      <c r="Q62" t="inlineStr">
+      <c r="AE62" t="n">
+        <v>-0.305</v>
+      </c>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="AG62" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00001234567901234568ngn-hng-tmcp-k-thng-vit-nam21042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="AH62" t="inlineStr">
         <is>
           <t>2026-08-31T10:35:54+07:00</t>
         </is>
@@ -33553,13 +35104,13 @@
         <v>545078.843</v>
       </c>
       <c r="I63" t="n">
+        <v>700801.926</v>
+      </c>
+      <c r="J63" t="n">
+        <v>128.569</v>
+      </c>
+      <c r="K63" t="n">
         <v>132997.785</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>-64704.99100000001</v>
@@ -33568,25 +35119,61 @@
         <v>-6.236</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>-7.932</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>-2.093</v>
       </c>
       <c r="P63" t="n">
+        <v>-64704.991</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>409618.537</v>
+      </c>
+      <c r="R63" t="n">
+        <v>-15.796</v>
+      </c>
+      <c r="S63" t="n">
+        <v>92.209</v>
+      </c>
+      <c r="T63" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="U63" t="n">
         <v>2.44</v>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="AG63" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025101639.pdf</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="AH63" t="inlineStr">
         <is>
           <t>2026-08-31T12:36:30+07:00</t>
         </is>
@@ -33621,13 +35208,13 @@
         <v>618911.535</v>
       </c>
       <c r="I64" t="n">
+        <v>757118.751</v>
+      </c>
+      <c r="J64" t="n">
+        <v>122.331</v>
+      </c>
+      <c r="K64" t="n">
         <v>201481.905</v>
-      </c>
-      <c r="J64" t="n">
-        <v>-95355.82799999999</v>
-      </c>
-      <c r="K64" t="n">
-        <v>-7.997</v>
       </c>
       <c r="L64" t="n">
         <v>-31183.875</v>
@@ -33636,25 +35223,61 @@
         <v>-2.615</v>
       </c>
       <c r="N64" t="n">
+        <v>-5.35</v>
+      </c>
+      <c r="O64" t="n">
+        <v>-3.451</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-121644.354</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>732641.061</v>
+      </c>
+      <c r="R64" t="n">
+        <v>-16.604</v>
+      </c>
+      <c r="S64" t="n">
+        <v>92.86799999999999</v>
+      </c>
+      <c r="T64" t="n">
+        <v>107.68</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3.255</v>
+      </c>
+      <c r="V64" t="n">
+        <v>-95355.82799999999</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-8.385</v>
+      </c>
+      <c r="X64" t="n">
+        <v>-11</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-7.997</v>
+      </c>
+      <c r="AC64" t="n">
         <v>-1000</v>
       </c>
-      <c r="O64" t="n">
+      <c r="AD64" t="n">
         <v>-9.27</v>
       </c>
-      <c r="P64" t="n">
-        <v>3.255</v>
-      </c>
-      <c r="Q64" t="inlineStr">
+      <c r="AE64" t="n">
+        <v>-0.5570000000000001</v>
+      </c>
+      <c r="AF64" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="AG64" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260317_-_TCB_-_Techcombank-VAS-bao_cao_tai_chinh_hop_nhat-YE25_1773755161.pdf</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="AH64" t="inlineStr">
         <is>
           <t>2026-08-31T01:41:25+07:00</t>
         </is>
@@ -33676,7 +35299,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="AH65" t="inlineStr">
         <is>
           <t>2026-08-31T10:40:47+07:00</t>
         </is>
@@ -33698,7 +35321,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="AH66" t="inlineStr">
         <is>
           <t>2026-08-31T12:42:52+07:00</t>
         </is>
@@ -33733,40 +35356,61 @@
         <v>279050.251</v>
       </c>
       <c r="I67" t="n">
+        <v>302186.389</v>
+      </c>
+      <c r="J67" t="n">
+        <v>108.291</v>
+      </c>
+      <c r="K67" t="n">
         <v>125552.772</v>
       </c>
-      <c r="J67" t="n">
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>4.499</v>
+      </c>
+      <c r="V67" t="n">
         <v>1.704</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>4.499</v>
-      </c>
-      <c r="Q67" t="inlineStr">
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="AG67" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_TPB_-_BCTC_hop_nhat_2025_da_kiem_toan_kem_giai_trinh_chenh_lech_LNST_signed_1774952109.pdf</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="AH67" t="inlineStr">
         <is>
           <t>2026-08-31T01:43:30+07:00</t>
         </is>
@@ -33801,40 +35445,61 @@
         <v>93896.377376687</v>
       </c>
       <c r="I68" t="n">
+        <v>84104.940067508</v>
+      </c>
+      <c r="J68" t="n">
+        <v>89.572</v>
+      </c>
+      <c r="K68" t="n">
         <v>19187.7140786</v>
       </c>
-      <c r="J68" t="n">
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2.043</v>
+      </c>
+      <c r="V68" t="n">
         <v>26350.65</v>
       </c>
-      <c r="K68" t="n">
+      <c r="W68" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="Y68" t="n">
         <v>20.42</v>
       </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="n">
+      <c r="AC68" t="n">
         <v>167</v>
       </c>
-      <c r="O68" t="n">
+      <c r="AD68" t="n">
         <v>27.264</v>
       </c>
-      <c r="P68" t="n">
-        <v>2.043</v>
-      </c>
-      <c r="Q68" t="inlineStr">
+      <c r="AE68" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="AF68" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="AG68" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014787653_VI_BaoCaoTaiChinh_Q1_2025_18042025134138.pdf</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="AH68" t="inlineStr">
         <is>
           <t>2026-08-31T10:42:19+07:00</t>
         </is>
@@ -33856,7 +35521,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="AH69" t="inlineStr">
         <is>
           <t>2026-08-31T12:46:28+07:00</t>
         </is>
@@ -33891,13 +35556,13 @@
         <v>99079.937892602</v>
       </c>
       <c r="I70" t="n">
+        <v>87680.386166857</v>
+      </c>
+      <c r="J70" t="n">
+        <v>88.495</v>
+      </c>
+      <c r="K70" t="n">
         <v>23789.312582522</v>
-      </c>
-      <c r="J70" t="n">
-        <v>9801.561999999998</v>
-      </c>
-      <c r="K70" t="n">
-        <v>6.977</v>
       </c>
       <c r="L70" t="n">
         <v>11145.647</v>
@@ -33906,25 +35571,61 @@
         <v>7.934</v>
       </c>
       <c r="N70" t="n">
+        <v>-4.005</v>
+      </c>
+      <c r="O70" t="n">
+        <v>-6.105</v>
+      </c>
+      <c r="P70" t="n">
+        <v>57946.823</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>27306.323</v>
+      </c>
+      <c r="R70" t="n">
+        <v>212.21</v>
+      </c>
+      <c r="S70" t="n">
+        <v>63.692</v>
+      </c>
+      <c r="T70" t="n">
+        <v>157.007</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="V70" t="n">
+        <v>9801.561999999998</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-3.436</v>
+      </c>
+      <c r="X70" t="n">
+        <v>10.286</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>6.977</v>
+      </c>
+      <c r="AC70" t="n">
         <v>114</v>
       </c>
-      <c r="O70" t="n">
+      <c r="AD70" t="n">
         <v>7.088</v>
       </c>
-      <c r="P70" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="Q70" t="inlineStr">
+      <c r="AE70" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="AF70" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="AG70" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_VAB_BCTC_hop_nhat_da_kiem_toan_Nam_2025_1775054500.pdf</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="AH70" t="inlineStr">
         <is>
           <t>2026-08-31T01:45:19+07:00</t>
         </is>
@@ -33959,40 +35660,61 @@
         <v>103017.174</v>
       </c>
       <c r="I71" t="n">
+        <v>96036.461</v>
+      </c>
+      <c r="J71" t="n">
+        <v>93.224</v>
+      </c>
+      <c r="K71" t="n">
         <v>49825.872</v>
       </c>
-      <c r="J71" t="n">
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>4.837</v>
+      </c>
+      <c r="V71" t="n">
         <v>14256.841</v>
       </c>
-      <c r="K71" t="n">
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="Y71" t="n">
         <v>8.176</v>
       </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
+      <c r="AC71" t="n">
         <v>51</v>
       </c>
-      <c r="O71" t="n">
+      <c r="AD71" t="n">
         <v>7.26</v>
       </c>
-      <c r="P71" t="n">
-        <v>4.837</v>
-      </c>
-      <c r="Q71" t="inlineStr">
+      <c r="AE71" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="AF71" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="AG71" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/1_vbb_2025_5_7_121b03c_vi_baocaotaichinh_hopnhat_q1_20251_16052025112437.pdf</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="AH71" t="inlineStr">
         <is>
           <t>2026-08-31T10:44:04+07:00</t>
         </is>
@@ -34027,13 +35749,13 @@
         <v>104208.415</v>
       </c>
       <c r="I72" t="n">
+        <v>101102.34</v>
+      </c>
+      <c r="J72" t="n">
+        <v>97.01900000000001</v>
+      </c>
+      <c r="K72" t="n">
         <v>45431.683</v>
-      </c>
-      <c r="J72" t="n">
-        <v>16300.747</v>
-      </c>
-      <c r="K72" t="n">
-        <v>9.122999999999999</v>
       </c>
       <c r="L72" t="n">
         <v>-3955.115</v>
@@ -34042,25 +35764,61 @@
         <v>-2.214</v>
       </c>
       <c r="N72" t="n">
+        <v>-10.987</v>
+      </c>
+      <c r="O72" t="n">
+        <v>-13.682</v>
+      </c>
+      <c r="P72" t="n">
+        <v>-16499.427</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>44170.618</v>
+      </c>
+      <c r="R72" t="n">
+        <v>-37.354</v>
+      </c>
+      <c r="S72" t="n">
+        <v>41.556</v>
+      </c>
+      <c r="T72" t="n">
+        <v>240.636</v>
+      </c>
+      <c r="U72" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="V72" t="n">
+        <v>16300.747</v>
+      </c>
+      <c r="W72" t="n">
+        <v>3.251</v>
+      </c>
+      <c r="X72" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>9.122999999999999</v>
+      </c>
+      <c r="AC72" t="n">
         <v>143</v>
       </c>
-      <c r="O72" t="n">
+      <c r="AD72" t="n">
         <v>20.803</v>
       </c>
-      <c r="P72" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="Q72" t="inlineStr">
+      <c r="AE72" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="AF72" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="AG72" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-vit-nam-thng-tn05082025-000000bo-co-ti-chnh-bn-nin-2025_1_1517.pdf</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="AH72" t="inlineStr">
         <is>
           <t>2026-08-31T12:48:36+07:00</t>
         </is>
@@ -34095,13 +35853,13 @@
         <v>101449.573</v>
       </c>
       <c r="I73" t="n">
+        <v>103772.418</v>
+      </c>
+      <c r="J73" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="K73" t="n">
         <v>56200.61</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>-8211.225</v>
@@ -34110,25 +35868,61 @@
         <v>-4.173</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>-11.339</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>-14.915</v>
       </c>
       <c r="P73" t="n">
+        <v>154563.686</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>63929.972</v>
+      </c>
+      <c r="R73" t="n">
+        <v>241.77</v>
+      </c>
+      <c r="S73" t="n">
+        <v>50.182</v>
+      </c>
+      <c r="T73" t="n">
+        <v>199.276</v>
+      </c>
+      <c r="U73" t="n">
         <v>5.54</v>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="AG73" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_603183_Bao_cao_tai_chinh_nam_2025_1776046427.pdf</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="AH73" t="inlineStr">
         <is>
           <t>2026-08-31T01:48:14+07:00</t>
         </is>
@@ -34150,7 +35944,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="AH74" t="inlineStr">
         <is>
           <t>2026-08-31T10:46:39+07:00</t>
         </is>
@@ -34185,40 +35979,61 @@
         <v>1586682.675</v>
       </c>
       <c r="I75" t="n">
+        <v>1522462.472</v>
+      </c>
+      <c r="J75" t="n">
+        <v>95.953</v>
+      </c>
+      <c r="K75" t="n">
         <v>485017.633</v>
       </c>
-      <c r="J75" t="n">
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>3.057</v>
+      </c>
+      <c r="V75" t="n">
         <v>-43033.196</v>
       </c>
-      <c r="K75" t="n">
+      <c r="W75" t="n">
+        <v>-18.312</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="Y75" t="n">
         <v>-1.94</v>
       </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
+      <c r="AC75" t="n">
         <v>-487</v>
       </c>
-      <c r="O75" t="n">
+      <c r="AD75" t="n">
         <v>-3.439</v>
       </c>
-      <c r="P75" t="n">
-        <v>3.057</v>
-      </c>
-      <c r="Q75" t="inlineStr">
+      <c r="AE75" t="n">
+        <v>-0.228</v>
+      </c>
+      <c r="AF75" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="AG75" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025111259.pdf</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="AH75" t="inlineStr">
         <is>
           <t>2026-08-31T12:50:26+07:00</t>
         </is>
@@ -34253,40 +36068,61 @@
         <v>1672534.846</v>
       </c>
       <c r="I76" t="n">
+        <v>1648549.996</v>
+      </c>
+      <c r="J76" t="n">
+        <v>98.566</v>
+      </c>
+      <c r="K76" t="n">
         <v>575462.635</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3.441</v>
+      </c>
+      <c r="V76" t="n">
         <v>819.975</v>
       </c>
-      <c r="K76" t="n">
+      <c r="W76" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y76" t="n">
         <v>0.034</v>
       </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
+      <c r="AC76" t="n">
         <v>7</v>
       </c>
-      <c r="O76" t="n">
+      <c r="AD76" t="n">
         <v>0.043</v>
       </c>
-      <c r="P76" t="n">
-        <v>3.441</v>
-      </c>
-      <c r="Q76" t="inlineStr">
+      <c r="AE76" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AF76" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="AG76" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_VCB_-_BCTC_hop_nhat_kiem_toan_nam_2025_1774870712.pdf</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="AH76" t="inlineStr">
         <is>
           <t>2026-08-31T01:50:20+07:00</t>
         </is>
@@ -34321,40 +36157,61 @@
         <v>282298.036</v>
       </c>
       <c r="I77" t="n">
+        <v>329264.074</v>
+      </c>
+      <c r="J77" t="n">
+        <v>116.637</v>
+      </c>
+      <c r="K77" t="n">
         <v>109632.918</v>
       </c>
-      <c r="J77" t="n">
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>3.884</v>
+      </c>
+      <c r="V77" t="n">
         <v>60162.859</v>
       </c>
-      <c r="K77" t="n">
+      <c r="W77" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="X77" t="n">
+        <v>7.583</v>
+      </c>
+      <c r="Y77" t="n">
         <v>12.136</v>
       </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
+      <c r="AC77" t="n">
         <v>370</v>
       </c>
-      <c r="O77" t="n">
+      <c r="AD77" t="n">
         <v>9.901</v>
       </c>
-      <c r="P77" t="n">
-        <v>3.884</v>
-      </c>
-      <c r="Q77" t="inlineStr">
+      <c r="AE77" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="AF77" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="AG77" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-07-29/no-name-1753727617.pdf</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="AH77" t="inlineStr">
         <is>
           <t>2026-08-31T10:48:45+07:00</t>
         </is>
@@ -34389,13 +36246,13 @@
         <v>304392.951</v>
       </c>
       <c r="I78" t="n">
+        <v>351360.111</v>
+      </c>
+      <c r="J78" t="n">
+        <v>115.43</v>
+      </c>
+      <c r="K78" t="n">
         <v>104990.528</v>
-      </c>
-      <c r="J78" t="n">
-        <v>50291.15800000001</v>
-      </c>
-      <c r="K78" t="n">
-        <v>9.473000000000001</v>
       </c>
       <c r="L78" t="n">
         <v>-74107.53099999999</v>
@@ -34404,25 +36261,61 @@
         <v>-13.959</v>
       </c>
       <c r="N78" t="n">
+        <v>-4.908</v>
+      </c>
+      <c r="O78" t="n">
+        <v>-5.453</v>
+      </c>
+      <c r="P78" t="n">
+        <v>421850.679</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>125888.148</v>
+      </c>
+      <c r="R78" t="n">
+        <v>335.1</v>
+      </c>
+      <c r="S78" t="n">
+        <v>86.631</v>
+      </c>
+      <c r="T78" t="n">
+        <v>115.432</v>
+      </c>
+      <c r="U78" t="n">
+        <v>3.449</v>
+      </c>
+      <c r="V78" t="n">
+        <v>50291.15800000001</v>
+      </c>
+      <c r="W78" t="n">
+        <v>-13.959</v>
+      </c>
+      <c r="X78" t="n">
+        <v>-4.909</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>9.473000000000001</v>
+      </c>
+      <c r="AC78" t="n">
         <v>-130</v>
       </c>
-      <c r="O78" t="n">
+      <c r="AD78" t="n">
         <v>-3.276</v>
       </c>
-      <c r="P78" t="n">
-        <v>3.449</v>
-      </c>
-      <c r="Q78" t="inlineStr">
+      <c r="AE78" t="n">
+        <v>-0.298</v>
+      </c>
+      <c r="AF78" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="AG78" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-quc-t-vit-nam06082025-000000bo-co-ti-chnh-hp-nht-bn-nin_1_0929.pdf</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="AH78" t="inlineStr">
         <is>
           <t>2026-08-31T12:52:16+07:00</t>
         </is>
@@ -34457,40 +36350,61 @@
         <v>294577.661</v>
       </c>
       <c r="I79" t="n">
+        <v>377113.195</v>
+      </c>
+      <c r="J79" t="n">
+        <v>128.018</v>
+      </c>
+      <c r="K79" t="n">
         <v>116961.762</v>
       </c>
-      <c r="J79" t="n">
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="V79" t="n">
         <v>26608.905</v>
       </c>
-      <c r="K79" t="n">
+      <c r="W79" t="n">
+        <v>-17.275</v>
+      </c>
+      <c r="X79" t="n">
+        <v>-10.284</v>
+      </c>
+      <c r="Y79" t="n">
         <v>4.785</v>
       </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
+      <c r="AC79" t="n">
         <v>-278</v>
       </c>
-      <c r="O79" t="n">
+      <c r="AD79" t="n">
         <v>-6.598</v>
       </c>
-      <c r="P79" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="Q79" t="inlineStr">
+      <c r="AE79" t="n">
+        <v>-0.593</v>
+      </c>
+      <c r="AF79" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="AG79" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260302_-_VIB_-_BCTC_hop_nhat_kiem_toan_2025_1772443477.pdf</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="AH79" t="inlineStr">
         <is>
           <t>2026-08-31T01:52:28+07:00</t>
         </is>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -31280,7 +31280,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2026-08-31T10:01:27+07:00</t>
+          <t>2026-08-31T16:51:48+07:00</t>
         </is>
       </c>
     </row>
@@ -32566,12 +32566,94 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>711310.758</v>
+      </c>
+      <c r="F30" t="n">
+        <v>61032.537</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7408.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>465321.208</v>
+      </c>
+      <c r="I30" t="n">
+        <v>440468.264</v>
+      </c>
+      <c r="J30" t="n">
+        <v>94.65900000000001</v>
+      </c>
+      <c r="K30" t="n">
+        <v>148462.094</v>
+      </c>
+      <c r="L30" t="n">
+        <v>103248.139</v>
+      </c>
+      <c r="M30" t="n">
+        <v>14.515</v>
+      </c>
+      <c r="N30" t="n">
+        <v>20.753</v>
+      </c>
+      <c r="O30" t="n">
+        <v>33.588</v>
+      </c>
+      <c r="P30" t="n">
+        <v>190653.82</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>22959.914</v>
+      </c>
+      <c r="R30" t="n">
+        <v>830.377</v>
+      </c>
+      <c r="S30" t="n">
+        <v>419.939</v>
+      </c>
+      <c r="T30" t="n">
+        <v>23.813</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.191</v>
+      </c>
+      <c r="V30" t="n">
+        <v>104881.84</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-10.601</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-4.327</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14.745</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>155</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.092</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/HDB_23052025143646.pdf</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>2026-08-31T10:08:58+07:00</t>
+          <t>2026-08-31T16:53:47+07:00</t>
         </is>
       </c>
     </row>
@@ -33070,12 +33152,94 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>499894.623</v>
+      </c>
+      <c r="F38" t="n">
+        <v>45872.206</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3281.91</v>
+      </c>
+      <c r="H38" t="n">
+        <v>293154.504</v>
+      </c>
+      <c r="I38" t="n">
+        <v>347669.189</v>
+      </c>
+      <c r="J38" t="n">
+        <v>118.596</v>
+      </c>
+      <c r="K38" t="n">
+        <v>80298.76300000001</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3081.205</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-11.673</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-16.57</v>
+      </c>
+      <c r="P38" t="n">
+        <v>67604.304</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>176873.865</v>
+      </c>
+      <c r="R38" t="n">
+        <v>38.222</v>
+      </c>
+      <c r="S38" t="n">
+        <v>77.506</v>
+      </c>
+      <c r="T38" t="n">
+        <v>129.022</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.739</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-07-22/no-name-1753123076.pdf</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>2026-08-31T10:13:34+07:00</t>
+          <t>2026-08-31T16:55:44+07:00</t>
         </is>
       </c>
     </row>
@@ -34849,7 +35013,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>2026-08-31T10:23:58+07:00</t>
+          <t>2026-08-31T16:58:48+07:00</t>
         </is>
       </c>
     </row>
@@ -35694,7 +35858,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>2026-08-31T10:28:16+07:00</t>
+          <t>2026-08-31T17:00:11+07:00</t>
         </is>
       </c>
     </row>
@@ -37052,7 +37216,7 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>2026-08-31T10:40:47+07:00</t>
+          <t>2026-08-31T17:05:53+07:00</t>
         </is>
       </c>
     </row>
@@ -37825,12 +37989,94 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2109260.616</v>
+      </c>
+      <c r="F98" t="n">
+        <v>204941.834</v>
+      </c>
+      <c r="G98" t="n">
+        <v>13687.153</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1509113.389</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1433896.493</v>
+      </c>
+      <c r="J98" t="n">
+        <v>95.01600000000001</v>
+      </c>
+      <c r="K98" t="n">
+        <v>452321.798</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-461316.069</v>
+      </c>
+      <c r="M98" t="n">
+        <v>-21.871</v>
+      </c>
+      <c r="N98" t="n">
+        <v>-14.033</v>
+      </c>
+      <c r="O98" t="n">
+        <v>-11.763</v>
+      </c>
+      <c r="P98" t="n">
+        <v>1888113.608</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>502117.121</v>
+      </c>
+      <c r="R98" t="n">
+        <v>376.031</v>
+      </c>
+      <c r="S98" t="n">
+        <v>44.043</v>
+      </c>
+      <c r="T98" t="n">
+        <v>227.051</v>
+      </c>
+      <c r="U98" t="n">
+        <v>2.997</v>
+      </c>
+      <c r="V98" t="n">
+        <v>-16699.62499999997</v>
+      </c>
+      <c r="W98" t="n">
+        <v>-17.035</v>
+      </c>
+      <c r="X98" t="n">
+        <v>-2.394</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>-0.792</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>-118</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>-0.862</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_23052025150224.pdf</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>2026-08-31T10:46:39+07:00</t>
+          <t>2026-08-31T17:07:33+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -6185,6 +6185,9 @@
       <c r="J57" t="n">
         <v>-0.341</v>
       </c>
+      <c r="L57" t="n">
+        <v>382141.116</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6205,6 +6208,9 @@
       </c>
       <c r="J58" t="n">
         <v>350.3</v>
+      </c>
+      <c r="L58" t="n">
+        <v>324.1</v>
       </c>
     </row>
   </sheetData>
@@ -6218,7 +6224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ78"/>
+  <dimension ref="A1:EA78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6351,6 +6357,7 @@
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
     <col width="12" customWidth="1" min="130" max="130"/>
+    <col width="12" customWidth="1" min="131" max="131"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7004,6 +7011,11 @@
           <t>2026-08</t>
         </is>
       </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7088,6 +7100,9 @@
       <c r="P3" t="n">
         <v>52.9</v>
       </c>
+      <c r="DZ3" t="n">
+        <v>53.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7109,6 +7124,9 @@
       <c r="P4" t="n">
         <v>14.48</v>
       </c>
+      <c r="DZ4" t="n">
+        <v>14.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7163,6 +7181,9 @@
       <c r="P5" t="n">
         <v>4.45</v>
       </c>
+      <c r="DZ5" t="n">
+        <v>4.89</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7505,6 +7526,9 @@
       <c r="DZ24" t="n">
         <v>26044.82</v>
       </c>
+      <c r="EA24" t="n">
+        <v>26003.68</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7523,6 +7547,9 @@
       <c r="P25" t="n">
         <v>25.01</v>
       </c>
+      <c r="DZ25" t="n">
+        <v>26.01</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7541,6 +7568,9 @@
       <c r="P26" t="n">
         <v>41.42</v>
       </c>
+      <c r="DZ26" t="n">
+        <v>37.9</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7559,6 +7589,9 @@
       <c r="P27" t="n">
         <v>9.529999999999999</v>
       </c>
+      <c r="DZ27" t="n">
+        <v>24.1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9479,6 +9512,9 @@
       <c r="DZ39" t="n">
         <v>11.29118768979197</v>
       </c>
+      <c r="EA39" t="n">
+        <v>11.12754173094876</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9497,6 +9533,9 @@
       <c r="DZ40" t="n">
         <v>1.753517800622156</v>
       </c>
+      <c r="EA40" t="n">
+        <v>1.728103636079406</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9515,6 +9554,9 @@
       <c r="DZ41" t="n">
         <v>12.46</v>
       </c>
+      <c r="EA41" t="n">
+        <v>12.46</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9532,6 +9574,9 @@
       </c>
       <c r="DZ42" t="n">
         <v>2.06</v>
+      </c>
+      <c r="EA42" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="43">
@@ -21311,7 +21356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PA47"/>
+  <dimension ref="A1:PG47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21731,6 +21776,12 @@
     <col width="12" customWidth="1" min="415" max="415"/>
     <col width="12" customWidth="1" min="416" max="416"/>
     <col width="12" customWidth="1" min="417" max="417"/>
+    <col width="12" customWidth="1" min="418" max="418"/>
+    <col width="12" customWidth="1" min="419" max="419"/>
+    <col width="12" customWidth="1" min="420" max="420"/>
+    <col width="12" customWidth="1" min="421" max="421"/>
+    <col width="12" customWidth="1" min="422" max="422"/>
+    <col width="12" customWidth="1" min="423" max="423"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23819,6 +23870,36 @@
           <t>2026-08-28</t>
         </is>
       </c>
+      <c r="PB1" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="PC1" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="PD1" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="PE1" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="PF1" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="PG1" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23870,6 +23951,9 @@
       <c r="Y2" t="n">
         <v>3.63</v>
       </c>
+      <c r="FD2" t="n">
+        <v>3.63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23939,6 +24023,9 @@
       <c r="OX3" t="n">
         <v>88.23999999999999</v>
       </c>
+      <c r="PE3" t="n">
+        <v>96.02</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24005,6 +24092,9 @@
       <c r="OT4" t="n">
         <v>118.06</v>
       </c>
+      <c r="PA4" t="n">
+        <v>118.75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24074,6 +24164,9 @@
       <c r="OZ5" t="n">
         <v>212.09</v>
       </c>
+      <c r="PA5" t="n">
+        <v>322.87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24152,6 +24245,9 @@
       <c r="OZ6" t="n">
         <v>1.2</v>
       </c>
+      <c r="PG6" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24230,6 +24326,9 @@
       <c r="OZ7" t="n">
         <v>6.3</v>
       </c>
+      <c r="PG7" t="n">
+        <v>6.35</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24308,6 +24407,9 @@
       <c r="OZ8" t="n">
         <v>6.6</v>
       </c>
+      <c r="PG8" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24386,6 +24488,9 @@
       <c r="OZ9" t="n">
         <v>6.55</v>
       </c>
+      <c r="PG9" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24464,6 +24569,9 @@
       <c r="OZ10" t="n">
         <v>3.7</v>
       </c>
+      <c r="PG10" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24542,6 +24650,9 @@
       <c r="OZ11" t="n">
         <v>4.27</v>
       </c>
+      <c r="PG11" t="n">
+        <v>4.27</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24620,6 +24731,9 @@
       <c r="OZ12" t="n">
         <v>4.32</v>
       </c>
+      <c r="PG12" t="n">
+        <v>4.32</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24698,6 +24812,9 @@
       <c r="OZ13" t="n">
         <v>4.45</v>
       </c>
+      <c r="PG13" t="n">
+        <v>4.45</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24776,6 +24893,9 @@
       <c r="OZ14" t="n">
         <v>4.58</v>
       </c>
+      <c r="PG14" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25001,6 +25121,9 @@
       <c r="OZ17" t="n">
         <v>200982.4</v>
       </c>
+      <c r="PG17" t="n">
+        <v>242406.28</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25112,6 +25235,9 @@
       <c r="PA18" t="n">
         <v>2.25</v>
       </c>
+      <c r="PG18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25223,6 +25349,9 @@
       <c r="OY19" t="n">
         <v>3.73</v>
       </c>
+      <c r="PE19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25415,6 +25544,9 @@
       <c r="OZ21" t="n">
         <v>4.67</v>
       </c>
+      <c r="PF21" t="n">
+        <v>4.79</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -26459,6 +26591,9 @@
       <c r="OZ33" t="n">
         <v>3.84</v>
       </c>
+      <c r="PF33" t="n">
+        <v>3.92</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26567,6 +26702,9 @@
       <c r="OZ34" t="n">
         <v>4.04</v>
       </c>
+      <c r="PF34" t="n">
+        <v>4.16</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26675,6 +26813,9 @@
       <c r="OZ35" t="n">
         <v>4.2</v>
       </c>
+      <c r="PF35" t="n">
+        <v>4.39</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26783,6 +26924,9 @@
       <c r="OZ36" t="n">
         <v>4.38</v>
       </c>
+      <c r="PF36" t="n">
+        <v>4.54</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26891,6 +27035,9 @@
       <c r="OZ37" t="n">
         <v>5.19</v>
       </c>
+      <c r="PF37" t="n">
+        <v>5.27</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -27419,6 +27566,9 @@
       <c r="OZ43" t="n">
         <v>0.47</v>
       </c>
+      <c r="PF43" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -27527,6 +27677,9 @@
       <c r="OZ44" t="n">
         <v>0.83</v>
       </c>
+      <c r="PF44" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -28547,6 +28700,9 @@
       <c r="OZ46" t="n">
         <v>0</v>
       </c>
+      <c r="PG46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -29475,6 +29631,9 @@
         <v>0</v>
       </c>
       <c r="OZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="PG47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29489,7 +29648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -29501,6 +29660,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29549,6 +29709,11 @@
           <t>2026-W35</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2026-W36</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29579,6 +29744,9 @@
       <c r="I2" t="n">
         <v>5.9</v>
       </c>
+      <c r="J2" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29630,6 +29798,9 @@
       <c r="I4" t="n">
         <v>6.2</v>
       </c>
+      <c r="J4" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29660,6 +29831,9 @@
       <c r="I5" t="n">
         <v>7</v>
       </c>
+      <c r="J5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29690,6 +29864,9 @@
       <c r="I6" t="n">
         <v>6.13</v>
       </c>
+      <c r="J6" t="n">
+        <v>6.13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29735,6 +29912,9 @@
       <c r="I8" t="n">
         <v>4.5</v>
       </c>
+      <c r="J8" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29765,6 +29945,9 @@
       <c r="I9" t="n">
         <v>7.11</v>
       </c>
+      <c r="J9" t="n">
+        <v>7.14</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29855,6 +30038,9 @@
       <c r="I14" t="n">
         <v>8.5</v>
       </c>
+      <c r="J14" t="n">
+        <v>7.97</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29885,6 +30071,9 @@
       <c r="I15" t="n">
         <v>8.119999999999999</v>
       </c>
+      <c r="J15" t="n">
+        <v>8.119999999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29932,6 +30121,9 @@
       </c>
       <c r="I17" t="n">
         <v>302</v>
+      </c>
+      <c r="J17" t="n">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -39170,12 +39362,94 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>962886.7830000001</v>
+      </c>
+      <c r="F109" t="n">
+        <v>75309.442</v>
+      </c>
+      <c r="G109" t="n">
+        <v>6760.976</v>
+      </c>
+      <c r="H109" t="n">
+        <v>624269.133</v>
+      </c>
+      <c r="I109" t="n">
+        <v>648552.733</v>
+      </c>
+      <c r="J109" t="n">
+        <v>103.89</v>
+      </c>
+      <c r="K109" t="n">
+        <v>173099.211</v>
+      </c>
+      <c r="L109" t="n">
+        <v>-40538.58100000001</v>
+      </c>
+      <c r="M109" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-7.459</v>
+      </c>
+      <c r="O109" t="n">
+        <v>-10.033</v>
+      </c>
+      <c r="P109" t="n">
+        <v>740760.497</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>202771.522</v>
+      </c>
+      <c r="R109" t="n">
+        <v>365.318</v>
+      </c>
+      <c r="S109" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="T109" t="n">
+        <v>213.856</v>
+      </c>
+      <c r="U109" t="n">
+        <v>2.773</v>
+      </c>
+      <c r="V109" t="n">
+        <v>118737.975</v>
+      </c>
+      <c r="W109" t="n">
+        <v>4.703</v>
+      </c>
+      <c r="X109" t="n">
+        <v>31.553</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>12.331</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1431</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>21.166</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán 6 tháng đầu năm 2026</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2026-3/2026-09-04/no-name-1788460885.pdf</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>2026-09-01T10:01:53+07:00</t>
+          <t>2026-09-04T08:27:55+07:00</t>
         </is>
       </c>
     </row>
@@ -40723,6 +40997,78 @@
         <is>
           <t>reported</t>
         </is>
+      </c>
+      <c r="E127" t="n">
+        <v>1273076.923</v>
+      </c>
+      <c r="F127" t="n">
+        <v>188997.15</v>
+      </c>
+      <c r="G127" t="n">
+        <v>10763.002</v>
+      </c>
+      <c r="H127" t="n">
+        <v>662447.73</v>
+      </c>
+      <c r="I127" t="n">
+        <v>835813.2830000001</v>
+      </c>
+      <c r="J127" t="n">
+        <v>126.17</v>
+      </c>
+      <c r="K127" t="n">
+        <v>184453.92</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-8462.984</v>
+      </c>
+      <c r="M127" t="n">
+        <v>-0.665</v>
+      </c>
+      <c r="N127" t="n">
+        <v>-3.883</v>
+      </c>
+      <c r="O127" t="n">
+        <v>-4.521</v>
+      </c>
+      <c r="P127" t="n">
+        <v>739557.791</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>259255.935</v>
+      </c>
+      <c r="R127" t="n">
+        <v>285.262</v>
+      </c>
+      <c r="S127" t="n">
+        <v>72.98699999999999</v>
+      </c>
+      <c r="T127" t="n">
+        <v>137.01</v>
+      </c>
+      <c r="U127" t="n">
+        <v>2.784</v>
+      </c>
+      <c r="V127" t="n">
+        <v>49624.19500000001</v>
+      </c>
+      <c r="W127" t="n">
+        <v>9.231999999999999</v>
+      </c>
+      <c r="X127" t="n">
+        <v>15.674</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>3.898</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1078</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>10.016</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.57</v>
       </c>
       <c r="AF127" t="inlineStr">
         <is>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -7070,6 +7070,9 @@
       <c r="P2" t="n">
         <v>14.5</v>
       </c>
+      <c r="DZ2" t="n">
+        <v>14.4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9513,7 +9516,7 @@
         <v>11.29118768979197</v>
       </c>
       <c r="EA39" t="n">
-        <v>11.12754173094876</v>
+        <v>11.13551538048197</v>
       </c>
     </row>
     <row r="40">
@@ -9534,7 +9537,7 @@
         <v>1.753517800622156</v>
       </c>
       <c r="EA40" t="n">
-        <v>1.728103636079406</v>
+        <v>1.729341941276036</v>
       </c>
     </row>
     <row r="41">
@@ -9656,6 +9659,9 @@
       <c r="DY43" t="n">
         <v>24.3</v>
       </c>
+      <c r="DZ43" t="n">
+        <v>50.5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10001,6 +10007,9 @@
       <c r="DY48" t="n">
         <v>221.8</v>
       </c>
+      <c r="DZ48" t="n">
+        <v>546.8</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -10073,6 +10082,9 @@
       <c r="DY50" t="n">
         <v>56.2</v>
       </c>
+      <c r="DZ50" t="n">
+        <v>101.3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12541,6 +12553,9 @@
       </c>
       <c r="DY62" t="n">
         <v>8.9</v>
+      </c>
+      <c r="DZ62" t="n">
+        <v>17.25</v>
       </c>
     </row>
     <row r="63">
@@ -21356,7 +21371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PG47"/>
+  <dimension ref="A1:PH47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21782,6 +21797,7 @@
     <col width="12" customWidth="1" min="421" max="421"/>
     <col width="12" customWidth="1" min="422" max="422"/>
     <col width="12" customWidth="1" min="423" max="423"/>
+    <col width="12" customWidth="1" min="424" max="424"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23900,6 +23916,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="PH1" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24167,6 +24188,9 @@
       <c r="PA5" t="n">
         <v>322.87</v>
       </c>
+      <c r="PG5" t="n">
+        <v>-1529.09</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25238,6 +25262,9 @@
       <c r="PG18" t="n">
         <v>2.25</v>
       </c>
+      <c r="PH18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25350,6 +25377,9 @@
         <v>3.73</v>
       </c>
       <c r="PE19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="PF19" t="n">
         <v>3.73</v>
       </c>
     </row>
@@ -29832,7 +29862,7 @@
         <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="6">
@@ -29865,7 +29895,7 @@
         <v>6.13</v>
       </c>
       <c r="J6" t="n">
-        <v>6.13</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="7">
@@ -29946,7 +29976,7 @@
         <v>7.11</v>
       </c>
       <c r="J9" t="n">
-        <v>7.14</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="10">

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -7530,7 +7530,7 @@
         <v>26044.82</v>
       </c>
       <c r="EA24" t="n">
-        <v>26003.68</v>
+        <v>25969.41</v>
       </c>
     </row>
     <row r="25">
@@ -9516,7 +9516,7 @@
         <v>11.29118768979197</v>
       </c>
       <c r="EA39" t="n">
-        <v>11.13551538048197</v>
+        <v>11.01768742958977</v>
       </c>
     </row>
     <row r="40">
@@ -9537,7 +9537,7 @@
         <v>1.753517800622156</v>
       </c>
       <c r="EA40" t="n">
-        <v>1.729341941276036</v>
+        <v>1.711043298566635</v>
       </c>
     </row>
     <row r="41">
@@ -9558,7 +9558,7 @@
         <v>12.46</v>
       </c>
       <c r="EA41" t="n">
-        <v>12.46</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="42">
@@ -9579,7 +9579,7 @@
         <v>2.06</v>
       </c>
       <c r="EA42" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="43">
@@ -14090,6 +14090,9 @@
       <c r="DZ68" t="n">
         <v>3.662</v>
       </c>
+      <c r="EA68" t="n">
+        <v>3.669</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -14486,6 +14489,9 @@
       <c r="DZ69" t="n">
         <v>3.771</v>
       </c>
+      <c r="EA69" t="n">
+        <v>3.788</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -15278,6 +15284,9 @@
       <c r="DZ71" t="n">
         <v>10.9</v>
       </c>
+      <c r="EA71" t="n">
+        <v>11.9</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -15674,6 +15683,9 @@
       <c r="DZ72" t="n">
         <v>-0.16</v>
       </c>
+      <c r="EA72" t="n">
+        <v>-0.212</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -16070,6 +16082,9 @@
       <c r="DZ73" t="n">
         <v>-0.479</v>
       </c>
+      <c r="EA73" t="n">
+        <v>-0.582</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -16511,6 +16526,9 @@
       <c r="O75" t="n">
         <v>1.943</v>
       </c>
+      <c r="P75" t="n">
+        <v>1.943</v>
+      </c>
       <c r="Q75" t="n">
         <v>0.37</v>
       </c>
@@ -17246,6 +17264,9 @@
       <c r="DZ76" t="n">
         <v>26249</v>
       </c>
+      <c r="EA76" t="n">
+        <v>26070</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -17636,6 +17657,9 @@
       <c r="DZ77" t="n">
         <v>14.975</v>
       </c>
+      <c r="EA77" t="n">
+        <v>14.26</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18031,6 +18055,9 @@
       </c>
       <c r="DZ78" t="n">
         <v>1764.78</v>
+      </c>
+      <c r="EA78" t="n">
+        <v>1827.72</v>
       </c>
     </row>
   </sheetData>
@@ -21371,7 +21398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PH47"/>
+  <dimension ref="A1:PK47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21798,6 +21825,9 @@
     <col width="12" customWidth="1" min="422" max="422"/>
     <col width="12" customWidth="1" min="423" max="423"/>
     <col width="12" customWidth="1" min="424" max="424"/>
+    <col width="12" customWidth="1" min="425" max="425"/>
+    <col width="12" customWidth="1" min="426" max="426"/>
+    <col width="12" customWidth="1" min="427" max="427"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23921,6 +23951,21 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="PI1" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="PJ1" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="PK1" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24191,6 +24236,9 @@
       <c r="PG5" t="n">
         <v>-1529.09</v>
       </c>
+      <c r="PK5" t="n">
+        <v>-465.93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24272,6 +24320,9 @@
       <c r="PG6" t="n">
         <v>6</v>
       </c>
+      <c r="PH6" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24353,6 +24404,9 @@
       <c r="PG7" t="n">
         <v>6.35</v>
       </c>
+      <c r="PH7" t="n">
+        <v>5.15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24434,6 +24488,9 @@
       <c r="PG8" t="n">
         <v>6.5</v>
       </c>
+      <c r="PH8" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24515,6 +24572,9 @@
       <c r="PG9" t="n">
         <v>6.5</v>
       </c>
+      <c r="PH9" t="n">
+        <v>6.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24596,6 +24656,9 @@
       <c r="PG10" t="n">
         <v>3.7</v>
       </c>
+      <c r="PH10" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24677,6 +24740,9 @@
       <c r="PG11" t="n">
         <v>4.27</v>
       </c>
+      <c r="PH11" t="n">
+        <v>4.27</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24758,6 +24824,9 @@
       <c r="PG12" t="n">
         <v>4.32</v>
       </c>
+      <c r="PH12" t="n">
+        <v>4.33</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24839,6 +24908,9 @@
       <c r="PG13" t="n">
         <v>4.45</v>
       </c>
+      <c r="PH13" t="n">
+        <v>4.46</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24920,6 +24992,9 @@
       <c r="PG14" t="n">
         <v>4.58</v>
       </c>
+      <c r="PH14" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24998,6 +25073,9 @@
       <c r="OZ15" t="n">
         <v>9596.25</v>
       </c>
+      <c r="PH15" t="n">
+        <v>5625.56</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25148,6 +25226,9 @@
       <c r="PG17" t="n">
         <v>242406.28</v>
       </c>
+      <c r="PH17" t="n">
+        <v>248031.84</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25265,6 +25346,9 @@
       <c r="PH18" t="n">
         <v>2.25</v>
       </c>
+      <c r="PK18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25382,6 +25466,9 @@
       <c r="PF19" t="n">
         <v>3.73</v>
       </c>
+      <c r="PG19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25577,6 +25664,9 @@
       <c r="PF21" t="n">
         <v>4.79</v>
       </c>
+      <c r="PG21" t="n">
+        <v>4.77</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25913,6 +26003,9 @@
       <c r="DK25" t="n">
         <v>4.1</v>
       </c>
+      <c r="FD25" t="n">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -26000,6 +26093,9 @@
       <c r="DK26" t="n">
         <v>-20</v>
       </c>
+      <c r="FD26" t="n">
+        <v>162</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -26624,6 +26720,9 @@
       <c r="PF33" t="n">
         <v>3.92</v>
       </c>
+      <c r="PG33" t="n">
+        <v>3.89</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26735,6 +26834,9 @@
       <c r="PF34" t="n">
         <v>4.16</v>
       </c>
+      <c r="PG34" t="n">
+        <v>4.11</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26846,6 +26948,9 @@
       <c r="PF35" t="n">
         <v>4.39</v>
       </c>
+      <c r="PG35" t="n">
+        <v>4.34</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26957,6 +27062,9 @@
       <c r="PF36" t="n">
         <v>4.54</v>
       </c>
+      <c r="PG36" t="n">
+        <v>4.52</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -27068,6 +27176,9 @@
       <c r="PF37" t="n">
         <v>5.27</v>
       </c>
+      <c r="PG37" t="n">
+        <v>5.25</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -27599,6 +27710,9 @@
       <c r="PF43" t="n">
         <v>0.4</v>
       </c>
+      <c r="PG43" t="n">
+        <v>0.43</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -27710,6 +27824,9 @@
       <c r="PF44" t="n">
         <v>0.87</v>
       </c>
+      <c r="PG44" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -28733,6 +28850,9 @@
       <c r="PG46" t="n">
         <v>0</v>
       </c>
+      <c r="PH46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -29664,6 +29784,9 @@
         <v>0</v>
       </c>
       <c r="PG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="PH47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29678,7 +29801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -29691,6 +29814,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29744,6 +29868,11 @@
           <t>2026-W36</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29777,6 +29906,9 @@
       <c r="J2" t="n">
         <v>5.9</v>
       </c>
+      <c r="K2" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29831,6 +29963,9 @@
       <c r="J4" t="n">
         <v>6.2</v>
       </c>
+      <c r="K4" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29864,6 +29999,9 @@
       <c r="J5" t="n">
         <v>7.15</v>
       </c>
+      <c r="K5" t="n">
+        <v>7.15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29897,6 +30035,9 @@
       <c r="J6" t="n">
         <v>6.15</v>
       </c>
+      <c r="K6" t="n">
+        <v>6.15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29945,6 +30086,9 @@
       <c r="J8" t="n">
         <v>4.5</v>
       </c>
+      <c r="K8" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29978,6 +30122,9 @@
       <c r="J9" t="n">
         <v>7.32</v>
       </c>
+      <c r="K9" t="n">
+        <v>7.17</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30071,6 +30218,9 @@
       <c r="J14" t="n">
         <v>7.97</v>
       </c>
+      <c r="K14" t="n">
+        <v>9.199999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30104,6 +30254,9 @@
       <c r="J15" t="n">
         <v>8.119999999999999</v>
       </c>
+      <c r="K15" t="n">
+        <v>8.119999999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -30154,6 +30307,9 @@
       </c>
       <c r="J17" t="n">
         <v>309</v>
+      </c>
+      <c r="K17" t="n">
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -7421,6 +7421,9 @@
       <c r="O18" t="n">
         <v>8.369999999999999</v>
       </c>
+      <c r="P18" t="n">
+        <v>8.970000000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7457,6 +7460,9 @@
       <c r="N20" t="n">
         <v>10.76</v>
       </c>
+      <c r="O20" t="n">
+        <v>10.39</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7530,7 +7536,7 @@
         <v>26044.82</v>
       </c>
       <c r="EA24" t="n">
-        <v>25969.41</v>
+        <v>25879.19</v>
       </c>
     </row>
     <row r="25">
@@ -7593,7 +7599,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="DZ27" t="n">
-        <v>24.1</v>
+        <v>33.62</v>
       </c>
     </row>
     <row r="28">
@@ -7889,6 +7895,9 @@
       <c r="DY31" t="n">
         <v>3.33</v>
       </c>
+      <c r="DZ31" t="n">
+        <v>4.55</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7958,6 +7967,9 @@
       <c r="DY32" t="n">
         <v>18.4</v>
       </c>
+      <c r="DZ32" t="n">
+        <v>40.6</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9516,7 +9528,7 @@
         <v>11.29118768979197</v>
       </c>
       <c r="EA39" t="n">
-        <v>11.01768742958977</v>
+        <v>11.08924285748085</v>
       </c>
     </row>
     <row r="40">
@@ -9537,7 +9549,7 @@
         <v>1.753517800622156</v>
       </c>
       <c r="EA40" t="n">
-        <v>1.711043298566635</v>
+        <v>1.722155833402237</v>
       </c>
     </row>
     <row r="41">
@@ -9558,7 +9570,7 @@
         <v>12.46</v>
       </c>
       <c r="EA41" t="n">
-        <v>12.64</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="42">
@@ -9579,7 +9591,7 @@
         <v>2.06</v>
       </c>
       <c r="EA42" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="43">
@@ -9731,6 +9743,9 @@
       <c r="DY44" t="n">
         <v>4.6</v>
       </c>
+      <c r="DZ44" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -11504,6 +11519,9 @@
       <c r="DY57" t="n">
         <v>1.25</v>
       </c>
+      <c r="DZ57" t="n">
+        <v>1.57</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -11753,6 +11771,9 @@
       <c r="DY58" t="n">
         <v>1.15</v>
       </c>
+      <c r="DZ58" t="n">
+        <v>1.24</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -12002,6 +12023,9 @@
       <c r="DY59" t="n">
         <v>0.73</v>
       </c>
+      <c r="DZ59" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -12251,6 +12275,9 @@
       <c r="DY60" t="n">
         <v>-0.55</v>
       </c>
+      <c r="DZ60" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -12499,6 +12526,9 @@
       </c>
       <c r="DY61" t="n">
         <v>0.66</v>
+      </c>
+      <c r="DZ61" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="62">
@@ -21398,7 +21428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PK47"/>
+  <dimension ref="A1:PN47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21828,6 +21858,9 @@
     <col width="12" customWidth="1" min="425" max="425"/>
     <col width="12" customWidth="1" min="426" max="426"/>
     <col width="12" customWidth="1" min="427" max="427"/>
+    <col width="12" customWidth="1" min="428" max="428"/>
+    <col width="12" customWidth="1" min="429" max="429"/>
+    <col width="12" customWidth="1" min="430" max="430"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23966,6 +23999,21 @@
           <t>2026-09-07</t>
         </is>
       </c>
+      <c r="PL1" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="PM1" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="PN1" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24092,6 +24140,9 @@
       <c r="PE3" t="n">
         <v>96.02</v>
       </c>
+      <c r="PM3" t="n">
+        <v>109.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24161,6 +24212,9 @@
       <c r="PA4" t="n">
         <v>118.75</v>
       </c>
+      <c r="PH4" t="n">
+        <v>118.07</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24239,6 +24293,9 @@
       <c r="PK5" t="n">
         <v>-465.93</v>
       </c>
+      <c r="PN5" t="n">
+        <v>285.01</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24323,6 +24380,9 @@
       <c r="PH6" t="n">
         <v>4.6</v>
       </c>
+      <c r="PN6" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24407,6 +24467,9 @@
       <c r="PH7" t="n">
         <v>5.15</v>
       </c>
+      <c r="PN7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24491,6 +24554,9 @@
       <c r="PH8" t="n">
         <v>6.5</v>
       </c>
+      <c r="PN8" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24575,6 +24641,9 @@
       <c r="PH9" t="n">
         <v>6.3</v>
       </c>
+      <c r="PN9" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24659,6 +24728,9 @@
       <c r="PH10" t="n">
         <v>3.7</v>
       </c>
+      <c r="PN10" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24743,6 +24815,9 @@
       <c r="PH11" t="n">
         <v>4.27</v>
       </c>
+      <c r="PN11" t="n">
+        <v>4.27</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24827,6 +24902,9 @@
       <c r="PH12" t="n">
         <v>4.33</v>
       </c>
+      <c r="PN12" t="n">
+        <v>4.33</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24911,6 +24989,9 @@
       <c r="PH13" t="n">
         <v>4.46</v>
       </c>
+      <c r="PN13" t="n">
+        <v>4.46</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24995,6 +25076,9 @@
       <c r="PH14" t="n">
         <v>4.58</v>
       </c>
+      <c r="PN14" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25076,6 +25160,9 @@
       <c r="PH15" t="n">
         <v>5625.56</v>
       </c>
+      <c r="PN15" t="n">
+        <v>-2577.59</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25229,6 +25316,9 @@
       <c r="PH17" t="n">
         <v>248031.84</v>
       </c>
+      <c r="PN17" t="n">
+        <v>252649.14</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25349,6 +25439,9 @@
       <c r="PK18" t="n">
         <v>2.25</v>
       </c>
+      <c r="PN18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25469,6 +25562,9 @@
       <c r="PG19" t="n">
         <v>3.73</v>
       </c>
+      <c r="PL19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25667,6 +25763,9 @@
       <c r="PG21" t="n">
         <v>4.77</v>
       </c>
+      <c r="PM21" t="n">
+        <v>4.83</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -26723,6 +26822,9 @@
       <c r="PG33" t="n">
         <v>3.89</v>
       </c>
+      <c r="PM33" t="n">
+        <v>3.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26837,6 +26939,9 @@
       <c r="PG34" t="n">
         <v>4.11</v>
       </c>
+      <c r="PM34" t="n">
+        <v>4.17</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26951,6 +27056,9 @@
       <c r="PG35" t="n">
         <v>4.34</v>
       </c>
+      <c r="PM35" t="n">
+        <v>4.43</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -27065,6 +27173,9 @@
       <c r="PG36" t="n">
         <v>4.52</v>
       </c>
+      <c r="PM36" t="n">
+        <v>4.61</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -27179,6 +27290,9 @@
       <c r="PG37" t="n">
         <v>5.25</v>
       </c>
+      <c r="PM37" t="n">
+        <v>5.28</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -27713,6 +27827,9 @@
       <c r="PG43" t="n">
         <v>0.43</v>
       </c>
+      <c r="PM43" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -27827,6 +27944,9 @@
       <c r="PG44" t="n">
         <v>0.88</v>
       </c>
+      <c r="PM44" t="n">
+        <v>0.88</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -28853,6 +28973,9 @@
       <c r="PH46" t="n">
         <v>0</v>
       </c>
+      <c r="PN46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -29787,6 +29910,9 @@
         <v>0</v>
       </c>
       <c r="PH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="PN47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30123,7 +30249,7 @@
         <v>7.32</v>
       </c>
       <c r="K9" t="n">
-        <v>7.17</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="10">
@@ -30219,7 +30345,7 @@
         <v>7.97</v>
       </c>
       <c r="K14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="15">
@@ -30309,7 +30435,7 @@
         <v>309</v>
       </c>
       <c r="K17" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -9528,7 +9528,7 @@
         <v>11.29118768979197</v>
       </c>
       <c r="EA39" t="n">
-        <v>11.08924285748085</v>
+        <v>10.87364191092571</v>
       </c>
     </row>
     <row r="40">
@@ -9549,7 +9549,7 @@
         <v>1.753517800622156</v>
       </c>
       <c r="EA40" t="n">
-        <v>1.722155833402237</v>
+        <v>1.688673076051811</v>
       </c>
     </row>
     <row r="41">
@@ -21428,7 +21428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PN47"/>
+  <dimension ref="A1:PO47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21861,6 +21861,7 @@
     <col width="12" customWidth="1" min="428" max="428"/>
     <col width="12" customWidth="1" min="429" max="429"/>
     <col width="12" customWidth="1" min="430" max="430"/>
+    <col width="12" customWidth="1" min="431" max="431"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24014,6 +24015,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="PO1" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24294,7 +24300,7 @@
         <v>-465.93</v>
       </c>
       <c r="PN5" t="n">
-        <v>285.01</v>
+        <v>367.01</v>
       </c>
     </row>
     <row r="6">
@@ -25442,6 +25448,9 @@
       <c r="PN18" t="n">
         <v>2.25</v>
       </c>
+      <c r="PO18" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25563,6 +25572,9 @@
         <v>3.73</v>
       </c>
       <c r="PL19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="PM19" t="n">
         <v>3.73</v>
       </c>
     </row>
@@ -30249,7 +30261,7 @@
         <v>7.32</v>
       </c>
       <c r="K9" t="n">
-        <v>7.06</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="10">
@@ -30345,7 +30357,7 @@
         <v>7.97</v>
       </c>
       <c r="K14" t="n">
-        <v>8.26</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="15">
